--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d40006\Documents\Dataland Project\Dataland\dataland-framework-toolbox\inputs\sfdr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dataland\datalandAlternative\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A91B7D7-4F81-46BF-99BF-699B9FC8F694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF6A987-99F1-4D4E-9B94-CF9C4465A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
+    <workbookView xWindow="63890" yWindow="-10810" windowWidth="38620" windowHeight="21100" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="438">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -1377,6 +1377,12 @@
   </si>
   <si>
     <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the market-based method (equity share approach preferably used).</t>
+  </si>
+  <si>
+    <t>Field Calculation</t>
+  </si>
+  <si>
+    <t>Sum: [extendedDecimalScope1GhgEmissionsInTonnes;extendedDecimalScope2GhgEmissionsInTonnes]; Division: [example1,example2]</t>
   </si>
 </sst>
 </file>
@@ -1794,17 +1800,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBCA27A-793A-4293-9394-36A2BE726731}">
-  <dimension ref="A1:N114"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O114"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1847,8 +1861,11 @@
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1886,7 +1903,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1924,7 +1941,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1962,7 +1979,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1998,7 +2015,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="6" customFormat="1">
+    <row r="6" spans="1:15" s="6" customFormat="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2033,7 +2050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1">
+    <row r="7" spans="1:15" s="6" customFormat="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2064,7 +2081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="6" customFormat="1">
+    <row r="8" spans="1:15" s="6" customFormat="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2108,7 +2125,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="6" customFormat="1">
+    <row r="9" spans="1:15" s="6" customFormat="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2152,7 +2169,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="6" customFormat="1">
+    <row r="10" spans="1:15" s="6" customFormat="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2184,8 +2201,11 @@
       <c r="K10" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="6" customFormat="1">
+      <c r="O10" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="6" customFormat="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2218,7 +2238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="6" customFormat="1">
+    <row r="12" spans="1:15" s="6" customFormat="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2251,7 +2271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="6" customFormat="1">
+    <row r="13" spans="1:15" s="6" customFormat="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2286,7 +2306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="6" customFormat="1">
+    <row r="14" spans="1:15" s="6" customFormat="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2317,7 +2337,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="6" customFormat="1">
+    <row r="15" spans="1:15" s="6" customFormat="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2348,7 +2368,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="6" customFormat="1">
+    <row r="16" spans="1:15" s="6" customFormat="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d40006\Documents\Dataland Project\Dataland\dataland-framework-toolbox\inputs\sfdr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A91B7D7-4F81-46BF-99BF-699B9FC8F694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212D04C2-B71C-4EF8-96DC-EA790CF686A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
+    <workbookView xWindow="19110" yWindow="480" windowWidth="19380" windowHeight="20490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Framework Data Model" sheetId="2" r:id="rId1"/>
+    <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Framework Data Model'!$A$1:$N$114</definedName>
@@ -48,28 +48,12 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="436">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -83,6 +67,9 @@
     <t>Field Name</t>
   </si>
   <si>
+    <t>Alias Export</t>
+  </si>
+  <si>
     <t>Tooltip - upload page</t>
   </si>
   <si>
@@ -110,9 +97,21 @@
     <t>Mandatory Field</t>
   </si>
   <si>
+    <t>Field Calculation</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
+    <t>Data Date</t>
+  </si>
+  <si>
+    <t>DATA_DATE</t>
+  </si>
+  <si>
+    <t>The year for which the data is reported.</t>
+  </si>
+  <si>
     <t> </t>
   </si>
   <si>
@@ -122,6 +121,9 @@
     <t>Fiscal Year Deviation</t>
   </si>
   <si>
+    <t>FISCAL_YEAR_DEVIATION</t>
+  </si>
+  <si>
     <t>Does the fiscal year deviate from the calendar year?</t>
   </si>
   <si>
@@ -131,12 +133,24 @@
     <t>Deviation| No Deviation</t>
   </si>
   <si>
+    <t>Extended</t>
+  </si>
+  <si>
     <t>Fiscal Year End</t>
   </si>
   <si>
+    <t>FISCAL_YEAR_END</t>
+  </si>
+  <si>
+    <t>The date the fiscal year ends.</t>
+  </si>
+  <si>
     <t>Referenced Reports</t>
   </si>
   <si>
+    <t>REFERENCED_REPORTS</t>
+  </si>
+  <si>
     <t>Please upload all relevant reports for this dataset in the PDF format.</t>
   </si>
   <si>
@@ -149,295 +163,1087 @@
     <t>Environmental</t>
   </si>
   <si>
+    <t>Greenhouse gas emissions</t>
+  </si>
+  <si>
+    <t>Scope 1 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 1 greenhouse gas emissions in tonnes, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used).</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Allowed Range: [0, INF]</t>
+  </si>
+  <si>
+    <t>Tonnes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Greenhouse gas emissions </t>
   </si>
   <si>
-    <t>Scope 1 GHG emissions</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Tonnes</t>
-  </si>
-  <si>
-    <t>Extended</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions</t>
   </si>
   <si>
+    <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach).</t>
+  </si>
+  <si>
     <t>Scope 2 GHG emissions (location-based)</t>
   </si>
   <si>
+    <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the location-based method (equity share approach preferably used).</t>
+  </si>
+  <si>
     <t>Scope 2 GHG emissions (market-based)</t>
   </si>
   <si>
+    <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the market-based method (equity share approach preferably used).</t>
+  </si>
+  <si>
     <t>Scope 1 and 2 GHG emissions</t>
   </si>
   <si>
+    <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach).</t>
+  </si>
+  <si>
     <t>Scope 1 and 2 GHG emissions (location-based)</t>
   </si>
   <si>
+    <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
+  </si>
+  <si>
     <t>Scope 1 and 2 GHG emissions (market-based)</t>
   </si>
   <si>
+    <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
+  </si>
+  <si>
     <t>Scope 3 GHG emissions</t>
   </si>
   <si>
+    <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 3 greenhouse gas emissions in tonnes, i.e. all indirect upstream and downstream emissions that are not included in scope 2 (equity share approach preferably used).</t>
+  </si>
+  <si>
+    <t>Scope 3 upstream GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope 3 downstream GHG emissions </t>
+  </si>
+  <si>
+    <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used).</t>
+  </si>
+  <si>
     <t>Scope 1 and 2 and 3 GHG emissions</t>
   </si>
   <si>
+    <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share).</t>
+  </si>
+  <si>
+    <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
+  </si>
+  <si>
+    <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
+  </si>
+  <si>
+    <t>Scope 4 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_4_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 4, as defined by the GHG Protocol, covers emissions avoided when a product is used as a substitute for other goods or services, fulfilling the same functions but with a lower carbon intensity.</t>
+  </si>
+  <si>
     <t>Enterprise Value</t>
   </si>
   <si>
+    <t>ENTERPRISE_VALUE_IN_EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4). </t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>TOTAL_REVENUE_IN_EUR</t>
+  </si>
+  <si>
+    <t>Total revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover. Overall turnover is equivalent to a firm's total revenues over some period of time.</t>
+  </si>
+  <si>
+    <t>Carbon footprint</t>
+  </si>
+  <si>
+    <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
+  </si>
+  <si>
+    <t>Tonnes of GHG emissions per million EUR enterprise value.</t>
+  </si>
+  <si>
+    <t>Tonnes / €M Enterprise Value</t>
+  </si>
+  <si>
+    <t>GHG intensity</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
+    <t>Tonnes of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions.</t>
+  </si>
+  <si>
+    <t>Tonnes / €M Revenue</t>
+  </si>
+  <si>
+    <t>GHG intensity - scope 1</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
+    <t>Tonnes of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions).</t>
+  </si>
+  <si>
+    <t>GHG intensity - scope 2</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
+    <t>Tonnes of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions.</t>
+  </si>
+  <si>
+    <t>GHG intensity - scope 3</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
+    <t>Tonnes of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions.</t>
+  </si>
+  <si>
+    <t>GHG intensity - scope 4</t>
+  </si>
+  <si>
+    <t>GHG_INTENSITY_SCOPE_4_IN_T_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
+    <t>Tonnes of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
+  </si>
+  <si>
+    <t>Fossil Fuel Sector Exposure</t>
+  </si>
+  <si>
+    <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company derive any revenues from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels? (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
+  </si>
+  <si>
+    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
+  </si>
+  <si>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>Financed scope 1 and scope 2 emissions</t>
+  </si>
+  <si>
+    <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>The sum of scope 1 and scope 2 emissions of financed companies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonnes </t>
+  </si>
+  <si>
+    <t>Financed scope 3 emissions</t>
+  </si>
+  <si>
+    <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>The scope 3 emissions of financed companies.</t>
+  </si>
+  <si>
+    <t>Energy performance</t>
+  </si>
+  <si>
+    <t>Renewable Energy Production</t>
+  </si>
+  <si>
+    <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
+  </si>
+  <si>
+    <t>GWh</t>
+  </si>
+  <si>
+    <t>Renewable Energy Consumption</t>
+  </si>
+  <si>
+    <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Production</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy produced, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
+  </si>
+  <si>
+    <t>Relative Non-Renewable Energy Production</t>
+  </si>
+  <si>
+    <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable).</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy consumed, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
+  </si>
+  <si>
+    <t>Relative Non-Renewable Energy Consumption</t>
+  </si>
+  <si>
+    <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable).</t>
+  </si>
+  <si>
+    <t>Applicable High Impact Climate Sectors</t>
+  </si>
+  <si>
+    <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
+  </si>
+  <si>
+    <t>Please select any sector(s) applicable activities (NACE Codes A-H, L).</t>
+  </si>
+  <si>
+    <t>Sector applicable activities.</t>
+  </si>
+  <si>
+    <t>Custom - SFDR High Impact Climate Sectors</t>
+  </si>
+  <si>
+    <t>Total High Impact Climate Sector Energy Consumption</t>
+  </si>
+  <si>
+    <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
+  </si>
+  <si>
+    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1).</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Fossil Fuels</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, nuclear energy, lignite and coal) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Crude Oil</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Natural Gas</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Lignite</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Coal</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Nuclear Energy</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Non-Renewable Energy Consumption Other</t>
+  </si>
+  <si>
+    <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
+  </si>
+  <si>
+    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Biodiversity</t>
+  </si>
+  <si>
+    <t>Primary Forest And Wooded Land Of Native Species Exposure</t>
+  </si>
+  <si>
+    <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company have sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments? Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
+  </si>
+  <si>
+    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
+  </si>
+  <si>
+    <t>Protected Areas Exposure</t>
+  </si>
+  <si>
+    <t>PROTECTED_AREAS_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company have sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions? For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
+  </si>
+  <si>
+    <t>Sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions. For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
+  </si>
+  <si>
+    <t>Rare Or Endangered Ecosystems Exposure</t>
+  </si>
+  <si>
+    <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company have sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated? For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
+  </si>
+  <si>
+    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
+  </si>
+  <si>
+    <t>Highly Biodiverse Grassland Exposure</t>
+  </si>
+  <si>
+    <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company have sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status?</t>
+  </si>
+  <si>
+    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.</t>
+  </si>
+  <si>
+    <t>Manufacture Of Agrochemical Pesticides Products</t>
+  </si>
+  <si>
+    <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
+  </si>
+  <si>
+    <t>Is the company involved in manufacture of pesticides and other agrochemical products? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
+  </si>
+  <si>
+    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
+  </si>
+  <si>
+    <t>Land Degradation Desertification Soil Sealing Exposure</t>
+  </si>
+  <si>
+    <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Is the company involved in activities, which cause land degradation, desertification or soil sealing? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
+  </si>
+  <si>
+    <t>Involvement in activities, which cause land degradation, desertification or soil sealing. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
+  </si>
+  <si>
+    <t>Sustainable Agriculture Policy</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have sustainable land or agriculture practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of sustainable land or agriculture practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.</t>
+  </si>
+  <si>
+    <t>Sustainable Oceans And Seas Policy</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have sustainable oceans or seas practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.) If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of sustainable oceans or seas practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.</t>
+  </si>
+  <si>
+    <t>Threatened Species Exposure</t>
+  </si>
+  <si>
+    <t>THREATENED_SPECIES_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company have operations, which affect threatened species? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
+  </si>
+  <si>
+    <t>Operations, which affect threatened species. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
+  </si>
+  <si>
+    <t>Biodiversity Protection Policy</t>
+  </si>
+  <si>
+    <t>BIODIVERSITY_PROTECTION_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2.) If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2 .</t>
+  </si>
+  <si>
+    <t>Deforestation Policy</t>
+  </si>
+  <si>
+    <t>DEFORESTATION_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a policy to address deforestation? If yes, please share the policy with us. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
+  </si>
+  <si>
+    <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Emissions To Water</t>
+  </si>
+  <si>
+    <t>EMISSIONS_TO_WATER_IN_T</t>
+  </si>
+  <si>
+    <t>Emissions to water in tonnes (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See  Regulation (EU) 2022/1288, Annex I, top (12).</t>
+  </si>
+  <si>
+    <t>Water Consumption</t>
+  </si>
+  <si>
+    <t>WATER_CONS_IN_M3</t>
+  </si>
+  <si>
+    <t>Amount of water consumed by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1 .</t>
+  </si>
+  <si>
+    <t>Cubic Meters</t>
+  </si>
+  <si>
+    <t>Water Reused</t>
+  </si>
+  <si>
+    <t>WATER_REUSED_IN_M3</t>
+  </si>
+  <si>
+    <t>Amount of water recycled and reused by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.2 .</t>
+  </si>
+  <si>
+    <t>Relative Water Usage</t>
+  </si>
+  <si>
+    <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
+  </si>
+  <si>
+    <t>Amount in cubic meters of fresh water used per million EUR revenue. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1.</t>
+  </si>
+  <si>
+    <t>Cubic Meters / €M Revenue</t>
+  </si>
+  <si>
+    <t>Water Management Policy</t>
+  </si>
+  <si>
+    <t>WATER_MANAGEMENT_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have policies and procedures for water management? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.) If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies and procedures for water management. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.</t>
+  </si>
+  <si>
+    <t>High Water Stress Area Exposure</t>
+  </si>
+  <si>
+    <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Does the company have sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy? See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
+  </si>
+  <si>
+    <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy. See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
+  </si>
+  <si>
+    <t>Waste</t>
+  </si>
+  <si>
+    <t>Hazardous and Radioactive Waste</t>
+  </si>
+  <si>
+    <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
+  </si>
+  <si>
+    <t>Tonnes of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactice waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).</t>
+  </si>
+  <si>
+    <t>Non-Recycled Waste</t>
+  </si>
+  <si>
+    <t>NON_RECYCLED_WASTE_IN_T</t>
+  </si>
+  <si>
+    <t>Tonnes of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17) and table 2, indicator nr. 13.</t>
+  </si>
+  <si>
+    <t>Emissions</t>
+  </si>
+  <si>
+    <t>Emissions of Inorganic Pollutants</t>
+  </si>
+  <si>
+    <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
+  </si>
+  <si>
+    <t>Tonnes of emissions by inorganic pollutants. Inorganic pollutants include those resulting from radiant energy, noise, heat, or light, as well as substances like arsenic, cadmium, lead, mercury, chromium, aluminum, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, iron, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27) and table 2, indicator nr. 1.</t>
+  </si>
+  <si>
+    <t>Emissions of Air Pollutants</t>
+  </si>
+  <si>
+    <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
+  </si>
+  <si>
+    <t>Tonnes of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and table 2, indicator nr. 2 and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.</t>
+  </si>
+  <si>
+    <t>Emissions of Ozone Depletion Substances</t>
+  </si>
+  <si>
+    <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
+  </si>
+  <si>
+    <t>Tonnes of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and table 2, indicator nr. 3 and the Montreal Protocol on Substances that Deplete the Ozone Layer.</t>
+  </si>
+  <si>
+    <t>Carbon Reduction Initiatives</t>
+  </si>
+  <si>
+    <t>CARBON_REDUCTION_INITIATIVES</t>
+  </si>
+  <si>
+    <t>Does the company have any policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.) If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Social and employee matters</t>
+  </si>
+  <si>
+    <t>Human Rights Legal Proceedings</t>
+  </si>
+  <si>
+    <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
+  </si>
+  <si>
+    <t>Has the company been involved in Human Rights related legal proceedings?</t>
+  </si>
+  <si>
+    <t>Involvement in Human Rights related legal proceedings.</t>
+  </si>
+  <si>
+    <t>ILO Core Labour Standards</t>
+  </si>
+  <si>
+    <t>ILO_CORE_LABOUR_STANDARDS</t>
+  </si>
+  <si>
+    <t>Does the company abide by the ILO Core Labour Standards?</t>
+  </si>
+  <si>
+    <t>Abidance by the ILO Core Labour Standards.</t>
+  </si>
+  <si>
+    <t>Environmental Policy</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have an environmental policy? If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of an environmental policy.</t>
+  </si>
+  <si>
+    <t>Corruption Legal Proceedings</t>
+  </si>
+  <si>
+    <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
+  </si>
+  <si>
+    <t>Has the company been involved in corruption-related legal proceedings?</t>
+  </si>
+  <si>
+    <t>Involvement in corruption-related legal proceedings.</t>
+  </si>
+  <si>
+    <t>Transparency Disclosure Policy</t>
+  </si>
+  <si>
+    <t>TRANSPARENCY_DISCLOSURE_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a transparency policy? If yes, please share the policy with us. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
+  </si>
+  <si>
+    <t>Existence of a transparency policy. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
+  </si>
+  <si>
+    <t>Human Rights Due Diligence Policy</t>
+  </si>
+  <si>
+    <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact? If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.</t>
+  </si>
+  <si>
+    <t>Policy against Child Labour</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_CHILD_LABOUR</t>
+  </si>
+  <si>
+    <t>Does the company have policies in place to abolish all forms of child labour? If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of child labour.</t>
+  </si>
+  <si>
+    <t>Policy against Forced Labour</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_FORCED_LABOUR</t>
+  </si>
+  <si>
+    <t>Does the company have policies in place to abolish all forms of forced labour? If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of forced labour.</t>
+  </si>
+  <si>
+    <t>Policy against Discrimination in the Workplace</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
+  </si>
+  <si>
+    <t>Does the company have policies in place to eliminate discrimination in the workplace? If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
+  </si>
+  <si>
+    <t>ISO 14001 Certificate</t>
+  </si>
+  <si>
+    <t>ISO_14001_CERTIFICATE</t>
+  </si>
+  <si>
+    <t>Is the company ISO 14001 certified (Environmental Management)? If yes, please share the certificate with us.</t>
+  </si>
+  <si>
+    <t>The company is ISO 14001 certified.</t>
+  </si>
+  <si>
+    <t>Policy against Bribery and Corruption</t>
+  </si>
+  <si>
+    <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
+  </si>
+  <si>
+    <t>Does the company have a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.) If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.</t>
+  </si>
+  <si>
+    <t>Fair Business Marketing Advertising Policy</t>
+  </si>
+  <si>
+    <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services? If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
+  </si>
+  <si>
+    <t>Technologies Expertise Transfer Policy</t>
+  </si>
+  <si>
+    <t>TECHNOLOGIES_EXPERTISE_TRANSFER_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise? If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise.</t>
+  </si>
+  <si>
+    <t>Fair Competition Policy</t>
+  </si>
+  <si>
+    <t>FAIR_COMPETITION_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have policies and procedures in place related to fair competition and anti-competitive cartels? If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
+  </si>
+  <si>
+    <t>Violation Of Tax Rules And Regulation</t>
+  </si>
+  <si>
+    <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
+  </si>
+  <si>
+    <t>Is the company involved in a violation of OECD Guidelines for Multinational Enterprises for Taxation? In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
+  </si>
+  <si>
+    <t>Involvement in a violation of OECD Guidelines for Multinational Enterprises for Taxation: In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
+  </si>
+  <si>
+    <t>UN Global Compact Principles Compliance Policy</t>
+  </si>
+  <si>
+    <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
+  </si>
+  <si>
+    <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
+  </si>
+  <si>
+    <t>OECD Guidelines For Multinational Enterprises Grievance Handling</t>
+  </si>
+  <si>
+    <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
+  </si>
+  <si>
+    <t>Does the company have grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
+  </si>
+  <si>
+    <t>Average Gross Hourly Earnings Male Employees</t>
+  </si>
+  <si>
+    <t>AVG_GROSS_HOURLY_EARNINGS_MALE_EMPLOYEES</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of male employees</t>
+  </si>
+  <si>
     <t>Currency</t>
   </si>
   <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>Carbon footprint</t>
-  </si>
-  <si>
-    <t>Tonnes / €M Revenue</t>
-  </si>
-  <si>
-    <t>GHG intensity</t>
-  </si>
-  <si>
-    <t>Fossil Fuel Sector Exposure</t>
-  </si>
-  <si>
-    <t>Energy performance</t>
-  </si>
-  <si>
-    <t>Renewable Energy Production</t>
-  </si>
-  <si>
-    <t>Allowed Range: [0, INF]</t>
-  </si>
-  <si>
-    <t>GWh</t>
-  </si>
-  <si>
-    <t>Renewable Energy Consumption</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Production</t>
-  </si>
-  <si>
-    <t>Relative Non-Renewable Energy Production</t>
-  </si>
-  <si>
-    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
-    <t>Percent</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption</t>
-  </si>
-  <si>
-    <t>Relative Non-Renewable Energy Consumption</t>
-  </si>
-  <si>
-    <t>Applicable High Impact Climate Sectors</t>
-  </si>
-  <si>
-    <t>Custom - SFDR High Impact Climate Sectors</t>
-  </si>
-  <si>
-    <t>Total High Impact Climate Sector Energy Consumption</t>
-  </si>
-  <si>
-    <t>Biodiversity</t>
-  </si>
-  <si>
-    <t>Primary Forest And Wooded Land Of Native Species Exposure</t>
-  </si>
-  <si>
-    <t>Protected Areas Exposure</t>
-  </si>
-  <si>
-    <t>Rare Or Endangered Ecosystems Exposure</t>
-  </si>
-  <si>
-    <t>Highly Biodiverse Grassland Exposure</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Emissions To Water</t>
-  </si>
-  <si>
-    <t>Waste</t>
-  </si>
-  <si>
-    <t>Hazardous and Radioactive Waste</t>
-  </si>
-  <si>
-    <t>Social</t>
-  </si>
-  <si>
-    <t>Social and employee matters</t>
-  </si>
-  <si>
-    <t>Human Rights Legal Proceedings</t>
-  </si>
-  <si>
-    <t>ILO Core Labour Standards</t>
-  </si>
-  <si>
-    <t>Environmental Policy</t>
-  </si>
-  <si>
-    <t>Corruption Legal Proceedings</t>
-  </si>
-  <si>
-    <t>Transparency Disclosure Policy</t>
-  </si>
-  <si>
-    <t>Human Rights Due Diligence Policy</t>
-  </si>
-  <si>
-    <t>Policy against Child Labour</t>
-  </si>
-  <si>
-    <t>Policy against Forced Labour</t>
-  </si>
-  <si>
-    <t>Policy against Discrimination in the Workplace</t>
-  </si>
-  <si>
-    <t>ISO 14001 Certificate</t>
-  </si>
-  <si>
-    <t>Policy against Bribery and Corruption</t>
-  </si>
-  <si>
-    <t>Fair Business Marketing Advertising Policy</t>
-  </si>
-  <si>
-    <t>Technologies Expertise Transfer Policy</t>
-  </si>
-  <si>
-    <t>Fair Competition Policy</t>
-  </si>
-  <si>
-    <t>Violation Of Tax Rules And Regulation</t>
-  </si>
-  <si>
-    <t>UN Global Compact Principles Compliance Policy</t>
-  </si>
-  <si>
-    <t>OECD Guidelines For Multinational Enterprises Grievance Handling</t>
-  </si>
-  <si>
-    <t>Average Gross Hourly Earnings Male Employees</t>
-  </si>
-  <si>
-    <t>Average gross hourly earnings of male employees</t>
-  </si>
-  <si>
     <t>Average Gross Hourly Earnings Female Employees</t>
   </si>
   <si>
+    <t>AVG_GROSS_HOURLY_EARNINGS_FEMALE_EMPLOYEES</t>
+  </si>
+  <si>
     <t>Average gross hourly earnings of female employees</t>
   </si>
   <si>
     <t>Unadjusted gender pay gap</t>
   </si>
   <si>
+    <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
+  </si>
+  <si>
+    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).</t>
+  </si>
+  <si>
+    <t>Female Board Members - Supervisory Board</t>
+  </si>
+  <si>
+    <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
+  </si>
+  <si>
+    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
+  </si>
+  <si>
     <t>Integer</t>
   </si>
   <si>
+    <t>Female Board Members - Board of Directors</t>
+  </si>
+  <si>
+    <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
+  </si>
+  <si>
+    <t>Number of females on the board of directors of the company</t>
+  </si>
+  <si>
+    <t>Male Board Members - Supervisory Board</t>
+  </si>
+  <si>
+    <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
+  </si>
+  <si>
+    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
+  </si>
+  <si>
+    <t>Male Board Members - Board of Directors</t>
+  </si>
+  <si>
+    <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
+  </si>
+  <si>
+    <t>Number of males on the board of directors of the company</t>
+  </si>
+  <si>
+    <t>Board gender diversity - Supervisory Board</t>
+  </si>
+  <si>
+    <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all supervisory board members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
+  </si>
+  <si>
     <t>Allowed Range: [0, 100]</t>
   </si>
   <si>
+    <t>Board gender diversity - Board of Directors</t>
+  </si>
+  <si>
+    <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all board of directors members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
+  </si>
+  <si>
     <t>Controversial Weapons Exposure</t>
   </si>
   <si>
-    <t>Emissions</t>
-  </si>
-  <si>
-    <t>Emissions of Inorganic Pollutants</t>
-  </si>
-  <si>
-    <t>Emissions of Air Pollutants</t>
-  </si>
-  <si>
-    <t>Emissions of Ozone Depletion Substances</t>
-  </si>
-  <si>
-    <t>Carbon Reduction Initiatives</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Fossil Fuels</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Crude Oil</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Natural Gas</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Lignite</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Coal</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Nuclear Energy</t>
-  </si>
-  <si>
-    <t>Non-Renewable Energy Consumption Other</t>
-  </si>
-  <si>
-    <t>Water Consumption</t>
-  </si>
-  <si>
-    <t>Cubic Meters</t>
-  </si>
-  <si>
-    <t>Water Reused</t>
-  </si>
-  <si>
-    <t>Relative Water Usage</t>
-  </si>
-  <si>
-    <t>Cubic Meters / €M Revenue</t>
-  </si>
-  <si>
-    <t>Water Management Policy</t>
-  </si>
-  <si>
-    <t>High Water Stress Area Exposure</t>
-  </si>
-  <si>
-    <t>Manufacture Of Agrochemical Pesticides Products</t>
-  </si>
-  <si>
-    <t>Land Degradation Desertification Soil Sealing Exposure</t>
-  </si>
-  <si>
-    <t>Sustainable Agriculture Policy</t>
-  </si>
-  <si>
-    <t>Sustainable Oceans And Seas Policy</t>
-  </si>
-  <si>
-    <t>Non-Recycled Waste</t>
-  </si>
-  <si>
-    <t>Threatened Species Exposure</t>
-  </si>
-  <si>
-    <t>Biodiversity Protection Policy</t>
-  </si>
-  <si>
-    <t>Deforestation Policy</t>
+    <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
+  </si>
+  <si>
+    <t>Is the company involved in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons? See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
+  </si>
+  <si>
+    <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
+  </si>
+  <si>
+    <t>Workplace Accident Prevention Policy</t>
+  </si>
+  <si>
+    <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a workplace accident prevention policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.) If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of a workplace accident prevention policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.</t>
+  </si>
+  <si>
+    <t>Rate Of Accidents</t>
+  </si>
+  <si>
+    <t>RATE_OF_ACCIDENTS</t>
+  </si>
+  <si>
+    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 2.</t>
+  </si>
+  <si>
+    <t>Workdays Lost</t>
+  </si>
+  <si>
+    <t>WORKDAYS_LOST</t>
+  </si>
+  <si>
+    <t>Number of workdays lost to injuries, accidents, fatalities or illness in total</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Supplier Code Of Conduct</t>
+  </si>
+  <si>
+    <t>SUPPLIER_CODE_OF_CONDUCT</t>
+  </si>
+  <si>
+    <t>Does the company have a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.) If yes, please share the document with us.</t>
+  </si>
+  <si>
+    <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.</t>
+  </si>
+  <si>
+    <t>Grievance Handling Mechanism</t>
+  </si>
+  <si>
+    <t>GRIEVANCE_HANDLING_MECHANISM</t>
+  </si>
+  <si>
+    <t>Does the company have a grievance/complaints handling mechanism related to employee matters? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Existence of a grievance/complaints handling mechanism related to employee matters. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
+  </si>
+  <si>
+    <t>Whistleblower Protection Policy</t>
+  </si>
+  <si>
+    <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a policy on the protection of whistleblowers? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.) If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of a policy on the protection of whistleblowers. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.</t>
+  </si>
+  <si>
+    <t>Reported Incidents Of Discrimination</t>
+  </si>
+  <si>
+    <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
+  </si>
+  <si>
+    <t>Number of reported discrimination-related incidents. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.1 .</t>
+  </si>
+  <si>
+    <t>Sanctioned Incidents Of Discrimination</t>
+  </si>
+  <si>
+    <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
+  </si>
+  <si>
+    <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.2 .</t>
+  </si>
+  <si>
+    <t>Excessive CEO pay ratio</t>
+  </si>
+  <si>
+    <t>EXCESSIVE_CEO_PAY_RATIO</t>
+  </si>
+  <si>
+    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual). See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 8.</t>
   </si>
   <si>
     <t>Green securities</t>
@@ -446,34 +1252,13 @@
     <t>Securities Not Certified As Green</t>
   </si>
   <si>
-    <t>Workplace Accident Prevention Policy</t>
-  </si>
-  <si>
-    <t>Rate Of Accidents</t>
-  </si>
-  <si>
-    <t>Workdays Lost</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>Supplier Code Of Conduct</t>
-  </si>
-  <si>
-    <t>Grievance Handling Mechanism</t>
-  </si>
-  <si>
-    <t>Whistleblower Protection Policy</t>
-  </si>
-  <si>
-    <t>Reported Incidents Of Discrimination</t>
-  </si>
-  <si>
-    <t>Sanctioned Incidents Of Discrimination</t>
-  </si>
-  <si>
-    <t>Excessive CEO pay ratio</t>
+    <t>SECURITIES_NOT_CERTIFIED_AS_GREEN</t>
+  </si>
+  <si>
+    <t>Does the company have securities in investments not certified as green under a future EU legal act setting up an EU Green Bond Standard?</t>
+  </si>
+  <si>
+    <t>Possession of securities in investments that are not certified as green under a future EU legal act setting up an EU Green Bond Standard.</t>
   </si>
   <si>
     <t>Human rights</t>
@@ -482,901 +1267,100 @@
     <t>Human Rights Policy</t>
   </si>
   <si>
+    <t>HUMAN_RIGHTS_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a human rights policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.) If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of a human rights policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.</t>
+  </si>
+  <si>
     <t>Human Rights Due Diligence</t>
   </si>
   <si>
+    <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
+  </si>
+  <si>
+    <t>Does the company have due diligence processes to identify, prevent, mitigate and address adverse human rights impacts? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
+  </si>
+  <si>
+    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
+  </si>
+  <si>
     <t>Trafficking In Human Beings Policy</t>
   </si>
   <si>
+    <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
+  </si>
+  <si>
+    <t>Does the company have a policy against trafficking in human beings? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.)  If yes, please share the policy with us.</t>
+  </si>
+  <si>
+    <t>Existence of a policy against trafficking in human beings. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.</t>
+  </si>
+  <si>
     <t>Reported Child Labour Incidents</t>
   </si>
   <si>
+    <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
+  </si>
+  <si>
+    <t>Does the company have reported incidents of child labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
+  </si>
+  <si>
+    <t>Reported incidents of child labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
+  </si>
+  <si>
     <t>Reported Forced Or Compulsory Labour Incidents</t>
   </si>
   <si>
+    <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
+  </si>
+  <si>
+    <t>Does the company have reported incidents of forced or compulsory labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
+  </si>
+  <si>
+    <t>Reported incidents of forced or compulsory labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
+  </si>
+  <si>
     <t>Number Of Reported Incidents Of Human Rights Violations</t>
   </si>
   <si>
+    <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of cases of severe human rights issues and incidents connected to the company. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 14. </t>
+  </si>
+  <si>
     <t>Anti-corruption and anti-bribery</t>
   </si>
   <si>
     <t>Cases of Insufficient Action against Bribery and Corruption</t>
   </si>
   <si>
+    <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 16. </t>
+  </si>
+  <si>
     <t>Reported Convictions Of Bribery and Corruption</t>
   </si>
   <si>
+    <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of reported convictions for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
+  </si>
+  <si>
     <t>Total Amount Of Reported Fines Of Bribery and Corruption</t>
   </si>
   <si>
-    <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
-  </si>
-  <si>
-    <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
-  </si>
-  <si>
-    <t>Data Date</t>
-  </si>
-  <si>
-    <t>Yes/No</t>
-  </si>
-  <si>
-    <t>Female Board Members - Supervisory Board</t>
-  </si>
-  <si>
-    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
-    <t>Female Board Members - Board of Directors</t>
-  </si>
-  <si>
-    <t>Number of females on the board of directors of the company</t>
-  </si>
-  <si>
-    <t>Male Board Members - Supervisory Board</t>
-  </si>
-  <si>
-    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
-    <t>Male Board Members - Board of Directors</t>
-  </si>
-  <si>
-    <t>Number of males on the board of directors of the company</t>
-  </si>
-  <si>
-    <t>Board gender diversity - Supervisory Board</t>
-  </si>
-  <si>
-    <t>Board gender diversity - Board of Directors</t>
-  </si>
-  <si>
-    <t>Scope 3 upstream GHG emissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope 3 downstream GHG emissions </t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 1</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 2</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 3</t>
-  </si>
-  <si>
-    <t>GHG intensity - scope 4</t>
-  </si>
-  <si>
-    <t>Financed scope 1 and scope 2 emissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonnes </t>
-  </si>
-  <si>
-    <t>Financed scope 3 emissions</t>
-  </si>
-  <si>
-    <t>Scope 4 GHG emissions</t>
-  </si>
-  <si>
-    <t>Scope 4, as defined by the GHG Protocol, covers emissions avoided when a product is used as a substitute for other goods or services, fulfilling the same functions but with a lower carbon intensity.</t>
-  </si>
-  <si>
-    <t>Number of workdays lost to injuries, accidents, fatalities or illness in total</t>
-  </si>
-  <si>
-    <t>The year for which the data is reported.</t>
-  </si>
-  <si>
-    <t>The date the fiscal year ends.</t>
-  </si>
-  <si>
-    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Scope 3 greenhouse gas emissions in tonnes, i.e. all indirect upstream and downstream emissions that are not included in scope 2 (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share).</t>
-  </si>
-  <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
-    <t>The sum of scope 1 and scope 2 emissions of financed companies.</t>
-  </si>
-  <si>
-    <t>The scope 3 emissions of financed companies.</t>
-  </si>
-  <si>
-    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
-    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
-    <t>Total value of non-renewable energy produced, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
-    <t>Total value of non-renewable energy consumed, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
-    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
-    <t>Sector applicable activities.</t>
-  </si>
-  <si>
-    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1).</t>
-  </si>
-  <si>
-    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
-    <t>Sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions. For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
-    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
-    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.</t>
-  </si>
-  <si>
-    <t>Emissions to water in tonnes (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See  Regulation (EU) 2022/1288, Annex I, top (12).</t>
-  </si>
-  <si>
-    <t>Tonnes of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactice waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).</t>
-  </si>
-  <si>
-    <t>Involvement in Human Rights related legal proceedings.</t>
-  </si>
-  <si>
-    <t>Abidance by the ILO Core Labour Standards.</t>
-  </si>
-  <si>
-    <t>Existence of an environmental policy.</t>
-  </si>
-  <si>
-    <t>Involvement in corruption-related legal proceedings.</t>
-  </si>
-  <si>
-    <t>The company is ISO 14001 certified.</t>
-  </si>
-  <si>
-    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.</t>
-  </si>
-  <si>
-    <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
-  </si>
-  <si>
-    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
-  </si>
-  <si>
-    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).</t>
-  </si>
-  <si>
-    <t>Percentage of female board members among all supervisory board members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
-    <t>Percentage of female board members among all board of directors members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
-    <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
-    <t>Tonnes of emissions by inorganic pollutants. Inorganic pollutants include those resulting from radiant energy, noise, heat, or light, as well as substances like arsenic, cadmium, lead, mercury, chromium, aluminum, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, iron, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27) and table 2, indicator nr. 1.</t>
-  </si>
-  <si>
-    <t>Tonnes of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and table 2, indicator nr. 2 and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.</t>
-  </si>
-  <si>
-    <t>Tonnes of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and table 2, indicator nr. 3 and the Montreal Protocol on Substances that Deplete the Ozone Layer.</t>
-  </si>
-  <si>
-    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.</t>
-  </si>
-  <si>
-    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, nuclear energy, lignite and coal) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Amount of water consumed by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1 .</t>
-  </si>
-  <si>
-    <t>Amount of water recycled and reused by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.2 .</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures for water management. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.</t>
-  </si>
-  <si>
-    <t>Involvement in activities, which cause land degradation, desertification or soil sealing. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
-    <t>Existence of sustainable land or agriculture practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.</t>
-  </si>
-  <si>
-    <t>Existence of sustainable oceans or seas practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.</t>
-  </si>
-  <si>
-    <t>Tonnes of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17) and table 2, indicator nr. 13.</t>
-  </si>
-  <si>
-    <t>Operations, which affect threatened species. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
-    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2 .</t>
-  </si>
-  <si>
-    <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
-    <t>Existence of a workplace accident prevention policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.</t>
-  </si>
-  <si>
-    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 2.</t>
-  </si>
-  <si>
-    <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.</t>
-  </si>
-  <si>
-    <t>Existence of a grievance/complaints handling mechanism related to employee matters. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Existence of a policy on the protection of whistleblowers. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.</t>
-  </si>
-  <si>
-    <t>Number of reported discrimination-related incidents. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.1 .</t>
-  </si>
-  <si>
-    <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.2 .</t>
-  </si>
-  <si>
-    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual). See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 8.</t>
-  </si>
-  <si>
-    <t>Existence of a human rights policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.</t>
-  </si>
-  <si>
-    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
-    <t>Existence of a policy against trafficking in human beings. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of cases of severe human rights issues and incidents connected to the company. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 14. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 16. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of reported convictions for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
+    <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
     <t xml:space="preserve">Amount of fines for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
-  </si>
-  <si>
-    <t>Existence of a transparency policy. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to abolish all forms of child labour.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to abolish all forms of forced labour.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise.</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
-  </si>
-  <si>
-    <t>Involvement in a violation of OECD Guidelines for Multinational Enterprises for Taxation: In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
-    <t>Does the company have policies and procedures for water management? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments? Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
-    <t>Does the company have sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions? For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
-    <t>Does the company have sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated? For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
-    <t>Does the company have sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status?</t>
-  </si>
-  <si>
-    <t>Does the company have an environmental policy? If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a transparency policy? If yes, please share the policy with us. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
-  </si>
-  <si>
-    <t>Does the company have policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have policies in place to abolish all forms of child labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have policies in place to abolish all forms of forced labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have policies in place to eliminate discrimination in the workplace? If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have policies and procedures in place related to fair competition and anti-competitive cartels? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have any policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have securities in investments not certified as green under a future EU legal act setting up an EU Green Bond Standard?</t>
-  </si>
-  <si>
-    <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy. See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
-    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
-    <t>Is the company involved in manufacture of pesticides and other agrochemical products? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
-    <t>Is the company involved in activities, which cause land degradation, desertification or soil sealing? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
-    <t>Does the company have sustainable land or agriculture practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have sustainable oceans or seas practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Does the company have operations, which affect threatened species? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
-    <t>Does the company have a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a policy to address deforestation? If yes, please share the policy with us. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
-    <t>Possession of securities in investments that are not certified as green under a future EU legal act setting up an EU Green Bond Standard.</t>
-  </si>
-  <si>
-    <t>Does the company have a workplace accident prevention policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.) If yes, please share the document with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a grievance/complaints handling mechanism related to employee matters? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Does the company have a policy on the protection of whistleblowers? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company have a human rights policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Reported incidents of child labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
-  </si>
-  <si>
-    <t>Reported incidents of forced or compulsory labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
-    <t>Does the company have due diligence processes to identify, prevent, mitigate and address adverse human rights impacts? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
-    <t>Does the company have reported incidents of child labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
-  </si>
-  <si>
-    <t>Does the company have reported incidents of forced or compulsory labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
-    <t>Does the company have a policy against trafficking in human beings? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.)  If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Does the company abide by the ILO Core Labour Standards?</t>
-  </si>
-  <si>
-    <t>Has the company been involved in Human Rights related legal proceedings?</t>
-  </si>
-  <si>
-    <t>Has the company been involved in corruption-related legal proceedings?</t>
-  </si>
-  <si>
-    <t>Is the company ISO 14001 certified (Environmental Management)? If yes, please share the certificate with us.</t>
-  </si>
-  <si>
-    <t>Please select any sector(s) applicable activities (NACE Codes A-H, L).</t>
-  </si>
-  <si>
-    <t>Is the company involved in a violation of OECD Guidelines for Multinational Enterprises for Taxation? In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
-    <t>Is the company involved in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons? See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy? See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
-    <t>Does the company derive any revenues from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels? (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
-    <t>Tonnes of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions).</t>
-  </si>
-  <si>
-    <t>Tonnes of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
-    <t>Tonnes of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions.</t>
-  </si>
-  <si>
-    <t>Tonnes of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
-  </si>
-  <si>
-    <t>Total revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover. Overall turnover is equivalent to a firm's total revenues over some period of time.</t>
-  </si>
-  <si>
-    <t>Tonnes / €M Enterprise Value</t>
-  </si>
-  <si>
-    <t>Tonnes of GHG emissions per million EUR enterprise value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4). </t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>Tonnes of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
-    <t>Amount in cubic meters of fresh water used per million EUR revenue. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1.</t>
-  </si>
-  <si>
-    <t>Alias Export</t>
-  </si>
-  <si>
-    <t>DATA_DATE</t>
-  </si>
-  <si>
-    <t>FISCAL_YEAR_DEVIATION</t>
-  </si>
-  <si>
-    <t>FISCAL_YEAR_END</t>
-  </si>
-  <si>
-    <t>REFERENCED_REPORTS</t>
-  </si>
-  <si>
-    <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>SCOPE_4_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>ENTERPRISE_VALUE_IN_EUR</t>
-  </si>
-  <si>
-    <t>TOTAL_REVENUE_IN_EUR</t>
-  </si>
-  <si>
-    <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>GHG_INTENSITY_SCOPE_4_IN_T_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
-  </si>
-  <si>
-    <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
-  </si>
-  <si>
-    <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
-  </si>
-  <si>
-    <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
-  </si>
-  <si>
-    <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
-  </si>
-  <si>
-    <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
-  </si>
-  <si>
-    <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
-  </si>
-  <si>
-    <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
-  </si>
-  <si>
-    <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
-  </si>
-  <si>
-    <t>PROTECTED_AREAS_EXPOSURE</t>
-  </si>
-  <si>
-    <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
-  </si>
-  <si>
-    <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
-  </si>
-  <si>
-    <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
-  </si>
-  <si>
-    <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
-  </si>
-  <si>
-    <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
-  </si>
-  <si>
-    <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
-  </si>
-  <si>
-    <t>THREATENED_SPECIES_EXPOSURE</t>
-  </si>
-  <si>
-    <t>BIODIVERSITY_PROTECTION_POLICY</t>
-  </si>
-  <si>
-    <t>DEFORESTATION_POLICY</t>
-  </si>
-  <si>
-    <t>EMISSIONS_TO_WATER_IN_T</t>
-  </si>
-  <si>
-    <t>WATER_CONS_IN_M3</t>
-  </si>
-  <si>
-    <t>WATER_REUSED_IN_M3</t>
-  </si>
-  <si>
-    <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
-  </si>
-  <si>
-    <t>WATER_MANAGEMENT_POLICY</t>
-  </si>
-  <si>
-    <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
-  </si>
-  <si>
-    <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
-  </si>
-  <si>
-    <t>NON_RECYCLED_WASTE_IN_T</t>
-  </si>
-  <si>
-    <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
-  </si>
-  <si>
-    <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
-  </si>
-  <si>
-    <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
-  </si>
-  <si>
-    <t>CARBON_REDUCTION_INITIATIVES</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
-  </si>
-  <si>
-    <t>ILO_CORE_LABOUR_STANDARDS</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL_POLICY</t>
-  </si>
-  <si>
-    <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
-  </si>
-  <si>
-    <t>TRANSPARENCY_DISCLOSURE_POLICY</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_CHILD_LABOUR</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_FORCED_LABOUR</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
-  </si>
-  <si>
-    <t>ISO_14001_CERTIFICATE</t>
-  </si>
-  <si>
-    <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
-  </si>
-  <si>
-    <t>TECHNOLOGIES_EXPERTISE_TRANSFER_POLICY</t>
-  </si>
-  <si>
-    <t>FAIR_COMPETITION_POLICY</t>
-  </si>
-  <si>
-    <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
-  </si>
-  <si>
-    <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
-  </si>
-  <si>
-    <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
-  </si>
-  <si>
-    <t>AVG_GROSS_HOURLY_EARNINGS_MALE_EMPLOYEES</t>
-  </si>
-  <si>
-    <t>AVG_GROSS_HOURLY_EARNINGS_FEMALE_EMPLOYEES</t>
-  </si>
-  <si>
-    <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
-  </si>
-  <si>
-    <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
-  </si>
-  <si>
-    <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
-  </si>
-  <si>
-    <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
-  </si>
-  <si>
-    <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
-  </si>
-  <si>
-    <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
-  </si>
-  <si>
-    <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
-  </si>
-  <si>
-    <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
-  </si>
-  <si>
-    <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
-  </si>
-  <si>
-    <t>RATE_OF_ACCIDENTS</t>
-  </si>
-  <si>
-    <t>WORKDAYS_LOST</t>
-  </si>
-  <si>
-    <t>SUPPLIER_CODE_OF_CONDUCT</t>
-  </si>
-  <si>
-    <t>GRIEVANCE_HANDLING_MECHANISM</t>
-  </si>
-  <si>
-    <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
-  </si>
-  <si>
-    <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
-  </si>
-  <si>
-    <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
-  </si>
-  <si>
-    <t>EXCESSIVE_CEO_PAY_RATIO</t>
-  </si>
-  <si>
-    <t>SECURITIES_NOT_CERTIFIED_AS_GREEN</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_POLICY</t>
-  </si>
-  <si>
-    <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
-  </si>
-  <si>
-    <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
-  </si>
-  <si>
-    <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
-  </si>
-  <si>
-    <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
-  </si>
-  <si>
-    <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
-  </si>
-  <si>
-    <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
-  </si>
-  <si>
-    <t>Greenhouse gas emissions</t>
-  </si>
-  <si>
-    <t>Scope 1 greenhouse gas emissions in tonnes, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the location-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the market-based method (equity share approach preferably used).</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1466,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{100D6088-3004-4D92-AED4-3E73A93BE4D1}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1793,18 +1777,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBCA27A-793A-4293-9394-36A2BE726731}">
-  <dimension ref="A1:N114"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O114"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="255.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1818,567 +1810,544 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>317</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>319</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>321</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" s="6" customFormat="1">
+    <row r="6" spans="1:15" s="6" customFormat="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>431</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>322</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>432</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>433</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="6" customFormat="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>323</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="6" customFormat="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>431</v>
+        <v>36</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>324</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>434</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>433</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="6" customFormat="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>431</v>
+        <v>36</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>325</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>435</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>433</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="6" customFormat="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>326</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="6" customFormat="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>327</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="6" customFormat="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>328</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>177</v>
+        <v>61</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="6" customFormat="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>431</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>329</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>178</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>433</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="6" customFormat="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>330</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="6" customFormat="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>331</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="6" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="6" customFormat="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>332</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="6" customFormat="1">
@@ -2386,30 +2355,30 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>333</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="6" customFormat="1">
@@ -2417,30 +2386,30 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="6" customFormat="1">
@@ -2448,32 +2417,32 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="6" customFormat="1">
@@ -2481,30 +2450,30 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
-        <v>313</v>
+        <v>85</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>314</v>
+        <v>86</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="6" customFormat="1">
@@ -2512,30 +2481,30 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>337</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>310</v>
+        <v>89</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>314</v>
+        <v>86</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="6" customFormat="1">
@@ -2543,32 +2512,32 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>312</v>
+        <v>92</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>311</v>
+        <v>93</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="6" customFormat="1">
@@ -2576,32 +2545,32 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>339</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>315</v>
+        <v>96</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="6" customFormat="1">
@@ -2609,30 +2578,30 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="F24" t="s">
-        <v>306</v>
+        <v>100</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="6" customFormat="1">
@@ -2640,30 +2609,30 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>341</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s">
-        <v>307</v>
+        <v>103</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="6" customFormat="1">
@@ -2671,30 +2640,30 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>342</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
-        <v>308</v>
+        <v>106</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="6" customFormat="1">
@@ -2702,30 +2671,30 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>343</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>309</v>
+        <v>109</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="6" customFormat="1">
@@ -2733,32 +2702,32 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>344</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>305</v>
+        <v>112</v>
       </c>
       <c r="G28" t="s">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="6" customFormat="1">
@@ -2766,30 +2735,30 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>345</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="6" customFormat="1">
@@ -2797,30 +2766,30 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>346</v>
+        <v>120</v>
       </c>
       <c r="F30" t="s">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="6" customFormat="1">
@@ -2828,32 +2797,32 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>347</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="6" customFormat="1">
@@ -2861,32 +2830,32 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>348</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="6" customFormat="1">
@@ -2894,34 +2863,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>349</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="6" customFormat="1">
@@ -2929,34 +2898,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>350</v>
+        <v>134</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="6" customFormat="1">
@@ -2964,34 +2933,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>351</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="6" customFormat="1">
@@ -2999,34 +2968,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>352</v>
+        <v>141</v>
       </c>
       <c r="F36" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="6" customFormat="1">
@@ -3034,34 +3003,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>353</v>
+        <v>144</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>301</v>
+        <v>145</v>
       </c>
       <c r="G37" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="6" customFormat="1">
@@ -3069,32 +3038,32 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>354</v>
+        <v>149</v>
       </c>
       <c r="F38" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="6" customFormat="1">
@@ -3102,34 +3071,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>355</v>
+        <v>152</v>
       </c>
       <c r="F39" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="6" customFormat="1">
@@ -3137,34 +3106,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>356</v>
+        <v>155</v>
       </c>
       <c r="F40" t="s">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="6" customFormat="1">
@@ -3172,34 +3141,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>357</v>
+        <v>158</v>
       </c>
       <c r="F41" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="6" customFormat="1">
@@ -3207,34 +3176,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>358</v>
+        <v>161</v>
       </c>
       <c r="F42" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="6" customFormat="1">
@@ -3242,34 +3211,34 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>359</v>
+        <v>164</v>
       </c>
       <c r="F43" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="6" customFormat="1">
@@ -3277,34 +3246,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>360</v>
+        <v>167</v>
       </c>
       <c r="F44" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="6" customFormat="1">
@@ -3312,34 +3281,34 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>361</v>
+        <v>170</v>
       </c>
       <c r="F45" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="6" customFormat="1">
@@ -3347,34 +3316,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>362</v>
+        <v>174</v>
       </c>
       <c r="F46" t="s">
-        <v>258</v>
+        <v>175</v>
       </c>
       <c r="G46" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="6" customFormat="1">
@@ -3382,34 +3351,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>62</v>
+        <v>177</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>363</v>
+        <v>178</v>
       </c>
       <c r="F47" t="s">
-        <v>259</v>
+        <v>179</v>
       </c>
       <c r="G47" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="6" customFormat="1">
@@ -3417,34 +3386,34 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>364</v>
+        <v>182</v>
       </c>
       <c r="F48" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="6" customFormat="1">
@@ -3452,34 +3421,34 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>365</v>
+        <v>186</v>
       </c>
       <c r="F49" t="s">
-        <v>261</v>
+        <v>187</v>
       </c>
       <c r="G49" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="6" customFormat="1">
@@ -3487,34 +3456,34 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>366</v>
+        <v>190</v>
       </c>
       <c r="F50" t="s">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="G50" t="s">
-        <v>277</v>
+        <v>192</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="6" customFormat="1">
@@ -3522,34 +3491,34 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>367</v>
+        <v>194</v>
       </c>
       <c r="F51" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="G51" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="6" customFormat="1">
@@ -3557,34 +3526,34 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>117</v>
+        <v>197</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="F52" t="s">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="G52" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="6" customFormat="1">
@@ -3592,34 +3561,34 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>369</v>
+        <v>202</v>
       </c>
       <c r="F53" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="G53" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
@@ -3627,34 +3596,34 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>370</v>
+        <v>206</v>
       </c>
       <c r="F54" t="s">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="G54" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
@@ -3662,34 +3631,34 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>371</v>
+        <v>210</v>
       </c>
       <c r="F55" t="s">
-        <v>283</v>
+        <v>211</v>
       </c>
       <c r="G55" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
@@ -3697,34 +3666,34 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>372</v>
+        <v>214</v>
       </c>
       <c r="F56" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="G56" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
@@ -3732,34 +3701,34 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>373</v>
+        <v>219</v>
       </c>
       <c r="F57" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
@@ -3767,34 +3736,34 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>108</v>
+        <v>221</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>374</v>
+        <v>222</v>
       </c>
       <c r="F58" t="s">
         <v>223</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>109</v>
+        <v>224</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
@@ -3802,34 +3771,34 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>375</v>
+        <v>226</v>
       </c>
       <c r="F59" t="s">
+        <v>227</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J59" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="K59" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
@@ -3837,34 +3806,34 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>376</v>
+        <v>229</v>
       </c>
       <c r="F60" t="s">
-        <v>316</v>
+        <v>230</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>112</v>
+        <v>231</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1">
@@ -3872,34 +3841,34 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>377</v>
+        <v>233</v>
       </c>
       <c r="F61" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="G61" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1">
@@ -3907,34 +3876,34 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F62" t="s">
+        <v>238</v>
+      </c>
+      <c r="G62" t="s">
+        <v>239</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="F62" t="s">
-        <v>304</v>
-      </c>
-      <c r="G62" t="s">
-        <v>276</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="I62" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1">
@@ -3942,32 +3911,32 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>67</v>
+        <v>240</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>68</v>
+        <v>241</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>379</v>
+        <v>242</v>
       </c>
       <c r="F63" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1">
@@ -3975,32 +3944,32 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>67</v>
+        <v>240</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>119</v>
+        <v>244</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>380</v>
+        <v>245</v>
       </c>
       <c r="F64" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1">
@@ -4008,32 +3977,32 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>381</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1">
@@ -4041,32 +4010,32 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>98</v>
+        <v>251</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>382</v>
+        <v>252</v>
       </c>
       <c r="F66" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1">
@@ -4074,32 +4043,32 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>99</v>
+        <v>254</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>383</v>
+        <v>255</v>
       </c>
       <c r="F67" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1">
@@ -4107,34 +4076,34 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>100</v>
+        <v>257</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>384</v>
+        <v>258</v>
       </c>
       <c r="F68" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="G68" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1">
@@ -4142,34 +4111,34 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="G69" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1">
@@ -4177,34 +4146,34 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>386</v>
+        <v>268</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="G70" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1">
@@ -4212,34 +4181,34 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G71" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1">
@@ -4247,34 +4216,34 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>74</v>
+        <v>275</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>388</v>
+        <v>276</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="G72" t="s">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1">
@@ -4282,34 +4251,34 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>389</v>
+        <v>280</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="6" customFormat="1">
@@ -4317,34 +4286,34 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>390</v>
+        <v>284</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="6" customFormat="1">
@@ -4352,34 +4321,34 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>391</v>
+        <v>288</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="6" customFormat="1">
@@ -4387,34 +4356,34 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>392</v>
+        <v>292</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="6" customFormat="1">
@@ -4422,34 +4391,34 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>393</v>
+        <v>296</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="6" customFormat="1">
@@ -4457,34 +4426,34 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>394</v>
+        <v>300</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G78" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="6" customFormat="1">
@@ -4492,34 +4461,34 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>395</v>
+        <v>304</v>
       </c>
       <c r="F79" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="G79" t="s">
-        <v>205</v>
+        <v>306</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="6" customFormat="1">
@@ -4527,34 +4496,34 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="6" customFormat="1">
@@ -4562,34 +4531,34 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>397</v>
+        <v>312</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="6" customFormat="1">
@@ -4597,34 +4566,34 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>255</v>
+        <v>318</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="6" customFormat="1">
@@ -4632,34 +4601,34 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>399</v>
+        <v>320</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>256</v>
+        <v>322</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="6" customFormat="1">
@@ -4667,34 +4636,34 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>86</v>
+        <v>323</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="F84" t="s">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="G84" t="s">
-        <v>206</v>
+        <v>326</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="6" customFormat="1">
@@ -4702,34 +4671,34 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>87</v>
+        <v>327</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>401</v>
+        <v>328</v>
       </c>
       <c r="F85" t="s">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="G85" t="s">
-        <v>207</v>
+        <v>330</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="6" customFormat="1">
@@ -4737,34 +4706,34 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>88</v>
+        <v>331</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>89</v>
+        <v>333</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="6" customFormat="1">
@@ -4772,34 +4741,34 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>90</v>
+        <v>335</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>403</v>
+        <v>336</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>91</v>
+        <v>337</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="6" customFormat="1">
@@ -4807,32 +4776,32 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>92</v>
+        <v>338</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>404</v>
+        <v>339</v>
       </c>
       <c r="F88" t="s">
-        <v>208</v>
+        <v>340</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="6" customFormat="1">
@@ -4840,30 +4809,30 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>150</v>
+        <v>341</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>405</v>
+        <v>342</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>151</v>
+        <v>343</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="6" customFormat="1">
@@ -4871,30 +4840,30 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>152</v>
+        <v>345</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>406</v>
+        <v>346</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>153</v>
+        <v>347</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="6" customFormat="1">
@@ -4902,30 +4871,30 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>154</v>
+        <v>348</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>155</v>
+        <v>350</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="6" customFormat="1">
@@ -4933,30 +4902,30 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>156</v>
+        <v>351</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>408</v>
+        <v>352</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>157</v>
+        <v>353</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="6" customFormat="1">
@@ -4964,32 +4933,32 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>158</v>
+        <v>354</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>409</v>
+        <v>355</v>
       </c>
       <c r="F93" t="s">
-        <v>209</v>
+        <v>356</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>94</v>
+        <v>357</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="6" customFormat="1">
@@ -4997,32 +4966,32 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>159</v>
+        <v>358</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>410</v>
+        <v>359</v>
       </c>
       <c r="F94" t="s">
-        <v>210</v>
+        <v>360</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>94</v>
+        <v>357</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="6" customFormat="1">
@@ -5030,34 +4999,34 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>95</v>
+        <v>361</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="F95" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="G95" t="s">
-        <v>211</v>
+        <v>364</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="6" customFormat="1">
@@ -5065,34 +5034,34 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>125</v>
+        <v>365</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="F96" t="s">
-        <v>286</v>
+        <v>367</v>
       </c>
       <c r="G96" t="s">
-        <v>233</v>
+        <v>368</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="6" customFormat="1">
@@ -5100,30 +5069,30 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>126</v>
+        <v>369</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>413</v>
+        <v>370</v>
       </c>
       <c r="F97" t="s">
-        <v>234</v>
+        <v>371</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="6" customFormat="1">
@@ -5131,32 +5100,32 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>127</v>
+        <v>372</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>171</v>
+        <v>374</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>128</v>
+        <v>375</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="6" customFormat="1">
@@ -5164,34 +5133,34 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>129</v>
+        <v>376</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="F99" t="s">
-        <v>287</v>
+        <v>378</v>
       </c>
       <c r="G99" t="s">
-        <v>235</v>
+        <v>379</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="6" customFormat="1">
@@ -5199,34 +5168,34 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>416</v>
+        <v>381</v>
       </c>
       <c r="F100" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="G100" t="s">
-        <v>236</v>
+        <v>383</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="6" customFormat="1">
@@ -5234,34 +5203,34 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>131</v>
+        <v>384</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F101" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G101" t="s">
-        <v>237</v>
+        <v>387</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="6" customFormat="1">
@@ -5269,32 +5238,32 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>132</v>
+        <v>388</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="F102" t="s">
-        <v>238</v>
+        <v>390</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="6" customFormat="1">
@@ -5302,32 +5271,32 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>133</v>
+        <v>391</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="F103" t="s">
-        <v>239</v>
+        <v>393</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:11" s="6" customFormat="1">
@@ -5335,30 +5304,30 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="F104" t="s">
-        <v>240</v>
+        <v>396</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="6" customFormat="1">
@@ -5366,34 +5335,34 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>123</v>
+        <v>397</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>124</v>
+        <v>398</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>275</v>
+        <v>400</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>285</v>
+        <v>401</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:11" s="6" customFormat="1">
@@ -5401,34 +5370,34 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>136</v>
+        <v>403</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="F106" t="s">
-        <v>290</v>
+        <v>405</v>
       </c>
       <c r="G106" t="s">
-        <v>241</v>
+        <v>406</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:11" s="6" customFormat="1">
@@ -5436,34 +5405,34 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="F107" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
       <c r="G107" t="s">
-        <v>242</v>
+        <v>410</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:11" s="6" customFormat="1">
@@ -5471,34 +5440,34 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>138</v>
+        <v>411</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="F108" t="s">
-        <v>296</v>
+        <v>413</v>
       </c>
       <c r="G108" t="s">
-        <v>243</v>
+        <v>414</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="6" customFormat="1">
@@ -5506,34 +5475,34 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>139</v>
+        <v>415</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="F109" t="s">
-        <v>294</v>
+        <v>417</v>
       </c>
       <c r="G109" t="s">
-        <v>291</v>
+        <v>418</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="6" customFormat="1">
@@ -5541,34 +5510,34 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F110" t="s">
-        <v>295</v>
+        <v>421</v>
       </c>
       <c r="G110" t="s">
-        <v>292</v>
+        <v>422</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="6" customFormat="1">
@@ -5576,32 +5545,32 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>141</v>
+        <v>423</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F111" t="s">
-        <v>244</v>
+        <v>425</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:11" s="6" customFormat="1">
@@ -5609,34 +5578,34 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>142</v>
+        <v>426</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>143</v>
+        <v>427</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>428</v>
       </c>
       <c r="F112" t="s">
-        <v>245</v>
+        <v>429</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:11" s="6" customFormat="1">
@@ -5644,34 +5613,34 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>142</v>
+        <v>426</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>144</v>
+        <v>430</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F113" t="s">
-        <v>246</v>
+        <v>432</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>93</v>
+        <v>344</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:11" s="6" customFormat="1">
@@ -5679,39 +5648,39 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>142</v>
+        <v>426</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>145</v>
+        <v>433</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F114" t="s">
-        <v>247</v>
+        <v>435</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N114" xr:uid="{6EBCA27A-793A-4293-9394-36A2BE726731}"/>
+  <autoFilter ref="A1:N114" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212D04C2-B71C-4EF8-96DC-EA790CF686A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D498692-B93A-4EA2-81B8-C4624553AE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="480" windowWidth="19380" windowHeight="20490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="429">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -172,9 +172,6 @@
     <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 1 greenhouse gas emissions in tonnes, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Number</t>
   </si>
   <si>
@@ -193,108 +190,72 @@
     <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the location-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the market-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 3 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 3 greenhouse gas emissions in tonnes, i.e. all indirect upstream and downstream emissions that are not included in scope 2 (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 3 upstream GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scope 3 downstream GHG emissions </t>
   </si>
   <si>
     <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 4 GHG emissions</t>
   </si>
   <si>
@@ -310,9 +271,6 @@
     <t>ENTERPRISE_VALUE_IN_EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4). </t>
-  </si>
-  <si>
     <t>EUR</t>
   </si>
   <si>
@@ -322,18 +280,12 @@
     <t>TOTAL_REVENUE_IN_EUR</t>
   </si>
   <si>
-    <t>Total revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover. Overall turnover is equivalent to a firm's total revenues over some period of time.</t>
-  </si>
-  <si>
     <t>Carbon footprint</t>
   </si>
   <si>
     <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
   </si>
   <si>
-    <t>Tonnes of GHG emissions per million EUR enterprise value.</t>
-  </si>
-  <si>
     <t>Tonnes / €M Enterprise Value</t>
   </si>
   <si>
@@ -343,9 +295,6 @@
     <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
     <t>Tonnes / €M Revenue</t>
   </si>
   <si>
@@ -355,27 +304,18 @@
     <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions).</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 2</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 3</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions.</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 4</t>
   </si>
   <si>
@@ -391,9 +331,6 @@
     <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company derive any revenues from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels? (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
     <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
   </si>
   <si>
@@ -406,9 +343,6 @@
     <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>The sum of scope 1 and scope 2 emissions of financed companies.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tonnes </t>
   </si>
   <si>
@@ -418,9 +352,6 @@
     <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>The scope 3 emissions of financed companies.</t>
-  </si>
-  <si>
     <t>Energy performance</t>
   </si>
   <si>
@@ -430,9 +361,6 @@
     <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
     <t>GWh</t>
   </si>
   <si>
@@ -442,27 +370,18 @@
     <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Production</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of non-renewable energy produced, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
     <t>Relative Non-Renewable Energy Production</t>
   </si>
   <si>
     <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
   </si>
   <si>
-    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
     <t>Percent</t>
   </si>
   <si>
@@ -472,27 +391,18 @@
     <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of non-renewable energy consumed, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
     <t>Relative Non-Renewable Energy Consumption</t>
   </si>
   <si>
     <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
   </si>
   <si>
-    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
     <t>Applicable High Impact Climate Sectors</t>
   </si>
   <si>
     <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
   </si>
   <si>
-    <t>Please select any sector(s) applicable activities (NACE Codes A-H, L).</t>
-  </si>
-  <si>
     <t>Sector applicable activities.</t>
   </si>
   <si>
@@ -505,72 +415,48 @@
     <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1).</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Fossil Fuels</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, nuclear energy, lignite and coal) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Crude Oil</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Natural Gas</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Lignite</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Coal</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Nuclear Energy</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Other</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Biodiversity</t>
   </si>
   <si>
@@ -580,9 +466,6 @@
     <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments? Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
     <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
   </si>
   <si>
@@ -592,9 +475,6 @@
     <t>PROTECTED_AREAS_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions? For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
     <t>Sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions. For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
   </si>
   <si>
@@ -604,9 +484,6 @@
     <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated? For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
     <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
   </si>
   <si>
@@ -616,9 +493,6 @@
     <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status?</t>
-  </si>
-  <si>
     <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.</t>
   </si>
   <si>
@@ -628,9 +502,6 @@
     <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
   </si>
   <si>
-    <t>Is the company involved in manufacture of pesticides and other agrochemical products? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
     <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
   </si>
   <si>
@@ -640,9 +511,6 @@
     <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
   </si>
   <si>
-    <t>Is the company involved in activities, which cause land degradation, desertification or soil sealing? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Involvement in activities, which cause land degradation, desertification or soil sealing. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
   </si>
   <si>
@@ -652,9 +520,6 @@
     <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have sustainable land or agriculture practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of sustainable land or agriculture practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.</t>
   </si>
   <si>
@@ -664,9 +529,6 @@
     <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have sustainable oceans or seas practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of sustainable oceans or seas practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.</t>
   </si>
   <si>
@@ -676,9 +538,6 @@
     <t>THREATENED_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have operations, which affect threatened species? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
     <t>Operations, which affect threatened species. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
   </si>
   <si>
@@ -688,9 +547,6 @@
     <t>BIODIVERSITY_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2 .</t>
   </si>
   <si>
@@ -700,9 +556,6 @@
     <t>DEFORESTATION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy to address deforestation? If yes, please share the policy with us. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
     <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
   </si>
   <si>
@@ -715,18 +568,12 @@
     <t>EMISSIONS_TO_WATER_IN_T</t>
   </si>
   <si>
-    <t>Emissions to water in tonnes (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See  Regulation (EU) 2022/1288, Annex I, top (12).</t>
-  </si>
-  <si>
     <t>Water Consumption</t>
   </si>
   <si>
     <t>WATER_CONS_IN_M3</t>
   </si>
   <si>
-    <t>Amount of water consumed by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1 .</t>
-  </si>
-  <si>
     <t>Cubic Meters</t>
   </si>
   <si>
@@ -736,18 +583,12 @@
     <t>WATER_REUSED_IN_M3</t>
   </si>
   <si>
-    <t>Amount of water recycled and reused by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.2 .</t>
-  </si>
-  <si>
     <t>Relative Water Usage</t>
   </si>
   <si>
     <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Amount in cubic meters of fresh water used per million EUR revenue. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1.</t>
-  </si>
-  <si>
     <t>Cubic Meters / €M Revenue</t>
   </si>
   <si>
@@ -757,9 +598,6 @@
     <t>WATER_MANAGEMENT_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures for water management? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures for water management. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.</t>
   </si>
   <si>
@@ -769,9 +607,6 @@
     <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy? See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy. See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
   </si>
   <si>
@@ -784,18 +619,12 @@
     <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactice waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).</t>
-  </si>
-  <si>
     <t>Non-Recycled Waste</t>
   </si>
   <si>
     <t>NON_RECYCLED_WASTE_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17) and table 2, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Emissions</t>
   </si>
   <si>
@@ -805,36 +634,24 @@
     <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of emissions by inorganic pollutants. Inorganic pollutants include those resulting from radiant energy, noise, heat, or light, as well as substances like arsenic, cadmium, lead, mercury, chromium, aluminum, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, iron, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27) and table 2, indicator nr. 1.</t>
-  </si>
-  <si>
     <t>Emissions of Air Pollutants</t>
   </si>
   <si>
     <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and table 2, indicator nr. 2 and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.</t>
-  </si>
-  <si>
     <t>Emissions of Ozone Depletion Substances</t>
   </si>
   <si>
     <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and table 2, indicator nr. 3 and the Montreal Protocol on Substances that Deplete the Ozone Layer.</t>
-  </si>
-  <si>
     <t>Carbon Reduction Initiatives</t>
   </si>
   <si>
     <t>CARBON_REDUCTION_INITIATIVES</t>
   </si>
   <si>
-    <t>Does the company have any policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.</t>
   </si>
   <si>
@@ -850,9 +667,6 @@
     <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Has the company been involved in Human Rights related legal proceedings?</t>
-  </si>
-  <si>
     <t>Involvement in Human Rights related legal proceedings.</t>
   </si>
   <si>
@@ -862,9 +676,6 @@
     <t>ILO_CORE_LABOUR_STANDARDS</t>
   </si>
   <si>
-    <t>Does the company abide by the ILO Core Labour Standards?</t>
-  </si>
-  <si>
     <t>Abidance by the ILO Core Labour Standards.</t>
   </si>
   <si>
@@ -874,9 +685,6 @@
     <t>ENVIRONMENTAL_POLICY</t>
   </si>
   <si>
-    <t>Does the company have an environmental policy? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of an environmental policy.</t>
   </si>
   <si>
@@ -886,9 +694,6 @@
     <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Has the company been involved in corruption-related legal proceedings?</t>
-  </si>
-  <si>
     <t>Involvement in corruption-related legal proceedings.</t>
   </si>
   <si>
@@ -898,9 +703,6 @@
     <t>TRANSPARENCY_DISCLOSURE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a transparency policy? If yes, please share the policy with us. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
-  </si>
-  <si>
     <t>Existence of a transparency policy. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
   </si>
   <si>
@@ -910,9 +712,6 @@
     <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.</t>
   </si>
   <si>
@@ -922,9 +721,6 @@
     <t>POLICY_AGAINST_CHILD_LABOUR</t>
   </si>
   <si>
-    <t>Does the company have policies in place to abolish all forms of child labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to abolish all forms of child labour.</t>
   </si>
   <si>
@@ -934,9 +730,6 @@
     <t>POLICY_AGAINST_FORCED_LABOUR</t>
   </si>
   <si>
-    <t>Does the company have policies in place to abolish all forms of forced labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to abolish all forms of forced labour.</t>
   </si>
   <si>
@@ -946,9 +739,6 @@
     <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
   </si>
   <si>
-    <t>Does the company have policies in place to eliminate discrimination in the workplace? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
   </si>
   <si>
@@ -958,9 +748,6 @@
     <t>ISO_14001_CERTIFICATE</t>
   </si>
   <si>
-    <t>Is the company ISO 14001 certified (Environmental Management)? If yes, please share the certificate with us.</t>
-  </si>
-  <si>
     <t>The company is ISO 14001 certified.</t>
   </si>
   <si>
@@ -970,9 +757,6 @@
     <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t>Does the company have a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.</t>
   </si>
   <si>
@@ -982,9 +766,6 @@
     <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
   </si>
   <si>
@@ -994,9 +775,6 @@
     <t>TECHNOLOGIES_EXPERTISE_TRANSFER_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise.</t>
   </si>
   <si>
@@ -1006,9 +784,6 @@
     <t>FAIR_COMPETITION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place related to fair competition and anti-competitive cartels? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
   </si>
   <si>
@@ -1018,9 +793,6 @@
     <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
   </si>
   <si>
-    <t>Is the company involved in a violation of OECD Guidelines for Multinational Enterprises for Taxation? In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
     <t>Involvement in a violation of OECD Guidelines for Multinational Enterprises for Taxation: In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
   </si>
   <si>
@@ -1030,9 +802,6 @@
     <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
   </si>
   <si>
@@ -1042,9 +811,6 @@
     <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
   </si>
   <si>
-    <t>Does the company have grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
   </si>
   <si>
@@ -1054,9 +820,6 @@
     <t>AVG_GROSS_HOURLY_EARNINGS_MALE_EMPLOYEES</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of male employees</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -1066,27 +829,18 @@
     <t>AVG_GROSS_HOURLY_EARNINGS_FEMALE_EMPLOYEES</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of female employees</t>
-  </si>
-  <si>
     <t>Unadjusted gender pay gap</t>
   </si>
   <si>
     <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
   </si>
   <si>
-    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).</t>
-  </si>
-  <si>
     <t>Female Board Members - Supervisory Board</t>
   </si>
   <si>
     <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
   </si>
   <si>
-    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
     <t>Integer</t>
   </si>
   <si>
@@ -1096,36 +850,24 @@
     <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
   </si>
   <si>
-    <t>Number of females on the board of directors of the company</t>
-  </si>
-  <si>
     <t>Male Board Members - Supervisory Board</t>
   </si>
   <si>
     <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
   </si>
   <si>
-    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
     <t>Male Board Members - Board of Directors</t>
   </si>
   <si>
     <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
   </si>
   <si>
-    <t>Number of males on the board of directors of the company</t>
-  </si>
-  <si>
     <t>Board gender diversity - Supervisory Board</t>
   </si>
   <si>
     <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
   </si>
   <si>
-    <t>Percentage of female board members among all supervisory board members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Allowed Range: [0, 100]</t>
   </si>
   <si>
@@ -1135,18 +877,12 @@
     <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
   </si>
   <si>
-    <t>Percentage of female board members among all board of directors members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Controversial Weapons Exposure</t>
   </si>
   <si>
     <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
   </si>
   <si>
-    <t>Is the company involved in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons? See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
     <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
   </si>
   <si>
@@ -1156,9 +892,6 @@
     <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a workplace accident prevention policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a workplace accident prevention policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.</t>
   </si>
   <si>
@@ -1168,18 +901,12 @@
     <t>RATE_OF_ACCIDENTS</t>
   </si>
   <si>
-    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 2.</t>
-  </si>
-  <si>
     <t>Workdays Lost</t>
   </si>
   <si>
     <t>WORKDAYS_LOST</t>
   </si>
   <si>
-    <t>Number of workdays lost to injuries, accidents, fatalities or illness in total</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
@@ -1189,9 +916,6 @@
     <t>SUPPLIER_CODE_OF_CONDUCT</t>
   </si>
   <si>
-    <t>Does the company have a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.) If yes, please share the document with us.</t>
-  </si>
-  <si>
     <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.</t>
   </si>
   <si>
@@ -1201,9 +925,6 @@
     <t>GRIEVANCE_HANDLING_MECHANISM</t>
   </si>
   <si>
-    <t>Does the company have a grievance/complaints handling mechanism related to employee matters? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Existence of a grievance/complaints handling mechanism related to employee matters. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
   </si>
   <si>
@@ -1213,9 +934,6 @@
     <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy on the protection of whistleblowers? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy on the protection of whistleblowers. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.</t>
   </si>
   <si>
@@ -1225,27 +943,18 @@
     <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
   </si>
   <si>
-    <t>Number of reported discrimination-related incidents. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.1 .</t>
-  </si>
-  <si>
     <t>Sanctioned Incidents Of Discrimination</t>
   </si>
   <si>
     <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
   </si>
   <si>
-    <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.2 .</t>
-  </si>
-  <si>
     <t>Excessive CEO pay ratio</t>
   </si>
   <si>
     <t>EXCESSIVE_CEO_PAY_RATIO</t>
   </si>
   <si>
-    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual). See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Green securities</t>
   </si>
   <si>
@@ -1255,9 +964,6 @@
     <t>SECURITIES_NOT_CERTIFIED_AS_GREEN</t>
   </si>
   <si>
-    <t>Does the company have securities in investments not certified as green under a future EU legal act setting up an EU Green Bond Standard?</t>
-  </si>
-  <si>
     <t>Possession of securities in investments that are not certified as green under a future EU legal act setting up an EU Green Bond Standard.</t>
   </si>
   <si>
@@ -1270,9 +976,6 @@
     <t>HUMAN_RIGHTS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a human rights policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a human rights policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.</t>
   </si>
   <si>
@@ -1282,9 +985,6 @@
     <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
   </si>
   <si>
-    <t>Does the company have due diligence processes to identify, prevent, mitigate and address adverse human rights impacts? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
   </si>
   <si>
@@ -1294,9 +994,6 @@
     <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy against trafficking in human beings? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.)  If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy against trafficking in human beings. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.</t>
   </si>
   <si>
@@ -1306,9 +1003,6 @@
     <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Does the company have reported incidents of child labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
-  </si>
-  <si>
     <t>Reported incidents of child labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
   </si>
   <si>
@@ -1318,9 +1012,6 @@
     <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Does the company have reported incidents of forced or compulsory labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Reported incidents of forced or compulsory labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
   </si>
   <si>
@@ -1330,9 +1021,6 @@
     <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of cases of severe human rights issues and incidents connected to the company. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 14. </t>
-  </si>
-  <si>
     <t>Anti-corruption and anti-bribery</t>
   </si>
   <si>
@@ -1342,32 +1030,689 @@
     <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 16. </t>
-  </si>
-  <si>
     <t>Reported Convictions Of Bribery and Corruption</t>
   </si>
   <si>
     <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of reported convictions for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
-  </si>
-  <si>
     <t>Total Amount Of Reported Fines Of Bribery and Corruption</t>
   </si>
   <si>
     <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount of fines for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
+    <t>Scope 1 greenhouse gas emissions, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used). See also Regulation (EU) 2016/1011 Annex III (1)(e)(i).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions computed using the location-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions computed using the market-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 3 greenhouse gas emissions in tons, i.e., all indirect upstream and downstream emissions that are neither covered by scope 1 ghg emissions nor by scope 2 ghg emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii) and Regulation (EU) 2022/1288, Annex I, top (4) and formula (2)+(3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4) and formula (1)+(2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2</t>
+  </si>
+  <si>
+    <t>Total net or gross revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services. Overall turnover is equivalent to a firm's total revenues over some period of time. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of GHG emissions per million EUR enterprise value. See also (EU) 2022/1288 Annex I formula (2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 2</t>
+  </si>
+  <si>
+    <t>Tons of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions). See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 4</t>
+  </si>
+  <si>
+    <t>The sum of scope 1 and scope 2 emissions of financed companies.
+Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
+  </si>
+  <si>
+    <t>The scope 3 emissions of financed companies.
+Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy produced, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy consumed, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Sector applicable activities. See also Regulation (EU) 2022/1288, Annex I, top (9).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+  </si>
+  <si>
+    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1). See also Regulation (EU) 2022/1288, Annex I, top (9).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+  </si>
+  <si>
+    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, lignite and coal, etc.) (non-renewable energy source).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. See also Regulation (EU) 2022/1288, Annex I, top (19).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <r>
+      <t>Sites or operations that are partially or fully located in or near protected or biodiversity-sensitive areas, where their activities adversely impact these regions.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+    </r>
+  </si>
+  <si>
+    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. See also Regulation (EU) 2022/1288, Annex I, top 18(a).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EC) No 1893/2006, Annex I, Division 20.2.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 9</t>
+  </si>
+  <si>
+    <t>Involvement in activities, which cause land degradation, desertification or soil sealing.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of sustainable land or agriculture practices or policies.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of sustainable oceans or seas practices or policies.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Operations, which affect threatened species. See also Regulation (EU) 2022/1288, Annex I, top (20).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.1</t>
+  </si>
+  <si>
+    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.2</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See also Regulation (EU) 2022/1288, Annex I, top (21).</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 15</t>
+    </r>
+  </si>
+  <si>
+    <t>Emissions to water in tons (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See Regulation (EU) 2022/1288, Annex I, top (12).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 8</t>
+  </si>
+  <si>
+    <t>Amount of water withdrawn by the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Amount of water recycled or reused by the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Amount in cubic meters of water withdrawn per million EUR revenue.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Existence of a policy for water management.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factors 7, 8</t>
+  </si>
+  <si>
+    <r>
+      <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 8</t>
+    </r>
+  </si>
+  <si>
+    <t>Tons of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactive waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 9</t>
+  </si>
+  <si>
+    <t>Tons of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <t>Tons of emissions by inorganic pollutants. Inorganic pollutants include substances like arsenic, cadmium, lead, mercury, chromium, aluminium, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 1</t>
+  </si>
+  <si>
+    <t>Tons of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 2</t>
+  </si>
+  <si>
+    <t>Tons of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and the Montreal Protocol on Substances that Deplete the Ozone Layer.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 3</t>
+  </si>
+  <si>
+    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 4</t>
+  </si>
+  <si>
+    <t>Involvement in Human Rights related legal proceedings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+  </si>
+  <si>
+    <t>Abidance by the ILO Core Labour Standards.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factors 12, 13, 14</t>
+  </si>
+  <si>
+    <t>Involvement in corruption-related legal proceedings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of child labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of forced labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <t>The whole company is ISO 14001 certified.</t>
+  </si>
+  <si>
+    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 15</t>
+  </si>
+  <si>
+    <t>Involvement in a violation of the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of male employees
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of female employees
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of females on the board of directors of the company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of males on the board of directors of the company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all supervisory board members.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all board of directors members.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <r>
+      <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 14</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of a workplace accident prevention policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 1</t>
+  </si>
+  <si>
+    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 2</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of workdays lost to injuries, accidents, fatalities or illness in total.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labour, and forced labour.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 4</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of a grievance/complaints handling mechanism related to employee matters.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 5</t>
+  </si>
+  <si>
+    <t>Existence of a policy on the protection of whistleblowers. See also Regulation (EU) 2022/1288, Annex I, top (26).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 6</t>
+  </si>
+  <si>
+    <t>Number of reported discrimination-related incidents.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.1</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.2</t>
+    </r>
+  </si>
+  <si>
+    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 8</t>
+  </si>
+  <si>
+    <t>Existence of a human rights policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 9</t>
+  </si>
+  <si>
+    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy against trafficking in human beings.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Operations or suppliers at significant risk of incidents of child labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Operations or suppliers at significant risk of incidents of forced or compulsory labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of cases of severe human rights issues and incidents connected to the company.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Number of reported convictions for violations of anti-corruption and anti-bribery laws.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
+    </r>
+  </si>
+  <si>
+    <t>Amount of fines for violations of anti-corruption and anti-bribery laws.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1419,6 +1764,19 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1859,7 +2217,7 @@
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1897,7 +2255,7 @@
       <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -1935,7 +2293,7 @@
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -1973,7 +2331,7 @@
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -2009,18 +2367,18 @@
       <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
-        <v>39</v>
+      <c r="F6" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>26</v>
@@ -2034,24 +2392,24 @@
         <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
+      <c r="F7" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>26</v>
@@ -2068,23 +2426,23 @@
         <v>36</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>26</v>
@@ -2101,23 +2459,23 @@
         <v>36</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>26</v>
@@ -2131,26 +2489,26 @@
         <v>35</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>26</v>
@@ -2164,26 +2522,26 @@
         <v>35</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>26</v>
@@ -2197,26 +2555,26 @@
         <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>26</v>
@@ -2233,23 +2591,23 @@
         <v>36</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
+        <v>56</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>26</v>
@@ -2263,24 +2621,24 @@
         <v>35</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>26</v>
@@ -2294,24 +2652,24 @@
         <v>35</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
+        <v>60</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>26</v>
@@ -2325,26 +2683,26 @@
         <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
+        <v>62</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>26</v>
@@ -2358,24 +2716,24 @@
         <v>35</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" t="s">
-        <v>76</v>
+        <v>64</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>26</v>
@@ -2389,24 +2747,24 @@
         <v>35</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>79</v>
+        <v>66</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>26</v>
@@ -2420,26 +2778,26 @@
         <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>26</v>
@@ -2453,24 +2811,24 @@
         <v>35</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>85</v>
+        <v>71</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>26</v>
@@ -2484,24 +2842,24 @@
         <v>35</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>89</v>
+        <v>74</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>26</v>
@@ -2515,26 +2873,26 @@
         <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" t="s">
-        <v>92</v>
+        <v>76</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>26</v>
@@ -2548,26 +2906,26 @@
         <v>35</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
+        <v>79</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>26</v>
@@ -2581,24 +2939,24 @@
         <v>35</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" t="s">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>26</v>
@@ -2612,24 +2970,24 @@
         <v>35</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
-        <v>103</v>
+        <v>84</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>26</v>
@@ -2643,24 +3001,24 @@
         <v>35</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
+        <v>86</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>26</v>
@@ -2674,24 +3032,24 @@
         <v>35</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" t="s">
-        <v>109</v>
+        <v>88</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>26</v>
@@ -2705,22 +3063,22 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" t="s">
-        <v>112</v>
+        <v>91</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="G28" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>19</v>
@@ -2738,24 +3096,24 @@
         <v>35</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" t="s">
-        <v>117</v>
+        <v>95</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>26</v>
@@ -2769,24 +3127,24 @@
         <v>35</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" t="s">
-        <v>121</v>
+        <v>98</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>26</v>
@@ -2800,26 +3158,26 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" t="s">
-        <v>125</v>
+        <v>101</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J31" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>26</v>
@@ -2833,26 +3191,26 @@
         <v>35</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" t="s">
-        <v>129</v>
+        <v>104</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J32" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>26</v>
@@ -2866,28 +3224,28 @@
         <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F33" t="s">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J33" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>26</v>
@@ -2901,28 +3259,28 @@
         <v>35</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>135</v>
+        <v>108</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J34" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>26</v>
@@ -2936,28 +3294,28 @@
         <v>35</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" t="s">
-        <v>139</v>
+        <v>111</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J35" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>26</v>
@@ -2971,28 +3329,28 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" t="s">
-        <v>142</v>
+        <v>113</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J36" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>26</v>
@@ -3006,22 +3364,22 @@
         <v>35</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>145</v>
+        <v>115</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="G37" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>19</v>
@@ -3041,26 +3399,26 @@
         <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" t="s">
-        <v>150</v>
+        <v>119</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J38" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>26</v>
@@ -3074,28 +3432,28 @@
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" t="s">
-        <v>153</v>
+        <v>121</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J39" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>26</v>
@@ -3109,28 +3467,28 @@
         <v>35</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F40" t="s">
-        <v>156</v>
+        <v>123</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J40" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>26</v>
@@ -3144,28 +3502,28 @@
         <v>35</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" t="s">
-        <v>159</v>
+        <v>125</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J41" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>26</v>
@@ -3179,28 +3537,28 @@
         <v>35</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" t="s">
-        <v>162</v>
+        <v>127</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J42" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>26</v>
@@ -3214,28 +3572,28 @@
         <v>35</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" t="s">
-        <v>165</v>
+        <v>129</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J43" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>26</v>
@@ -3249,28 +3607,28 @@
         <v>35</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" t="s">
-        <v>168</v>
+        <v>131</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J44" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>26</v>
@@ -3284,28 +3642,28 @@
         <v>35</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" t="s">
-        <v>171</v>
+        <v>133</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J45" s="4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>26</v>
@@ -3319,22 +3677,22 @@
         <v>35</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F46" t="s">
-        <v>175</v>
+        <v>136</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="G46" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>19</v>
@@ -3354,22 +3712,22 @@
         <v>35</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F47" t="s">
-        <v>179</v>
+        <v>139</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G47" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>19</v>
@@ -3389,22 +3747,22 @@
         <v>35</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F48" t="s">
-        <v>183</v>
+        <v>142</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>19</v>
@@ -3424,22 +3782,22 @@
         <v>35</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F49" t="s">
-        <v>187</v>
+        <v>145</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="G49" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>19</v>
@@ -3459,22 +3817,22 @@
         <v>35</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F50" t="s">
-        <v>191</v>
+        <v>148</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="G50" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>19</v>
@@ -3494,22 +3852,22 @@
         <v>35</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F51" t="s">
-        <v>195</v>
+        <v>151</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="G51" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>19</v>
@@ -3529,22 +3887,22 @@
         <v>35</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F52" t="s">
-        <v>199</v>
+        <v>154</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="G52" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>19</v>
@@ -3564,22 +3922,22 @@
         <v>35</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F53" t="s">
-        <v>203</v>
+        <v>157</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="G53" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>19</v>
@@ -3599,22 +3957,22 @@
         <v>35</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F54" t="s">
-        <v>207</v>
+        <v>160</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="G54" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>19</v>
@@ -3634,22 +3992,22 @@
         <v>35</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F55" t="s">
-        <v>211</v>
+        <v>163</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="G55" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>19</v>
@@ -3669,22 +4027,22 @@
         <v>35</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F56" t="s">
-        <v>215</v>
+        <v>166</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="G56" t="s">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>19</v>
@@ -3704,28 +4062,28 @@
         <v>35</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F57" t="s">
-        <v>220</v>
+        <v>170</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H57" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="J57" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>26</v>
@@ -3739,28 +4097,28 @@
         <v>35</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F58" t="s">
-        <v>223</v>
+        <v>172</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H58" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J58" s="4" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>26</v>
@@ -3774,28 +4132,28 @@
         <v>35</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F59" t="s">
-        <v>227</v>
+        <v>175</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H59" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J59" s="4" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>26</v>
@@ -3809,28 +4167,28 @@
         <v>35</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F60" t="s">
-        <v>230</v>
+        <v>177</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H60" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J60" s="5" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>26</v>
@@ -3844,22 +4202,22 @@
         <v>35</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F61" t="s">
-        <v>234</v>
+        <v>180</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>19</v>
@@ -3879,22 +4237,22 @@
         <v>35</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F62" t="s">
-        <v>238</v>
+        <v>183</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="G62" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>19</v>
@@ -3914,26 +4272,26 @@
         <v>35</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F63" t="s">
-        <v>243</v>
+        <v>187</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="J63" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>26</v>
@@ -3947,26 +4305,26 @@
         <v>35</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F64" t="s">
-        <v>246</v>
+        <v>189</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="J64" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>26</v>
@@ -3980,26 +4338,26 @@
         <v>35</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F65" t="s">
-        <v>250</v>
+        <v>192</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I65" s="4" t="s">
+      <c r="J65" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>26</v>
@@ -4013,26 +4371,26 @@
         <v>35</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F66" t="s">
-        <v>253</v>
+        <v>194</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>387</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="J66" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>26</v>
@@ -4046,26 +4404,26 @@
         <v>35</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F67" t="s">
-        <v>256</v>
+        <v>196</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="J67" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>26</v>
@@ -4079,22 +4437,22 @@
         <v>35</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F68" t="s">
-        <v>259</v>
+        <v>198</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="G68" t="s">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>19</v>
@@ -4111,25 +4469,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>265</v>
+        <v>203</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="G69" t="s">
-        <v>266</v>
+        <v>204</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>19</v>
@@ -4146,25 +4504,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>267</v>
+        <v>205</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>269</v>
+        <v>206</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="G70" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>19</v>
@@ -4181,25 +4539,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>273</v>
+        <v>209</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="G71" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>19</v>
@@ -4216,25 +4574,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>277</v>
+        <v>212</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="G72" t="s">
-        <v>278</v>
+        <v>213</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>19</v>
@@ -4251,25 +4609,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>279</v>
+        <v>214</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>281</v>
+        <v>215</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>282</v>
+        <v>216</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>19</v>
@@ -4286,25 +4644,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>283</v>
+        <v>217</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>285</v>
+        <v>218</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>286</v>
+        <v>219</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>19</v>
@@ -4321,25 +4679,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>287</v>
+        <v>220</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>289</v>
+        <v>221</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>19</v>
@@ -4356,25 +4714,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>291</v>
+        <v>223</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>293</v>
+        <v>224</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>19</v>
@@ -4391,25 +4749,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>297</v>
+        <v>227</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>298</v>
+        <v>228</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>19</v>
@@ -4426,25 +4784,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>301</v>
+        <v>230</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="G78" t="s">
-        <v>302</v>
+        <v>231</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>19</v>
@@ -4461,25 +4819,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>303</v>
+        <v>232</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F79" t="s">
-        <v>305</v>
+        <v>233</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="G79" t="s">
-        <v>306</v>
+        <v>234</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>19</v>
@@ -4496,25 +4854,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>307</v>
+        <v>235</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>309</v>
+        <v>236</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>19</v>
@@ -4531,25 +4889,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>311</v>
+        <v>238</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>313</v>
+        <v>239</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>19</v>
@@ -4566,25 +4924,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>315</v>
+        <v>241</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>317</v>
+        <v>242</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>19</v>
@@ -4601,25 +4959,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>319</v>
+        <v>244</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>321</v>
+        <v>245</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>19</v>
@@ -4636,25 +4994,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F84" t="s">
-        <v>325</v>
+        <v>248</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="G84" t="s">
-        <v>326</v>
+        <v>249</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>19</v>
@@ -4671,25 +5029,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>327</v>
+        <v>250</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F85" t="s">
-        <v>329</v>
+        <v>251</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="G85" t="s">
-        <v>330</v>
+        <v>252</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>19</v>
@@ -4706,28 +5064,28 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>333</v>
+        <v>254</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>334</v>
+        <v>255</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>19</v>
@@ -4741,28 +5099,28 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>335</v>
+        <v>256</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>337</v>
+        <v>257</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>334</v>
+        <v>255</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>19</v>
@@ -4776,29 +5134,29 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>338</v>
+        <v>258</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F88" t="s">
-        <v>340</v>
+        <v>259</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>26</v>
@@ -4809,26 +5167,26 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>343</v>
+      <c r="F89" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
@@ -4840,26 +5198,26 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>345</v>
+        <v>263</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>347</v>
+        <v>264</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4" t="s">
@@ -4871,26 +5229,26 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>350</v>
+        <v>266</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
@@ -4902,26 +5260,26 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>351</v>
+        <v>267</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>353</v>
+        <v>268</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
@@ -4933,29 +5291,29 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>354</v>
+        <v>269</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F93" t="s">
-        <v>356</v>
+        <v>270</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>26</v>
@@ -4966,29 +5324,29 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>358</v>
+        <v>272</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="F94" t="s">
-        <v>360</v>
+        <v>273</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>26</v>
@@ -4999,25 +5357,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>361</v>
+        <v>274</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F95" t="s">
-        <v>363</v>
+        <v>275</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="G95" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>19</v>
@@ -5034,25 +5392,25 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="F96" t="s">
-        <v>367</v>
+        <v>278</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="G96" t="s">
-        <v>368</v>
+        <v>279</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>19</v>
@@ -5069,26 +5427,26 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>369</v>
+        <v>280</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="F97" t="s">
-        <v>371</v>
+        <v>281</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I97" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4" t="s">
@@ -5100,29 +5458,29 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>372</v>
+        <v>282</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>374</v>
+        <v>283</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>413</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I98" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J98" s="4" t="s">
-        <v>375</v>
+        <v>284</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>26</v>
@@ -5133,25 +5491,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>376</v>
+        <v>285</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F99" t="s">
-        <v>378</v>
+        <v>286</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="G99" t="s">
-        <v>379</v>
+        <v>287</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>19</v>
@@ -5168,25 +5526,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>380</v>
+        <v>288</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="F100" t="s">
-        <v>382</v>
+        <v>289</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="G100" t="s">
-        <v>383</v>
+        <v>290</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>19</v>
@@ -5203,25 +5561,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>384</v>
+        <v>291</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F101" t="s">
-        <v>386</v>
+        <v>292</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="G101" t="s">
-        <v>387</v>
+        <v>293</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>19</v>
@@ -5238,26 +5596,26 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>388</v>
+        <v>294</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F102" t="s">
-        <v>390</v>
+        <v>295</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>19</v>
@@ -5271,26 +5629,26 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>391</v>
+        <v>296</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F103" t="s">
-        <v>393</v>
+        <v>297</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>19</v>
@@ -5304,26 +5662,26 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>394</v>
+        <v>298</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F104" t="s">
-        <v>396</v>
+        <v>299</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4" t="s">
@@ -5335,25 +5693,25 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>397</v>
+        <v>300</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>400</v>
+        <v>302</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>401</v>
+        <v>303</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>19</v>
@@ -5370,25 +5728,25 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>403</v>
+        <v>305</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F106" t="s">
-        <v>405</v>
+        <v>306</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="G106" t="s">
-        <v>406</v>
+        <v>307</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>19</v>
@@ -5405,25 +5763,25 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>407</v>
+        <v>308</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F107" t="s">
-        <v>409</v>
+        <v>309</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="G107" t="s">
-        <v>410</v>
+        <v>310</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5440,25 +5798,25 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F108" t="s">
-        <v>413</v>
+        <v>312</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="G108" t="s">
-        <v>414</v>
+        <v>313</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>19</v>
@@ -5475,25 +5833,25 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>415</v>
+        <v>314</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="F109" t="s">
-        <v>417</v>
+        <v>315</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="G109" t="s">
-        <v>418</v>
+        <v>316</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>19</v>
@@ -5510,25 +5868,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>419</v>
+        <v>317</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F110" t="s">
-        <v>421</v>
+        <v>318</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>424</v>
       </c>
       <c r="G110" t="s">
-        <v>422</v>
+        <v>319</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>19</v>
@@ -5545,26 +5903,26 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>423</v>
+        <v>320</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="F111" t="s">
+        <v>321</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>425</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>19</v>
@@ -5578,28 +5936,28 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C112" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F112" t="s">
-        <v>429</v>
-      </c>
       <c r="G112" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>19</v>
@@ -5613,28 +5971,28 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>426</v>
+        <v>322</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>430</v>
+        <v>325</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F113" t="s">
-        <v>432</v>
+        <v>326</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>19</v>
@@ -5648,28 +6006,28 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>426</v>
+        <v>322</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>433</v>
+        <v>327</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F114" t="s">
-        <v>435</v>
+        <v>328</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>334</v>
+        <v>255</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>19</v>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212D04C2-B71C-4EF8-96DC-EA790CF686A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5B0553-AA9D-4BA5-A800-C924596E1F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="480" windowWidth="19380" windowHeight="20490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="429">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -172,9 +172,6 @@
     <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 1 greenhouse gas emissions in tonnes, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Number</t>
   </si>
   <si>
@@ -193,108 +190,69 @@
     <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the location-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the market-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 3 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 3 greenhouse gas emissions in tonnes, i.e. all indirect upstream and downstream emissions that are not included in scope 2 (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 3 upstream GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope 3 downstream GHG emissions </t>
-  </si>
-  <si>
     <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 4 GHG emissions</t>
   </si>
   <si>
@@ -310,9 +268,6 @@
     <t>ENTERPRISE_VALUE_IN_EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4). </t>
-  </si>
-  <si>
     <t>EUR</t>
   </si>
   <si>
@@ -322,18 +277,12 @@
     <t>TOTAL_REVENUE_IN_EUR</t>
   </si>
   <si>
-    <t>Total revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover. Overall turnover is equivalent to a firm's total revenues over some period of time.</t>
-  </si>
-  <si>
     <t>Carbon footprint</t>
   </si>
   <si>
     <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
   </si>
   <si>
-    <t>Tonnes of GHG emissions per million EUR enterprise value.</t>
-  </si>
-  <si>
     <t>Tonnes / €M Enterprise Value</t>
   </si>
   <si>
@@ -343,9 +292,6 @@
     <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
     <t>Tonnes / €M Revenue</t>
   </si>
   <si>
@@ -355,27 +301,18 @@
     <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions).</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 2</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 3</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions.</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 4</t>
   </si>
   <si>
@@ -391,9 +328,6 @@
     <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company derive any revenues from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels? (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
     <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
   </si>
   <si>
@@ -406,9 +340,6 @@
     <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>The sum of scope 1 and scope 2 emissions of financed companies.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tonnes </t>
   </si>
   <si>
@@ -418,9 +349,6 @@
     <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>The scope 3 emissions of financed companies.</t>
-  </si>
-  <si>
     <t>Energy performance</t>
   </si>
   <si>
@@ -430,9 +358,6 @@
     <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
     <t>GWh</t>
   </si>
   <si>
@@ -442,27 +367,18 @@
     <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Production</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of non-renewable energy produced, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
     <t>Relative Non-Renewable Energy Production</t>
   </si>
   <si>
     <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
   </si>
   <si>
-    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
     <t>Percent</t>
   </si>
   <si>
@@ -472,27 +388,18 @@
     <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of non-renewable energy consumed, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
     <t>Relative Non-Renewable Energy Consumption</t>
   </si>
   <si>
     <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
   </si>
   <si>
-    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
     <t>Applicable High Impact Climate Sectors</t>
   </si>
   <si>
     <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
   </si>
   <si>
-    <t>Please select any sector(s) applicable activities (NACE Codes A-H, L).</t>
-  </si>
-  <si>
     <t>Sector applicable activities.</t>
   </si>
   <si>
@@ -505,72 +412,48 @@
     <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1).</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Fossil Fuels</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, nuclear energy, lignite and coal) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Crude Oil</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Natural Gas</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Lignite</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Coal</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Nuclear Energy</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Other</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Biodiversity</t>
   </si>
   <si>
@@ -580,9 +463,6 @@
     <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments? Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
     <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
   </si>
   <si>
@@ -592,9 +472,6 @@
     <t>PROTECTED_AREAS_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions? For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
     <t>Sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions. For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
   </si>
   <si>
@@ -604,9 +481,6 @@
     <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated? For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
     <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
   </si>
   <si>
@@ -616,9 +490,6 @@
     <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status?</t>
-  </si>
-  <si>
     <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.</t>
   </si>
   <si>
@@ -628,9 +499,6 @@
     <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
   </si>
   <si>
-    <t>Is the company involved in manufacture of pesticides and other agrochemical products? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
     <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
   </si>
   <si>
@@ -640,9 +508,6 @@
     <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
   </si>
   <si>
-    <t>Is the company involved in activities, which cause land degradation, desertification or soil sealing? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Involvement in activities, which cause land degradation, desertification or soil sealing. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
   </si>
   <si>
@@ -652,9 +517,6 @@
     <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have sustainable land or agriculture practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of sustainable land or agriculture practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.</t>
   </si>
   <si>
@@ -664,9 +526,6 @@
     <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have sustainable oceans or seas practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of sustainable oceans or seas practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.</t>
   </si>
   <si>
@@ -676,9 +535,6 @@
     <t>THREATENED_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have operations, which affect threatened species? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
     <t>Operations, which affect threatened species. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
   </si>
   <si>
@@ -688,9 +544,6 @@
     <t>BIODIVERSITY_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2 .</t>
   </si>
   <si>
@@ -700,9 +553,6 @@
     <t>DEFORESTATION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy to address deforestation? If yes, please share the policy with us. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
     <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
   </si>
   <si>
@@ -715,18 +565,9 @@
     <t>EMISSIONS_TO_WATER_IN_T</t>
   </si>
   <si>
-    <t>Emissions to water in tonnes (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See  Regulation (EU) 2022/1288, Annex I, top (12).</t>
-  </si>
-  <si>
-    <t>Water Consumption</t>
-  </si>
-  <si>
     <t>WATER_CONS_IN_M3</t>
   </si>
   <si>
-    <t>Amount of water consumed by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1 .</t>
-  </si>
-  <si>
     <t>Cubic Meters</t>
   </si>
   <si>
@@ -736,18 +577,9 @@
     <t>WATER_REUSED_IN_M3</t>
   </si>
   <si>
-    <t>Amount of water recycled and reused by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.2 .</t>
-  </si>
-  <si>
-    <t>Relative Water Usage</t>
-  </si>
-  <si>
     <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Amount in cubic meters of fresh water used per million EUR revenue. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1.</t>
-  </si>
-  <si>
     <t>Cubic Meters / €M Revenue</t>
   </si>
   <si>
@@ -757,9 +589,6 @@
     <t>WATER_MANAGEMENT_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures for water management? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures for water management. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.</t>
   </si>
   <si>
@@ -769,9 +598,6 @@
     <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy? See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy. See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
   </si>
   <si>
@@ -784,18 +610,12 @@
     <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactice waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).</t>
-  </si>
-  <si>
     <t>Non-Recycled Waste</t>
   </si>
   <si>
     <t>NON_RECYCLED_WASTE_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17) and table 2, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Emissions</t>
   </si>
   <si>
@@ -805,36 +625,24 @@
     <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of emissions by inorganic pollutants. Inorganic pollutants include those resulting from radiant energy, noise, heat, or light, as well as substances like arsenic, cadmium, lead, mercury, chromium, aluminum, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, iron, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27) and table 2, indicator nr. 1.</t>
-  </si>
-  <si>
     <t>Emissions of Air Pollutants</t>
   </si>
   <si>
     <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and table 2, indicator nr. 2 and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.</t>
-  </si>
-  <si>
     <t>Emissions of Ozone Depletion Substances</t>
   </si>
   <si>
     <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and table 2, indicator nr. 3 and the Montreal Protocol on Substances that Deplete the Ozone Layer.</t>
-  </si>
-  <si>
     <t>Carbon Reduction Initiatives</t>
   </si>
   <si>
     <t>CARBON_REDUCTION_INITIATIVES</t>
   </si>
   <si>
-    <t>Does the company have any policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.</t>
   </si>
   <si>
@@ -850,9 +658,6 @@
     <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Has the company been involved in Human Rights related legal proceedings?</t>
-  </si>
-  <si>
     <t>Involvement in Human Rights related legal proceedings.</t>
   </si>
   <si>
@@ -862,9 +667,6 @@
     <t>ILO_CORE_LABOUR_STANDARDS</t>
   </si>
   <si>
-    <t>Does the company abide by the ILO Core Labour Standards?</t>
-  </si>
-  <si>
     <t>Abidance by the ILO Core Labour Standards.</t>
   </si>
   <si>
@@ -874,9 +676,6 @@
     <t>ENVIRONMENTAL_POLICY</t>
   </si>
   <si>
-    <t>Does the company have an environmental policy? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of an environmental policy.</t>
   </si>
   <si>
@@ -886,9 +685,6 @@
     <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Has the company been involved in corruption-related legal proceedings?</t>
-  </si>
-  <si>
     <t>Involvement in corruption-related legal proceedings.</t>
   </si>
   <si>
@@ -898,9 +694,6 @@
     <t>TRANSPARENCY_DISCLOSURE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a transparency policy? If yes, please share the policy with us. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
-  </si>
-  <si>
     <t>Existence of a transparency policy. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
   </si>
   <si>
@@ -910,9 +703,6 @@
     <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.</t>
   </si>
   <si>
@@ -922,9 +712,6 @@
     <t>POLICY_AGAINST_CHILD_LABOUR</t>
   </si>
   <si>
-    <t>Does the company have policies in place to abolish all forms of child labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to abolish all forms of child labour.</t>
   </si>
   <si>
@@ -934,9 +721,6 @@
     <t>POLICY_AGAINST_FORCED_LABOUR</t>
   </si>
   <si>
-    <t>Does the company have policies in place to abolish all forms of forced labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to abolish all forms of forced labour.</t>
   </si>
   <si>
@@ -946,9 +730,6 @@
     <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
   </si>
   <si>
-    <t>Does the company have policies in place to eliminate discrimination in the workplace? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
   </si>
   <si>
@@ -958,9 +739,6 @@
     <t>ISO_14001_CERTIFICATE</t>
   </si>
   <si>
-    <t>Is the company ISO 14001 certified (Environmental Management)? If yes, please share the certificate with us.</t>
-  </si>
-  <si>
     <t>The company is ISO 14001 certified.</t>
   </si>
   <si>
@@ -970,9 +748,6 @@
     <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t>Does the company have a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.</t>
   </si>
   <si>
@@ -982,9 +757,6 @@
     <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
   </si>
   <si>
@@ -994,9 +766,6 @@
     <t>TECHNOLOGIES_EXPERTISE_TRANSFER_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise.</t>
   </si>
   <si>
@@ -1006,21 +775,12 @@
     <t>FAIR_COMPETITION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place related to fair competition and anti-competitive cartels? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
   </si>
   <si>
-    <t>Violation Of Tax Rules And Regulation</t>
-  </si>
-  <si>
     <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
   </si>
   <si>
-    <t>Is the company involved in a violation of OECD Guidelines for Multinational Enterprises for Taxation? In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
     <t>Involvement in a violation of OECD Guidelines for Multinational Enterprises for Taxation: In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
   </si>
   <si>
@@ -1030,9 +790,6 @@
     <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
   </si>
   <si>
@@ -1042,9 +799,6 @@
     <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
   </si>
   <si>
-    <t>Does the company have grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
   </si>
   <si>
@@ -1054,9 +808,6 @@
     <t>AVG_GROSS_HOURLY_EARNINGS_MALE_EMPLOYEES</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of male employees</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -1066,27 +817,18 @@
     <t>AVG_GROSS_HOURLY_EARNINGS_FEMALE_EMPLOYEES</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of female employees</t>
-  </si>
-  <si>
     <t>Unadjusted gender pay gap</t>
   </si>
   <si>
     <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
   </si>
   <si>
-    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).</t>
-  </si>
-  <si>
     <t>Female Board Members - Supervisory Board</t>
   </si>
   <si>
     <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
   </si>
   <si>
-    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
     <t>Integer</t>
   </si>
   <si>
@@ -1096,36 +838,24 @@
     <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
   </si>
   <si>
-    <t>Number of females on the board of directors of the company</t>
-  </si>
-  <si>
     <t>Male Board Members - Supervisory Board</t>
   </si>
   <si>
     <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
   </si>
   <si>
-    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
     <t>Male Board Members - Board of Directors</t>
   </si>
   <si>
     <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
   </si>
   <si>
-    <t>Number of males on the board of directors of the company</t>
-  </si>
-  <si>
     <t>Board gender diversity - Supervisory Board</t>
   </si>
   <si>
     <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
   </si>
   <si>
-    <t>Percentage of female board members among all supervisory board members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Allowed Range: [0, 100]</t>
   </si>
   <si>
@@ -1135,18 +865,12 @@
     <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
   </si>
   <si>
-    <t>Percentage of female board members among all board of directors members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Controversial Weapons Exposure</t>
   </si>
   <si>
     <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
   </si>
   <si>
-    <t>Is the company involved in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons? See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
     <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
   </si>
   <si>
@@ -1156,9 +880,6 @@
     <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a workplace accident prevention policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a workplace accident prevention policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.</t>
   </si>
   <si>
@@ -1168,18 +889,12 @@
     <t>RATE_OF_ACCIDENTS</t>
   </si>
   <si>
-    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 2.</t>
-  </si>
-  <si>
     <t>Workdays Lost</t>
   </si>
   <si>
     <t>WORKDAYS_LOST</t>
   </si>
   <si>
-    <t>Number of workdays lost to injuries, accidents, fatalities or illness in total</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
@@ -1189,9 +904,6 @@
     <t>SUPPLIER_CODE_OF_CONDUCT</t>
   </si>
   <si>
-    <t>Does the company have a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.) If yes, please share the document with us.</t>
-  </si>
-  <si>
     <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.</t>
   </si>
   <si>
@@ -1201,9 +913,6 @@
     <t>GRIEVANCE_HANDLING_MECHANISM</t>
   </si>
   <si>
-    <t>Does the company have a grievance/complaints handling mechanism related to employee matters? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Existence of a grievance/complaints handling mechanism related to employee matters. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
   </si>
   <si>
@@ -1213,9 +922,6 @@
     <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy on the protection of whistleblowers? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy on the protection of whistleblowers. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.</t>
   </si>
   <si>
@@ -1225,27 +931,18 @@
     <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
   </si>
   <si>
-    <t>Number of reported discrimination-related incidents. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.1 .</t>
-  </si>
-  <si>
     <t>Sanctioned Incidents Of Discrimination</t>
   </si>
   <si>
     <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
   </si>
   <si>
-    <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.2 .</t>
-  </si>
-  <si>
     <t>Excessive CEO pay ratio</t>
   </si>
   <si>
     <t>EXCESSIVE_CEO_PAY_RATIO</t>
   </si>
   <si>
-    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual). See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Green securities</t>
   </si>
   <si>
@@ -1255,9 +952,6 @@
     <t>SECURITIES_NOT_CERTIFIED_AS_GREEN</t>
   </si>
   <si>
-    <t>Does the company have securities in investments not certified as green under a future EU legal act setting up an EU Green Bond Standard?</t>
-  </si>
-  <si>
     <t>Possession of securities in investments that are not certified as green under a future EU legal act setting up an EU Green Bond Standard.</t>
   </si>
   <si>
@@ -1270,9 +964,6 @@
     <t>HUMAN_RIGHTS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a human rights policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a human rights policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.</t>
   </si>
   <si>
@@ -1282,9 +973,6 @@
     <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
   </si>
   <si>
-    <t>Does the company have due diligence processes to identify, prevent, mitigate and address adverse human rights impacts? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
   </si>
   <si>
@@ -1294,33 +982,18 @@
     <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy against trafficking in human beings? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.)  If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of a policy against trafficking in human beings. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.</t>
   </si>
   <si>
-    <t>Reported Child Labour Incidents</t>
-  </si>
-  <si>
     <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Does the company have reported incidents of child labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
-  </si>
-  <si>
     <t>Reported incidents of child labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
   </si>
   <si>
-    <t>Reported Forced Or Compulsory Labour Incidents</t>
-  </si>
-  <si>
     <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Does the company have reported incidents of forced or compulsory labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Reported incidents of forced or compulsory labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
   </si>
   <si>
@@ -1330,9 +1003,6 @@
     <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of cases of severe human rights issues and incidents connected to the company. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 14. </t>
-  </si>
-  <si>
     <t>Anti-corruption and anti-bribery</t>
   </si>
   <si>
@@ -1342,32 +1012,714 @@
     <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 16. </t>
-  </si>
-  <si>
-    <t>Reported Convictions Of Bribery and Corruption</t>
-  </si>
-  <si>
     <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of reported convictions for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
-  </si>
-  <si>
     <t>Total Amount Of Reported Fines Of Bribery and Corruption</t>
   </si>
   <si>
     <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount of fines for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
+    <t>Scope 1 greenhouse gas emissions, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used). See also Regulation (EU) 2016/1011 Annex III (1)(e)(i).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions computed using the location-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions computed using the market-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 3 greenhouse gas emissions in tons, i.e., all indirect upstream and downstream emissions that are neither covered by scope 1 ghg emissions nor by scope 2 ghg emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii) and Regulation (EU) 2022/1288, Annex I, top (4) and formula (2)+(3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4) and formula (1)+(2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2</t>
+  </si>
+  <si>
+    <t>Total net or gross revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services. Overall turnover is equivalent to a firm's total revenues over some period of time. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of GHG emissions per million EUR enterprise value. See also (EU) 2022/1288 Annex I formula (2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 2</t>
+  </si>
+  <si>
+    <t>Tons of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions). See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 4</t>
+  </si>
+  <si>
+    <t>The sum of scope 1 and scope 2 emissions of financed companies.
+Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
+  </si>
+  <si>
+    <t>The scope 3 emissions of financed companies.
+Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy produced, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy consumed, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Sector applicable activities. See also Regulation (EU) 2022/1288, Annex I, top (9).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+  </si>
+  <si>
+    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1). See also Regulation (EU) 2022/1288, Annex I, top (9).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+  </si>
+  <si>
+    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, lignite and coal, etc.) (non-renewable energy source).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. See also Regulation (EU) 2022/1288, Annex I, top (19).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <r>
+      <t>Sites or operations that are partially or fully located in or near protected or biodiversity-sensitive areas, where their activities adversely impact these regions.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+    </r>
+  </si>
+  <si>
+    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. See also Regulation (EU) 2022/1288, Annex I, top 18(a).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EC) No 1893/2006, Annex I, Division 20.2.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 9</t>
+  </si>
+  <si>
+    <t>Involvement in activities, which cause land degradation, desertification or soil sealing.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of sustainable land or agriculture practices or policies.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of sustainable oceans or seas practices or policies.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Operations, which affect threatened species. See also Regulation (EU) 2022/1288, Annex I, top (20).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.1</t>
+  </si>
+  <si>
+    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.2</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See also Regulation (EU) 2022/1288, Annex I, top (21).</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 15</t>
+    </r>
+  </si>
+  <si>
+    <t>Emissions to water in tons (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See Regulation (EU) 2022/1288, Annex I, top (12).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 8</t>
+  </si>
+  <si>
+    <t>Amount of water withdrawn by the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Amount of water recycled or reused by the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Amount in cubic meters of water withdrawn per million EUR revenue.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Existence of a policy for water management.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factors 7, 8</t>
+  </si>
+  <si>
+    <r>
+      <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 8</t>
+    </r>
+  </si>
+  <si>
+    <t>Tons of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactive waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 9</t>
+  </si>
+  <si>
+    <t>Tons of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <t>Tons of emissions by inorganic pollutants. Inorganic pollutants include substances like arsenic, cadmium, lead, mercury, chromium, aluminium, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 1</t>
+  </si>
+  <si>
+    <t>Tons of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 2</t>
+  </si>
+  <si>
+    <t>Tons of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and the Montreal Protocol on Substances that Deplete the Ozone Layer.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 3</t>
+  </si>
+  <si>
+    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 4</t>
+  </si>
+  <si>
+    <t>Involvement in Human Rights related legal proceedings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+  </si>
+  <si>
+    <t>Abidance by the ILO Core Labour Standards.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factors 12, 13, 14</t>
+  </si>
+  <si>
+    <t>Involvement in corruption-related legal proceedings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of child labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of forced labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <t>The whole company is ISO 14001 certified.</t>
+  </si>
+  <si>
+    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 15</t>
+  </si>
+  <si>
+    <t>Involvement in a violation of the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of male employees
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of female employees
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of females on the board of directors of the company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of males on the board of directors of the company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all supervisory board members.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all board of directors members.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <r>
+      <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 14</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of a workplace accident prevention policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 1</t>
+  </si>
+  <si>
+    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 2</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of workdays lost to injuries, accidents, fatalities or illness in total.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labour, and forced labour.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 4</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of a grievance/complaints handling mechanism related to employee matters.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 5</t>
+  </si>
+  <si>
+    <t>Existence of a policy on the protection of whistleblowers. See also Regulation (EU) 2022/1288, Annex I, top (26).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 6</t>
+  </si>
+  <si>
+    <t>Number of reported discrimination-related incidents.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.1</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.2</t>
+    </r>
+  </si>
+  <si>
+    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 8</t>
+  </si>
+  <si>
+    <t>Existence of a human rights policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 9</t>
+  </si>
+  <si>
+    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy against trafficking in human beings.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Operations or suppliers at significant risk of incidents of child labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Operations or suppliers at significant risk of incidents of forced or compulsory labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of cases of severe human rights issues and incidents connected to the company.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Number of reported convictions for violations of anti-corruption and anti-bribery laws.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
+    </r>
+  </si>
+  <si>
+    <t>Amount of fines for violations of anti-corruption and anti-bribery laws.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
+  </si>
+  <si>
+    <t>Scope 3 downstream GHG emissions</t>
+  </si>
+  <si>
+    <t>Violation of UNGC principles and OECD Guidelines for Multinational Enterprises</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Water Withdrawal</t>
+    </r>
+  </si>
+  <si>
+    <t>Water Withdrawal Intensity</t>
+  </si>
+  <si>
+    <t>Risk of Child Labour Incidents</t>
+  </si>
+  <si>
+    <t>Risk of Forced Or Compulsory Labour Incidents</t>
+  </si>
+  <si>
+    <t>Number of Reported Convictions Of Bribery and Corruption</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1423,6 +1775,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1462,7 +1827,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1859,7 +2226,7 @@
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1897,7 +2264,7 @@
       <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -1929,13 +2296,13 @@
       <c r="C4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -1967,13 +2334,13 @@
       <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -2003,24 +2370,24 @@
       <c r="C6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
-        <v>39</v>
+      <c r="F6" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>26</v>
@@ -2034,24 +2401,24 @@
         <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
+      <c r="F7" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>26</v>
@@ -2067,24 +2434,24 @@
       <c r="C8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>47</v>
+      <c r="D8" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>26</v>
@@ -2100,24 +2467,24 @@
       <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>50</v>
+      <c r="D9" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>26</v>
@@ -2131,26 +2498,26 @@
         <v>35</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>26</v>
@@ -2164,26 +2531,26 @@
         <v>35</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>26</v>
@@ -2197,26 +2564,26 @@
         <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>59</v>
+        <v>42</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>26</v>
@@ -2232,24 +2599,24 @@
       <c r="C13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>62</v>
+      <c r="D13" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
+        <v>56</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>26</v>
@@ -2263,24 +2630,24 @@
         <v>35</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>42</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>26</v>
@@ -2294,24 +2661,24 @@
         <v>35</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>68</v>
+        <v>42</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>422</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>26</v>
@@ -2325,26 +2692,26 @@
         <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
+        <v>61</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>26</v>
@@ -2358,24 +2725,24 @@
         <v>35</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>74</v>
+        <v>42</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" t="s">
-        <v>76</v>
+        <v>63</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>26</v>
@@ -2389,24 +2756,24 @@
         <v>35</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>77</v>
+        <v>42</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>79</v>
+        <v>65</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>26</v>
@@ -2420,26 +2787,26 @@
         <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>80</v>
+        <v>42</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>26</v>
@@ -2453,24 +2820,24 @@
         <v>35</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>83</v>
+        <v>42</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>85</v>
+        <v>70</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>26</v>
@@ -2484,24 +2851,24 @@
         <v>35</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>87</v>
+        <v>42</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>89</v>
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>26</v>
@@ -2515,26 +2882,26 @@
         <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>90</v>
+        <v>42</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" t="s">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>26</v>
@@ -2548,26 +2915,26 @@
         <v>35</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>94</v>
+        <v>42</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
+        <v>78</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>26</v>
@@ -2581,24 +2948,24 @@
         <v>35</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>98</v>
+        <v>42</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" t="s">
-        <v>100</v>
+        <v>81</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>26</v>
@@ -2612,24 +2979,24 @@
         <v>35</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>101</v>
+        <v>42</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
-        <v>103</v>
+        <v>83</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>26</v>
@@ -2643,24 +3010,24 @@
         <v>35</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>104</v>
+        <v>42</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
+        <v>85</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>26</v>
@@ -2674,24 +3041,24 @@
         <v>35</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>107</v>
+        <v>42</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" t="s">
-        <v>109</v>
+        <v>87</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>26</v>
@@ -2705,22 +3072,22 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>110</v>
+        <v>42</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" t="s">
-        <v>112</v>
+        <v>90</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="G28" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>19</v>
@@ -2738,24 +3105,24 @@
         <v>35</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>115</v>
+        <v>42</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" t="s">
-        <v>117</v>
+        <v>94</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>26</v>
@@ -2769,24 +3136,24 @@
         <v>35</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>119</v>
+        <v>42</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" t="s">
-        <v>121</v>
+        <v>97</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>26</v>
@@ -2800,26 +3167,26 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>123</v>
+        <v>98</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" t="s">
-        <v>125</v>
+        <v>100</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J31" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>26</v>
@@ -2833,26 +3200,26 @@
         <v>35</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>127</v>
+        <v>98</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" t="s">
-        <v>129</v>
+        <v>103</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J32" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>26</v>
@@ -2866,28 +3233,28 @@
         <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>130</v>
+        <v>98</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F33" t="s">
-        <v>132</v>
+        <v>105</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J33" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>26</v>
@@ -2901,28 +3268,28 @@
         <v>35</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>133</v>
+        <v>98</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>135</v>
+        <v>107</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J34" s="4" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>26</v>
@@ -2936,28 +3303,28 @@
         <v>35</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>137</v>
+        <v>98</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" t="s">
-        <v>139</v>
+        <v>110</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J35" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>26</v>
@@ -2971,28 +3338,28 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" t="s">
-        <v>142</v>
+        <v>112</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J36" s="4" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>26</v>
@@ -3006,22 +3373,22 @@
         <v>35</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>143</v>
+        <v>98</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>145</v>
+        <v>114</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="G37" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>19</v>
@@ -3041,26 +3408,26 @@
         <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>148</v>
+        <v>98</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" t="s">
-        <v>150</v>
+        <v>118</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J38" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>26</v>
@@ -3074,28 +3441,28 @@
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>151</v>
+        <v>98</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" t="s">
-        <v>153</v>
+        <v>120</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J39" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>26</v>
@@ -3109,28 +3476,28 @@
         <v>35</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F40" t="s">
-        <v>156</v>
+      <c r="F40" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J40" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>26</v>
@@ -3144,28 +3511,28 @@
         <v>35</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" t="s">
-        <v>159</v>
+        <v>124</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J41" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>26</v>
@@ -3179,28 +3546,28 @@
         <v>35</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>160</v>
+        <v>98</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" t="s">
-        <v>162</v>
+        <v>126</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J42" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>26</v>
@@ -3214,28 +3581,28 @@
         <v>35</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>163</v>
+        <v>98</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" t="s">
-        <v>165</v>
+        <v>128</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J43" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>26</v>
@@ -3249,28 +3616,28 @@
         <v>35</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>166</v>
+        <v>98</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" t="s">
-        <v>168</v>
+        <v>130</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J44" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>26</v>
@@ -3284,28 +3651,28 @@
         <v>35</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>169</v>
+        <v>98</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" t="s">
-        <v>171</v>
+        <v>132</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J45" s="4" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>26</v>
@@ -3319,22 +3686,22 @@
         <v>35</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>173</v>
+        <v>133</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F46" t="s">
-        <v>175</v>
+        <v>135</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="G46" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>19</v>
@@ -3354,22 +3721,22 @@
         <v>35</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>177</v>
+        <v>133</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F47" t="s">
-        <v>179</v>
+        <v>138</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="G47" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>19</v>
@@ -3389,22 +3756,22 @@
         <v>35</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>181</v>
+        <v>133</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F48" t="s">
-        <v>183</v>
+        <v>141</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>19</v>
@@ -3424,22 +3791,22 @@
         <v>35</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>185</v>
+        <v>133</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F49" t="s">
-        <v>187</v>
+        <v>144</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="G49" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>19</v>
@@ -3459,22 +3826,22 @@
         <v>35</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>189</v>
+        <v>133</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F50" t="s">
-        <v>191</v>
+        <v>147</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="G50" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>19</v>
@@ -3494,22 +3861,22 @@
         <v>35</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>193</v>
+        <v>133</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>149</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F51" t="s">
-        <v>195</v>
+        <v>150</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="G51" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>19</v>
@@ -3529,22 +3896,22 @@
         <v>35</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>197</v>
+        <v>133</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F52" t="s">
-        <v>199</v>
+        <v>153</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="G52" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>19</v>
@@ -3564,22 +3931,22 @@
         <v>35</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>201</v>
+        <v>133</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F53" t="s">
-        <v>203</v>
+        <v>156</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="G53" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>19</v>
@@ -3599,22 +3966,22 @@
         <v>35</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>205</v>
+        <v>133</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F54" t="s">
-        <v>207</v>
+        <v>159</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G54" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>19</v>
@@ -3634,22 +4001,22 @@
         <v>35</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>209</v>
+        <v>133</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F55" t="s">
-        <v>211</v>
+        <v>162</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="G55" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>19</v>
@@ -3669,22 +4036,22 @@
         <v>35</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>213</v>
+        <v>133</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F56" t="s">
-        <v>215</v>
+        <v>165</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="G56" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>19</v>
@@ -3704,28 +4071,28 @@
         <v>35</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>218</v>
+        <v>167</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>168</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F57" t="s">
-        <v>220</v>
+        <v>169</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H57" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="J57" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>26</v>
@@ -3739,28 +4106,28 @@
         <v>35</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>221</v>
+        <v>167</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>424</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F58" t="s">
-        <v>223</v>
+        <v>170</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H58" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J58" s="4" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>26</v>
@@ -3774,28 +4141,28 @@
         <v>35</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>225</v>
+        <v>167</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F59" t="s">
-        <v>227</v>
+        <v>173</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H59" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J59" s="4" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>26</v>
@@ -3809,28 +4176,28 @@
         <v>35</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>228</v>
+        <v>167</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>425</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F60" t="s">
-        <v>230</v>
+        <v>174</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H60" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J60" s="5" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>26</v>
@@ -3844,22 +4211,22 @@
         <v>35</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>232</v>
+        <v>167</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F61" t="s">
-        <v>234</v>
+        <v>177</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>19</v>
@@ -3879,22 +4246,22 @@
         <v>35</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>236</v>
+        <v>167</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>179</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F62" t="s">
-        <v>238</v>
+        <v>180</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="G62" t="s">
-        <v>239</v>
+        <v>181</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>19</v>
@@ -3914,26 +4281,26 @@
         <v>35</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>241</v>
+        <v>182</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F63" t="s">
-        <v>243</v>
+        <v>184</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="J63" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>26</v>
@@ -3947,26 +4314,26 @@
         <v>35</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>244</v>
+        <v>182</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F64" t="s">
-        <v>246</v>
+        <v>186</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="J64" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>26</v>
@@ -3980,26 +4347,26 @@
         <v>35</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>248</v>
+        <v>187</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F65" t="s">
-        <v>250</v>
+        <v>189</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I65" s="4" t="s">
+      <c r="J65" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>26</v>
@@ -4013,26 +4380,26 @@
         <v>35</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>251</v>
+        <v>187</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F66" t="s">
-        <v>253</v>
+        <v>191</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="J66" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>26</v>
@@ -4046,26 +4413,26 @@
         <v>35</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>254</v>
+        <v>187</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F67" t="s">
-        <v>256</v>
+        <v>193</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="J67" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>26</v>
@@ -4079,22 +4446,22 @@
         <v>35</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>257</v>
+        <v>187</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F68" t="s">
-        <v>259</v>
+        <v>195</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="G68" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>19</v>
@@ -4111,25 +4478,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>263</v>
+        <v>198</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>265</v>
+        <v>200</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="G69" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>19</v>
@@ -4146,25 +4513,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>267</v>
+        <v>198</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>269</v>
+        <v>203</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="G70" t="s">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>19</v>
@@ -4181,25 +4548,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>271</v>
+        <v>198</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>273</v>
+        <v>206</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="G71" t="s">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>19</v>
@@ -4216,25 +4583,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>275</v>
+        <v>198</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>277</v>
+        <v>209</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="G72" t="s">
-        <v>278</v>
+        <v>210</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>19</v>
@@ -4251,25 +4618,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>279</v>
+        <v>198</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>281</v>
+        <v>212</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>19</v>
@@ -4286,25 +4653,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>283</v>
+        <v>198</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>214</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>285</v>
+        <v>215</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>19</v>
@@ -4321,25 +4688,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>287</v>
+        <v>198</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>289</v>
+        <v>218</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>387</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>19</v>
@@ -4356,25 +4723,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>291</v>
+        <v>198</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>293</v>
+        <v>221</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>19</v>
@@ -4391,25 +4758,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>295</v>
+        <v>198</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>297</v>
+        <v>224</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>19</v>
@@ -4426,25 +4793,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>299</v>
+        <v>198</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>301</v>
+        <v>227</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="G78" t="s">
-        <v>302</v>
+        <v>228</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>19</v>
@@ -4461,25 +4828,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>303</v>
+        <v>198</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F79" t="s">
-        <v>305</v>
+        <v>230</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="G79" t="s">
-        <v>306</v>
+        <v>231</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>19</v>
@@ -4496,25 +4863,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>307</v>
+        <v>198</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>309</v>
+        <v>233</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>19</v>
@@ -4531,25 +4898,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>311</v>
+        <v>198</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>313</v>
+        <v>236</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>314</v>
+        <v>237</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>19</v>
@@ -4566,25 +4933,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>315</v>
+        <v>198</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>317</v>
+        <v>239</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>318</v>
+        <v>240</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>19</v>
@@ -4601,25 +4968,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>319</v>
+        <v>198</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>321</v>
+        <v>241</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>322</v>
+        <v>242</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>19</v>
@@ -4636,25 +5003,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>323</v>
+        <v>198</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>243</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F84" t="s">
-        <v>325</v>
+        <v>244</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="G84" t="s">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>19</v>
@@ -4671,25 +5038,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>327</v>
+        <v>198</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F85" t="s">
-        <v>329</v>
+        <v>247</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="G85" t="s">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>19</v>
@@ -4706,28 +5073,28 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>331</v>
+        <v>198</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>333</v>
+        <v>250</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>334</v>
+        <v>251</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>19</v>
@@ -4741,28 +5108,28 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>335</v>
+        <v>198</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>337</v>
+        <v>253</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>334</v>
+        <v>251</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>19</v>
@@ -4776,29 +5143,29 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>338</v>
+        <v>198</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F88" t="s">
-        <v>340</v>
+        <v>255</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>26</v>
@@ -4809,26 +5176,26 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>341</v>
+        <v>198</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>343</v>
+        <v>257</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
@@ -4840,26 +5207,26 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>345</v>
+        <v>198</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>347</v>
+        <v>260</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4" t="s">
@@ -4871,26 +5238,26 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="E91" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>350</v>
+      <c r="F91" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
@@ -4902,26 +5269,26 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>351</v>
+        <v>198</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>353</v>
+        <v>264</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
@@ -4933,29 +5300,29 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>354</v>
+        <v>198</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>265</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F93" t="s">
-        <v>356</v>
+        <v>266</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>357</v>
+        <v>267</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>26</v>
@@ -4966,29 +5333,29 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>358</v>
+        <v>198</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="F94" t="s">
-        <v>360</v>
+        <v>269</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>357</v>
+        <v>267</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>26</v>
@@ -4999,25 +5366,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>361</v>
+        <v>198</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F95" t="s">
-        <v>363</v>
+        <v>271</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="G95" t="s">
-        <v>364</v>
+        <v>272</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>19</v>
@@ -5034,25 +5401,25 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>365</v>
+        <v>198</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="F96" t="s">
-        <v>367</v>
+        <v>274</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="G96" t="s">
-        <v>368</v>
+        <v>275</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>19</v>
@@ -5069,26 +5436,26 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>369</v>
+        <v>198</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>276</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="F97" t="s">
-        <v>371</v>
+        <v>277</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I97" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4" t="s">
@@ -5100,29 +5467,29 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>372</v>
+        <v>198</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>374</v>
+        <v>279</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I98" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J98" s="4" t="s">
-        <v>375</v>
+        <v>280</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>26</v>
@@ -5133,25 +5500,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>376</v>
+        <v>198</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>281</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F99" t="s">
-        <v>378</v>
+        <v>282</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="G99" t="s">
-        <v>379</v>
+        <v>283</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>19</v>
@@ -5168,25 +5535,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>380</v>
+        <v>198</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="F100" t="s">
-        <v>382</v>
+        <v>285</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="G100" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>19</v>
@@ -5203,25 +5570,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>384</v>
+        <v>198</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F101" t="s">
-        <v>386</v>
+        <v>288</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="G101" t="s">
-        <v>387</v>
+        <v>289</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>19</v>
@@ -5238,26 +5605,26 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>388</v>
+        <v>198</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F102" t="s">
-        <v>390</v>
+        <v>291</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>19</v>
@@ -5271,26 +5638,26 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>391</v>
+        <v>198</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F103" t="s">
-        <v>393</v>
+        <v>293</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>19</v>
@@ -5304,26 +5671,26 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>394</v>
+        <v>198</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F104" t="s">
-        <v>396</v>
+        <v>295</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4" t="s">
@@ -5335,25 +5702,25 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>398</v>
+        <v>296</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>297</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>400</v>
+        <v>298</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>401</v>
+        <v>299</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>19</v>
@@ -5370,25 +5737,25 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>402</v>
+        <v>300</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>403</v>
+        <v>301</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F106" t="s">
-        <v>405</v>
+        <v>302</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>413</v>
       </c>
       <c r="G106" t="s">
-        <v>406</v>
+        <v>303</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>19</v>
@@ -5405,25 +5772,25 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>402</v>
+        <v>300</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>407</v>
+        <v>304</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F107" t="s">
-        <v>409</v>
+        <v>305</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="G107" t="s">
-        <v>410</v>
+        <v>306</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5440,25 +5807,25 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>411</v>
+        <v>300</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F108" t="s">
-        <v>413</v>
+        <v>308</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="G108" t="s">
-        <v>414</v>
+        <v>309</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>19</v>
@@ -5475,25 +5842,25 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>415</v>
+        <v>300</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>426</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F109" t="s">
-        <v>417</v>
-      </c>
       <c r="G109" t="s">
-        <v>418</v>
+        <v>311</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>19</v>
@@ -5510,25 +5877,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>419</v>
+        <v>300</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>427</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F110" t="s">
-        <v>421</v>
+        <v>312</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="G110" t="s">
-        <v>422</v>
+        <v>313</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>19</v>
@@ -5545,26 +5912,26 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>423</v>
+        <v>300</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>314</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="F111" t="s">
-        <v>425</v>
+        <v>315</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>19</v>
@@ -5578,28 +5945,28 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>427</v>
+        <v>316</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F112" t="s">
-        <v>429</v>
+        <v>318</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>19</v>
@@ -5613,28 +5980,28 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>430</v>
+        <v>316</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F113" t="s">
-        <v>432</v>
+        <v>319</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>19</v>
@@ -5648,28 +6015,28 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>433</v>
+        <v>316</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>320</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F114" t="s">
-        <v>435</v>
+        <v>321</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>334</v>
+        <v>251</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>19</v>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5B0553-AA9D-4BA5-A800-C924596E1F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC97FBC-0DD9-4118-B187-D8039C864A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="392">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Please upload all relevant reports for this dataset in the PDF format.</t>
   </si>
   <si>
-    <t>All relevant reports for this dataset in PDF format.</t>
-  </si>
-  <si>
     <t>Report Preupload</t>
   </si>
   <si>
@@ -328,9 +325,6 @@
     <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
   </si>
   <si>
-    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
     <t>Yes/No</t>
   </si>
   <si>
@@ -400,9 +394,6 @@
     <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
   </si>
   <si>
-    <t>Sector applicable activities.</t>
-  </si>
-  <si>
     <t>Custom - SFDR High Impact Climate Sectors</t>
   </si>
   <si>
@@ -463,99 +454,66 @@
     <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
     <t>Protected Areas Exposure</t>
   </si>
   <si>
     <t>PROTECTED_AREAS_EXPOSURE</t>
   </si>
   <si>
-    <t>Sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions. For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
     <t>Rare Or Endangered Ecosystems Exposure</t>
   </si>
   <si>
     <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
   </si>
   <si>
-    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
     <t>Highly Biodiverse Grassland Exposure</t>
   </si>
   <si>
     <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
   </si>
   <si>
-    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.</t>
-  </si>
-  <si>
     <t>Manufacture Of Agrochemical Pesticides Products</t>
   </si>
   <si>
     <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
   </si>
   <si>
-    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
     <t>Land Degradation Desertification Soil Sealing Exposure</t>
   </si>
   <si>
     <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
   </si>
   <si>
-    <t>Involvement in activities, which cause land degradation, desertification or soil sealing. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Sustainable Agriculture Policy</t>
   </si>
   <si>
     <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
   </si>
   <si>
-    <t>Existence of sustainable land or agriculture practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>Sustainable Oceans And Seas Policy</t>
   </si>
   <si>
     <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
   </si>
   <si>
-    <t>Existence of sustainable oceans or seas practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.</t>
-  </si>
-  <si>
     <t>Threatened Species Exposure</t>
   </si>
   <si>
     <t>THREATENED_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Operations, which affect threatened species. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
     <t>Biodiversity Protection Policy</t>
   </si>
   <si>
     <t>BIODIVERSITY_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2 .</t>
-  </si>
-  <si>
     <t>Deforestation Policy</t>
   </si>
   <si>
     <t>DEFORESTATION_POLICY</t>
   </si>
   <si>
-    <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
     <t>Water</t>
   </si>
   <si>
@@ -577,6 +535,9 @@
     <t>WATER_REUSED_IN_M3</t>
   </si>
   <si>
+    <t>Relative Water Usage</t>
+  </si>
+  <si>
     <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
@@ -589,18 +550,12 @@
     <t>WATER_MANAGEMENT_POLICY</t>
   </si>
   <si>
-    <t>Existence of policies and procedures for water management. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.</t>
-  </si>
-  <si>
     <t>High Water Stress Area Exposure</t>
   </si>
   <si>
     <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
   </si>
   <si>
-    <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy. See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Waste</t>
   </si>
   <si>
@@ -643,9 +598,6 @@
     <t>CARBON_REDUCTION_INITIATIVES</t>
   </si>
   <si>
-    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.</t>
-  </si>
-  <si>
     <t>Social</t>
   </si>
   <si>
@@ -658,18 +610,12 @@
     <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Involvement in Human Rights related legal proceedings.</t>
-  </si>
-  <si>
     <t>ILO Core Labour Standards</t>
   </si>
   <si>
     <t>ILO_CORE_LABOUR_STANDARDS</t>
   </si>
   <si>
-    <t>Abidance by the ILO Core Labour Standards.</t>
-  </si>
-  <si>
     <t>Environmental Policy</t>
   </si>
   <si>
@@ -685,9 +631,6 @@
     <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Involvement in corruption-related legal proceedings.</t>
-  </si>
-  <si>
     <t>Transparency Disclosure Policy</t>
   </si>
   <si>
@@ -703,27 +646,18 @@
     <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
   </si>
   <si>
-    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.</t>
-  </si>
-  <si>
     <t>Policy against Child Labour</t>
   </si>
   <si>
     <t>POLICY_AGAINST_CHILD_LABOUR</t>
   </si>
   <si>
-    <t>Existence of policies in place to abolish all forms of child labour.</t>
-  </si>
-  <si>
     <t>Policy against Forced Labour</t>
   </si>
   <si>
     <t>POLICY_AGAINST_FORCED_LABOUR</t>
   </si>
   <si>
-    <t>Existence of policies in place to abolish all forms of forced labour.</t>
-  </si>
-  <si>
     <t>Policy against Discrimination in the Workplace</t>
   </si>
   <si>
@@ -739,18 +673,12 @@
     <t>ISO_14001_CERTIFICATE</t>
   </si>
   <si>
-    <t>The company is ISO 14001 certified.</t>
-  </si>
-  <si>
     <t>Policy against Bribery and Corruption</t>
   </si>
   <si>
     <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.</t>
-  </si>
-  <si>
     <t>Fair Business Marketing Advertising Policy</t>
   </si>
   <si>
@@ -778,30 +706,24 @@
     <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
   </si>
   <si>
+    <t>Violation Of Tax Rules And Regulation</t>
+  </si>
+  <si>
     <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
   </si>
   <si>
-    <t>Involvement in a violation of OECD Guidelines for Multinational Enterprises for Taxation: In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
     <t>UN Global Compact Principles Compliance Policy</t>
   </si>
   <si>
     <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
   </si>
   <si>
-    <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>OECD Guidelines For Multinational Enterprises Grievance Handling</t>
   </si>
   <si>
     <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
   </si>
   <si>
-    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>Average Gross Hourly Earnings Male Employees</t>
   </si>
   <si>
@@ -871,18 +793,12 @@
     <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
   </si>
   <si>
-    <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
     <t>Workplace Accident Prevention Policy</t>
   </si>
   <si>
     <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
   </si>
   <si>
-    <t>Existence of a workplace accident prevention policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.</t>
-  </si>
-  <si>
     <t>Rate Of Accidents</t>
   </si>
   <si>
@@ -904,27 +820,18 @@
     <t>SUPPLIER_CODE_OF_CONDUCT</t>
   </si>
   <si>
-    <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.</t>
-  </si>
-  <si>
     <t>Grievance Handling Mechanism</t>
   </si>
   <si>
     <t>GRIEVANCE_HANDLING_MECHANISM</t>
   </si>
   <si>
-    <t>Existence of a grievance/complaints handling mechanism related to employee matters. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Whistleblower Protection Policy</t>
   </si>
   <si>
     <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Existence of a policy on the protection of whistleblowers. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.</t>
-  </si>
-  <si>
     <t>Reported Incidents Of Discrimination</t>
   </si>
   <si>
@@ -964,39 +871,30 @@
     <t>HUMAN_RIGHTS_POLICY</t>
   </si>
   <si>
-    <t>Existence of a human rights policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.</t>
-  </si>
-  <si>
     <t>Human Rights Due Diligence</t>
   </si>
   <si>
     <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
   </si>
   <si>
-    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Trafficking In Human Beings Policy</t>
   </si>
   <si>
     <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
   </si>
   <si>
-    <t>Existence of a policy against trafficking in human beings. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.</t>
+    <t>Reported Child Labour Incidents</t>
   </si>
   <si>
     <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Reported incidents of child labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
+    <t>Reported Forced Or Compulsory Labour Incidents</t>
   </si>
   <si>
     <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Reported incidents of forced or compulsory labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Number Of Reported Incidents Of Human Rights Violations</t>
   </si>
   <si>
@@ -1010,6 +908,9 @@
   </si>
   <si>
     <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
+  </si>
+  <si>
+    <t>Reported Convictions Of Bribery and Corruption</t>
   </si>
   <si>
     <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
@@ -1690,7 +1591,7 @@
     <t>Scope 3 downstream GHG emissions</t>
   </si>
   <si>
-    <t>Violation of UNGC principles and OECD Guidelines for Multinational Enterprises</t>
+    <t>Data Point Type Name Overwrite</t>
   </si>
   <si>
     <r>
@@ -1699,27 +1600,15 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Water Withdrawal</t>
+      <t>Water Consumption</t>
     </r>
-  </si>
-  <si>
-    <t>Water Withdrawal Intensity</t>
-  </si>
-  <si>
-    <t>Risk of Child Labour Incidents</t>
-  </si>
-  <si>
-    <t>Risk of Forced Or Compulsory Labour Incidents</t>
-  </si>
-  <si>
-    <t>Number of Reported Convictions Of Bribery and Corruption</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1788,6 +1677,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1806,9 +1707,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1831,9 +1736,11 @@
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{F4874FAC-3F68-485B-89BC-5B693C7A2A35}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{074E82A9-1A36-405D-A4C5-F2557832B1C3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2145,8 +2052,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O114"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:P114"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
@@ -2163,7 +2070,7 @@
     <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2209,8 +2116,11 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2248,7 +2158,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2267,9 +2177,7 @@
       <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
         <v>24</v>
       </c>
@@ -2286,7 +2194,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2305,9 +2213,7 @@
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>20</v>
       </c>
@@ -2324,7 +2230,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2343,11 +2249,9 @@
       <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
@@ -2360,734 +2264,718 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:15" s="6" customFormat="1">
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="6" customFormat="1">
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="6" customFormat="1">
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K8" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="6" customFormat="1">
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="6" customFormat="1">
+    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="6" customFormat="1">
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="6" customFormat="1">
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="6" customFormat="1">
+    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="6" customFormat="1">
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="6" customFormat="1">
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="6" customFormat="1">
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="6" customFormat="1">
+    <row r="17" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="6" customFormat="1">
+    <row r="18" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="6" customFormat="1">
+    <row r="19" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="6" customFormat="1">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="D20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="6" customFormat="1">
+    <row r="21" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="6" customFormat="1">
+    <row r="22" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="6" customFormat="1">
+    <row r="23" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="6" customFormat="1">
+    <row r="24" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="6" customFormat="1">
+    <row r="25" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="6" customFormat="1">
+    <row r="26" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="6" customFormat="1">
+    <row r="27" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="6" customFormat="1">
+    <row r="28" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G28"/>
+      <c r="H28" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="G28" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>19</v>
@@ -3097,299 +2985,289 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="6" customFormat="1">
+    <row r="29" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="6" customFormat="1">
+    <row r="30" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="6" customFormat="1">
+    <row r="31" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J31" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="6" customFormat="1">
+    <row r="32" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J32" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="6" customFormat="1">
+    <row r="33" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J33" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="6" customFormat="1">
+    <row r="34" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D34" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="K34" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="4" t="s">
+      <c r="E35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="6" customFormat="1">
-      <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J35" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="6" customFormat="1">
+    <row r="36" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J36" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="6" customFormat="1">
+    <row r="37" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D37" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G37"/>
+      <c r="H37" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G37" t="s">
-        <v>115</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="I37" s="4" t="s">
         <v>19</v>
       </c>
@@ -3400,308 +3278,292 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="6" customFormat="1">
+    <row r="38" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J38" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="6" customFormat="1">
+    <row r="39" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J39" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="6" customFormat="1">
+    <row r="40" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J40" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="6" customFormat="1">
+    <row r="41" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J41" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="6" customFormat="1">
+    <row r="42" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J42" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="6" customFormat="1">
+    <row r="43" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J43" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="6" customFormat="1">
+    <row r="44" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J44" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="6" customFormat="1">
+    <row r="45" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J45" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="6" customFormat="1">
+    <row r="46" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="G46" t="s">
-        <v>136</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="G46"/>
       <c r="H46" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>19</v>
@@ -3713,30 +3575,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="6" customFormat="1">
+    <row r="47" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>137</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="G47" t="s">
-        <v>139</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="G47"/>
       <c r="H47" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>19</v>
@@ -3748,30 +3608,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="6" customFormat="1">
+    <row r="48" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>19</v>
@@ -3783,30 +3641,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="6" customFormat="1">
+    <row r="49" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="G49" t="s">
-        <v>145</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="G49"/>
       <c r="H49" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>19</v>
@@ -3818,30 +3674,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="6" customFormat="1">
+    <row r="50" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="G50" t="s">
-        <v>148</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G50"/>
       <c r="H50" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>19</v>
@@ -3853,30 +3707,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="6" customFormat="1">
+    <row r="51" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="G51" t="s">
-        <v>151</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="G51"/>
       <c r="H51" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>19</v>
@@ -3888,30 +3740,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="6" customFormat="1">
+    <row r="52" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="G52" t="s">
-        <v>154</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="G52"/>
       <c r="H52" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>19</v>
@@ -3923,30 +3773,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="6" customFormat="1">
+    <row r="53" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G53" t="s">
-        <v>157</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="G53"/>
       <c r="H53" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>19</v>
@@ -3958,30 +3806,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
+    <row r="54" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="G54" t="s">
-        <v>160</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="G54"/>
       <c r="H54" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>19</v>
@@ -3993,30 +3839,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="6" customFormat="1">
+    <row r="55" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G55" t="s">
-        <v>163</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="G55"/>
       <c r="H55" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>19</v>
@@ -4028,30 +3872,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="6" customFormat="1">
+    <row r="56" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G56" t="s">
-        <v>166</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="G56"/>
       <c r="H56" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>19</v>
@@ -4063,170 +3905,160 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="6" customFormat="1">
+    <row r="57" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="J57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J57" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K57" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="6" customFormat="1">
+    <row r="58" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="G58" s="4"/>
       <c r="H58" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J58" s="4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="6" customFormat="1">
+    <row r="59" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="G59" s="4"/>
       <c r="H59" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J59" s="4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="6" customFormat="1">
+    <row r="60" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>425</v>
+        <v>160</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="G60" s="4"/>
       <c r="H60" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J60" s="5" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="6" customFormat="1">
+    <row r="61" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G61" t="s">
-        <v>178</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="G61"/>
       <c r="H61" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>19</v>
@@ -4238,30 +4070,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="6" customFormat="1">
+    <row r="62" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="G62" t="s">
-        <v>181</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="G62"/>
       <c r="H62" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>19</v>
@@ -4273,195 +4103,193 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="6" customFormat="1">
+    <row r="63" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="J63" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K63" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="6" customFormat="1">
+    <row r="64" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="J64" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J64" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K64" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="6" customFormat="1">
+    <row r="65" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I65" s="4" t="s">
+      <c r="J65" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J65" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K65" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="6" customFormat="1">
+    <row r="66" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="J66" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K66" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="6" customFormat="1">
+    <row r="67" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="J67" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J67" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="K67" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="6" customFormat="1">
+    <row r="68" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="G68" t="s">
-        <v>196</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="G68"/>
       <c r="H68" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>19</v>
@@ -4473,30 +4301,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="6" customFormat="1">
+    <row r="69" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G69" t="s">
-        <v>201</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="G69"/>
       <c r="H69" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>19</v>
@@ -4508,30 +4334,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="6" customFormat="1">
+    <row r="70" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G70" t="s">
-        <v>204</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G70"/>
       <c r="H70" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>19</v>
@@ -4543,30 +4367,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:11" s="6" customFormat="1">
+    <row r="71" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G71" t="s">
-        <v>207</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G71"/>
       <c r="H71" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>19</v>
@@ -4578,30 +4400,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="6" customFormat="1">
+    <row r="72" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G72" t="s">
-        <v>210</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="G72"/>
       <c r="H72" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>19</v>
@@ -4613,30 +4433,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="6" customFormat="1">
+    <row r="73" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>213</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="G73" s="5"/>
       <c r="H73" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>19</v>
@@ -4648,30 +4466,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="6" customFormat="1">
+    <row r="74" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>216</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="G74" s="5"/>
       <c r="H74" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>19</v>
@@ -4683,30 +4499,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="6" customFormat="1">
+    <row r="75" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D75" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="E75" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>219</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="G75" s="5"/>
       <c r="H75" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>19</v>
@@ -4718,30 +4532,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="6" customFormat="1">
+    <row r="76" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>222</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>19</v>
@@ -4753,30 +4565,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="6" customFormat="1">
+    <row r="77" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>225</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>19</v>
@@ -4788,30 +4598,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="6" customFormat="1">
+    <row r="78" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="G78" t="s">
-        <v>228</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="G78"/>
       <c r="H78" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>19</v>
@@ -4823,30 +4631,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="6" customFormat="1">
+    <row r="79" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G79" t="s">
-        <v>231</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="G79"/>
       <c r="H79" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>19</v>
@@ -4858,30 +4664,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="6" customFormat="1">
+    <row r="80" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>234</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>19</v>
@@ -4893,30 +4697,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="6" customFormat="1">
+    <row r="81" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>237</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>19</v>
@@ -4928,30 +4730,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="6" customFormat="1">
+    <row r="82" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>240</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>19</v>
@@ -4963,30 +4763,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:11" s="6" customFormat="1">
+    <row r="83" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>423</v>
+        <v>217</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>242</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="G83" s="5"/>
       <c r="H83" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>19</v>
@@ -4998,30 +4796,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:11" s="6" customFormat="1">
+    <row r="84" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G84" t="s">
-        <v>245</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="G84"/>
       <c r="H84" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>19</v>
@@ -5033,30 +4829,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:11" s="6" customFormat="1">
+    <row r="85" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="G85" t="s">
-        <v>248</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="G85"/>
       <c r="H85" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>19</v>
@@ -5068,33 +4862,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="6" customFormat="1">
+    <row r="86" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>19</v>
@@ -5103,33 +4895,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:11" s="6" customFormat="1">
+    <row r="87" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>19</v>
@@ -5138,253 +4928,249 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="6" customFormat="1">
+    <row r="88" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:11" s="6" customFormat="1">
+    <row r="89" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:11" s="6" customFormat="1">
+    <row r="90" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:11" s="6" customFormat="1">
+    <row r="91" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="6" customFormat="1">
+    <row r="92" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="1:11" s="6" customFormat="1">
+    <row r="93" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="6" customFormat="1">
+    <row r="94" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:11" s="6" customFormat="1">
+    <row r="95" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="G95" t="s">
-        <v>272</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="G95"/>
       <c r="H95" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>19</v>
@@ -5396,30 +5182,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:11" s="6" customFormat="1">
+    <row r="96" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="G96" t="s">
-        <v>275</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="G96"/>
       <c r="H96" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>19</v>
@@ -5431,94 +5215,92 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="6" customFormat="1">
+    <row r="97" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I97" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="6" customFormat="1">
+    <row r="98" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I98" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J98" s="4" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="99" spans="1:11" s="6" customFormat="1">
+    <row r="99" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="G99" t="s">
-        <v>283</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="G99"/>
       <c r="H99" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>19</v>
@@ -5530,30 +5312,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:11" s="6" customFormat="1">
+    <row r="100" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="G100" t="s">
-        <v>286</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="G100"/>
       <c r="H100" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>19</v>
@@ -5565,30 +5345,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:11" s="6" customFormat="1">
+    <row r="101" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="G101" t="s">
-        <v>289</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="G101"/>
       <c r="H101" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>19</v>
@@ -5600,31 +5378,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:11" s="6" customFormat="1">
+    <row r="102" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>19</v>
@@ -5633,31 +5411,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:11" s="6" customFormat="1">
+    <row r="103" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>19</v>
@@ -5666,61 +5444,59 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="6" customFormat="1">
+    <row r="104" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:11" s="6" customFormat="1">
+    <row r="105" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>299</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="G105" s="5"/>
       <c r="H105" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>19</v>
@@ -5732,30 +5508,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="6" customFormat="1">
+    <row r="106" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G106" t="s">
-        <v>303</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="G106"/>
       <c r="H106" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>19</v>
@@ -5767,30 +5541,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:11" s="6" customFormat="1">
+    <row r="107" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="G107" t="s">
-        <v>306</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="G107"/>
       <c r="H107" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5802,30 +5574,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:11" s="6" customFormat="1">
+    <row r="108" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G108" t="s">
-        <v>309</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="G108"/>
       <c r="H108" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>19</v>
@@ -5837,30 +5607,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="6" customFormat="1">
+    <row r="109" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>426</v>
+        <v>276</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G109" t="s">
-        <v>311</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="G109"/>
       <c r="H109" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>19</v>
@@ -5872,30 +5640,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="6" customFormat="1">
+    <row r="110" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="G110" t="s">
-        <v>313</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="G110"/>
       <c r="H110" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>19</v>
@@ -5907,31 +5673,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:11" s="6" customFormat="1">
+    <row r="111" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>314</v>
+        <v>280</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>19</v>
@@ -5940,33 +5706,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:11" s="6" customFormat="1">
+    <row r="112" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>19</v>
@@ -5975,33 +5739,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:11" s="6" customFormat="1">
+    <row r="113" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>428</v>
+        <v>285</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>19</v>
@@ -6010,33 +5772,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:11" s="6" customFormat="1">
+    <row r="114" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>19</v>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC97FBC-0DD9-4118-B187-D8039C864A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815CF9E9-3A7D-494B-AD1A-2F6BDD17ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -316,9 +316,6 @@
     <t>GHG_INTENSITY_SCOPE_4_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
-  </si>
-  <si>
     <t>Fossil Fuel Sector Exposure</t>
   </si>
   <si>
@@ -1603,12 +1600,15 @@
       <t>Water Consumption</t>
     </r>
   </si>
+  <si>
+    <t>Tons of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2053,24 +2053,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P114"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="255.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="255.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2117,10 +2117,10 @@
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2158,7 +2158,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2194,7 +2194,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2230,7 +2230,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2264,7 +2264,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" s="6" customFormat="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>37</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
@@ -2297,7 +2297,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" s="6" customFormat="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
@@ -2328,7 +2328,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" s="6" customFormat="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
@@ -2361,7 +2361,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" s="6" customFormat="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
@@ -2394,7 +2394,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" s="6" customFormat="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
@@ -2425,7 +2425,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" s="6" customFormat="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
@@ -2456,7 +2456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" s="6" customFormat="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>53</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -2487,7 +2487,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" s="6" customFormat="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>55</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
@@ -2520,7 +2520,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" s="6" customFormat="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>57</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
@@ -2551,7 +2551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" s="6" customFormat="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2562,13 +2562,13 @@
         <v>41</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
@@ -2582,7 +2582,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" s="6" customFormat="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
@@ -2613,7 +2613,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" s="6" customFormat="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>62</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
@@ -2644,7 +2644,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" s="6" customFormat="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>64</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
@@ -2675,7 +2675,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" s="6" customFormat="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" s="6" customFormat="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>69</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
@@ -2737,7 +2737,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" s="6" customFormat="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
@@ -2768,7 +2768,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" s="6" customFormat="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>74</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
@@ -2799,7 +2799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" s="6" customFormat="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>77</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
@@ -2830,7 +2830,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" s="6" customFormat="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
@@ -2861,7 +2861,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" s="6" customFormat="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>82</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
@@ -2892,7 +2892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" s="6" customFormat="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>84</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
@@ -2923,7 +2923,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" s="6" customFormat="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>86</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>87</v>
+        <v>391</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
@@ -2954,7 +2954,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" s="6" customFormat="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -2965,17 +2965,17 @@
         <v>41</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G28"/>
       <c r="H28" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>19</v>
@@ -2985,7 +2985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" s="6" customFormat="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -2996,13 +2996,13 @@
         <v>41</v>
       </c>
       <c r="D29" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
@@ -3010,13 +3010,13 @@
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" s="6" customFormat="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -3027,13 +3027,13 @@
         <v>41</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
@@ -3041,13 +3041,13 @@
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" s="6" customFormat="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -3055,16 +3055,16 @@
         <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
@@ -3074,13 +3074,13 @@
         <v>39</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" s="6" customFormat="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -3088,16 +3088,16 @@
         <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D32" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
@@ -3107,13 +3107,13 @@
         <v>39</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" s="6" customFormat="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -3121,16 +3121,16 @@
         <v>34</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D33" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
@@ -3140,13 +3140,13 @@
         <v>39</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" s="6" customFormat="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -3154,16 +3154,16 @@
         <v>34</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D34" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
@@ -3173,30 +3173,30 @@
         <v>39</v>
       </c>
       <c r="J34" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="6" customFormat="1">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="E35" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
@@ -3206,13 +3206,13 @@
         <v>39</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" s="6" customFormat="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -3220,16 +3220,16 @@
         <v>34</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
@@ -3239,13 +3239,13 @@
         <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" s="6" customFormat="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -3253,20 +3253,20 @@
         <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G37"/>
       <c r="H37" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>19</v>
@@ -3278,7 +3278,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" s="6" customFormat="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -3286,16 +3286,16 @@
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
@@ -3305,13 +3305,13 @@
         <v>39</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" s="6" customFormat="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -3319,16 +3319,16 @@
         <v>34</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
@@ -3338,13 +3338,13 @@
         <v>39</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" s="6" customFormat="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -3352,16 +3352,16 @@
         <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
@@ -3371,13 +3371,13 @@
         <v>39</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" s="6" customFormat="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -3385,16 +3385,16 @@
         <v>34</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D41" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
@@ -3404,13 +3404,13 @@
         <v>39</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" s="6" customFormat="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -3418,16 +3418,16 @@
         <v>34</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="F42" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
@@ -3437,13 +3437,13 @@
         <v>39</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" s="6" customFormat="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -3451,16 +3451,16 @@
         <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D43" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="F43" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
@@ -3470,13 +3470,13 @@
         <v>39</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" s="6" customFormat="1">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -3484,16 +3484,16 @@
         <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D44" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="F44" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
@@ -3503,13 +3503,13 @@
         <v>39</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" s="6" customFormat="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -3517,16 +3517,16 @@
         <v>34</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D45" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="F45" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
@@ -3536,13 +3536,13 @@
         <v>39</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" s="6" customFormat="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -3550,20 +3550,20 @@
         <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="E46" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G46"/>
       <c r="H46" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>19</v>
@@ -3575,7 +3575,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" s="6" customFormat="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -3583,20 +3583,20 @@
         <v>34</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D47" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G47"/>
       <c r="H47" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>19</v>
@@ -3608,7 +3608,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" s="6" customFormat="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -3616,20 +3616,20 @@
         <v>34</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D48" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>19</v>
@@ -3641,7 +3641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" s="6" customFormat="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3649,20 +3649,20 @@
         <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G49"/>
       <c r="H49" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>19</v>
@@ -3674,7 +3674,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" s="6" customFormat="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -3682,20 +3682,20 @@
         <v>34</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D50" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G50"/>
       <c r="H50" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>19</v>
@@ -3707,7 +3707,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" s="6" customFormat="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -3715,20 +3715,20 @@
         <v>34</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D51" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G51"/>
       <c r="H51" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>19</v>
@@ -3740,7 +3740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" s="6" customFormat="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -3748,20 +3748,20 @@
         <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D52" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G52"/>
       <c r="H52" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>19</v>
@@ -3773,7 +3773,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" s="6" customFormat="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -3781,20 +3781,20 @@
         <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D53" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G53"/>
       <c r="H53" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>19</v>
@@ -3806,7 +3806,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" s="6" customFormat="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -3814,20 +3814,20 @@
         <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D54" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G54"/>
       <c r="H54" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>19</v>
@@ -3839,7 +3839,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" s="6" customFormat="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -3847,20 +3847,20 @@
         <v>34</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D55" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G55"/>
       <c r="H55" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>19</v>
@@ -3872,7 +3872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" s="6" customFormat="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -3880,20 +3880,20 @@
         <v>34</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D56" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G56"/>
       <c r="H56" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>19</v>
@@ -3905,7 +3905,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" s="6" customFormat="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -3913,16 +3913,16 @@
         <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="E57" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4" t="s">
@@ -3938,7 +3938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" s="6" customFormat="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -3946,16 +3946,16 @@
         <v>34</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4" t="s">
@@ -3965,13 +3965,13 @@
         <v>39</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" s="6" customFormat="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -3979,16 +3979,16 @@
         <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D59" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4" t="s">
@@ -3998,13 +3998,13 @@
         <v>39</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" s="6" customFormat="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -4012,16 +4012,16 @@
         <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D60" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4" t="s">
@@ -4031,13 +4031,13 @@
         <v>39</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" s="6" customFormat="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4045,20 +4045,20 @@
         <v>34</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D61" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G61"/>
       <c r="H61" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>19</v>
@@ -4070,7 +4070,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" s="6" customFormat="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -4078,20 +4078,20 @@
         <v>34</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D62" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G62"/>
       <c r="H62" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>19</v>
@@ -4103,7 +4103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" s="6" customFormat="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -4111,16 +4111,16 @@
         <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="E63" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="F63" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
@@ -4136,7 +4136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" s="6" customFormat="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -4144,16 +4144,16 @@
         <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="F64" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
@@ -4169,7 +4169,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" s="6" customFormat="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -4177,16 +4177,16 @@
         <v>34</v>
       </c>
       <c r="C65" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="E65" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
@@ -4202,7 +4202,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" s="6" customFormat="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -4210,16 +4210,16 @@
         <v>34</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D66" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
@@ -4235,7 +4235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" s="6" customFormat="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4243,16 +4243,16 @@
         <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D67" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
@@ -4268,7 +4268,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" s="6" customFormat="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -4276,20 +4276,20 @@
         <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D68" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G68"/>
       <c r="H68" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>19</v>
@@ -4301,28 +4301,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" s="6" customFormat="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="D69" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="E69" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="F69" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G69"/>
       <c r="H69" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>19</v>
@@ -4334,28 +4334,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" s="6" customFormat="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D70" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="F70" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G70"/>
       <c r="H70" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>19</v>
@@ -4367,28 +4367,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" s="6" customFormat="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D71" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="G71"/>
       <c r="H71" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>19</v>
@@ -4400,28 +4400,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" s="6" customFormat="1">
       <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D72" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G72"/>
       <c r="H72" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>19</v>
@@ -4433,28 +4433,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" s="6" customFormat="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D73" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>19</v>
@@ -4466,28 +4466,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" s="6" customFormat="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D74" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>19</v>
@@ -4499,28 +4499,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" s="6" customFormat="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D75" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>19</v>
@@ -4532,28 +4532,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" s="6" customFormat="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D76" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>19</v>
@@ -4565,28 +4565,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" s="6" customFormat="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D77" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>19</v>
@@ -4598,28 +4598,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" s="6" customFormat="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D78" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G78"/>
       <c r="H78" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>19</v>
@@ -4631,28 +4631,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" s="6" customFormat="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D79" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G79"/>
       <c r="H79" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>19</v>
@@ -4664,28 +4664,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" s="6" customFormat="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D80" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>19</v>
@@ -4697,28 +4697,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" s="6" customFormat="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D81" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>19</v>
@@ -4730,28 +4730,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" s="6" customFormat="1">
       <c r="A82" s="4">
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D82" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>19</v>
@@ -4763,28 +4763,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" s="6" customFormat="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D83" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="F83" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>19</v>
@@ -4796,28 +4796,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" s="6" customFormat="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D84" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G84"/>
       <c r="H84" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>19</v>
@@ -4829,28 +4829,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" s="6" customFormat="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D85" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="F85" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G85"/>
       <c r="H85" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>19</v>
@@ -4862,28 +4862,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" s="6" customFormat="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D86" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="F86" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>39</v>
@@ -4895,28 +4895,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" s="6" customFormat="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D87" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>39</v>
@@ -4928,24 +4928,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" s="6" customFormat="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D88" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
@@ -4953,34 +4953,34 @@
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" s="6" customFormat="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D89" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="F89" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>39</v>
@@ -4990,28 +4990,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" s="6" customFormat="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D90" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="F90" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>39</v>
@@ -5021,28 +5021,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" s="6" customFormat="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D91" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>39</v>
@@ -5052,28 +5052,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" s="6" customFormat="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D92" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>39</v>
@@ -5083,94 +5083,94 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" s="6" customFormat="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D93" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" s="6" customFormat="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D94" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" s="6" customFormat="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D95" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G95"/>
       <c r="H95" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>19</v>
@@ -5182,28 +5182,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" s="6" customFormat="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D96" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G96"/>
       <c r="H96" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>19</v>
@@ -5215,24 +5215,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" s="6" customFormat="1">
       <c r="A97" s="4">
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D97" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="F97" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
@@ -5246,24 +5246,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" s="6" customFormat="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D98" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="F98" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
@@ -5273,34 +5273,34 @@
         <v>39</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="99" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" s="6" customFormat="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D99" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="F99" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G99"/>
       <c r="H99" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>19</v>
@@ -5312,28 +5312,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" s="6" customFormat="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D100" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G100"/>
       <c r="H100" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>19</v>
@@ -5345,28 +5345,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" s="6" customFormat="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D101" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G101"/>
       <c r="H101" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>19</v>
@@ -5378,28 +5378,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" s="6" customFormat="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D102" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="F102" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>39</v>
@@ -5411,28 +5411,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" s="6" customFormat="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D103" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="F103" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>39</v>
@@ -5444,24 +5444,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" s="6" customFormat="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D104" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="F104" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
@@ -5475,28 +5475,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" s="6" customFormat="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C105" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D105" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="E105" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>19</v>
@@ -5508,28 +5508,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" s="6" customFormat="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C106" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D106" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="E106" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="F106" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G106"/>
       <c r="H106" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>19</v>
@@ -5541,28 +5541,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" s="6" customFormat="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D107" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G107"/>
       <c r="H107" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5574,28 +5574,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" s="6" customFormat="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D108" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="F108" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G108"/>
       <c r="H108" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>19</v>
@@ -5607,28 +5607,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" s="6" customFormat="1">
       <c r="A109" s="4">
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D109" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="F109" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G109"/>
       <c r="H109" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>19</v>
@@ -5640,28 +5640,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" s="6" customFormat="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D110" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G110"/>
       <c r="H110" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>19</v>
@@ -5673,28 +5673,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" s="6" customFormat="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D111" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>39</v>
@@ -5706,28 +5706,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" s="6" customFormat="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C112" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D112" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="E112" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="F112" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>39</v>
@@ -5739,28 +5739,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" s="6" customFormat="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D113" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="F113" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>39</v>
@@ -5772,28 +5772,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" s="6" customFormat="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D114" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="F114" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>39</v>

--- a/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
+++ b/dataland-framework-toolbox/inputs/sfdr/sfdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\sfdr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212D04C2-B71C-4EF8-96DC-EA790CF686A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815CF9E9-3A7D-494B-AD1A-2F6BDD17ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="480" windowWidth="19380" windowHeight="20490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="392">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Please upload all relevant reports for this dataset in the PDF format.</t>
   </si>
   <si>
-    <t>All relevant reports for this dataset in PDF format.</t>
-  </si>
-  <si>
     <t>Report Preupload</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 1 greenhouse gas emissions in tonnes, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Number</t>
   </si>
   <si>
@@ -193,108 +187,69 @@
     <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the location-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 2 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Scope 2 greenhouse gas emissions in tonnes from the consumption of purchased electricity, steam, or other sources of energy computed using the market-based method (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 3 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Scope 3 greenhouse gas emissions in tonnes, i.e. all indirect upstream and downstream emissions that are not included in scope 2 (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 3 upstream GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_3_UPSTREAM_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope 3 downstream GHG emissions </t>
-  </si>
-  <si>
     <t>SCOPE_3_DOWNSTREAM_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions (location-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_LOCATION_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 1 and 2 and 3 GHG emissions (market-based)</t>
   </si>
   <si>
     <t>SCOPE_1_2_3_GHG_EMISSIONS_MARKET_IN_T</t>
   </si>
   <si>
-    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used).</t>
-  </si>
-  <si>
     <t>Scope 4 GHG emissions</t>
   </si>
   <si>
@@ -310,9 +265,6 @@
     <t>ENTERPRISE_VALUE_IN_EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4). </t>
-  </si>
-  <si>
     <t>EUR</t>
   </si>
   <si>
@@ -322,18 +274,12 @@
     <t>TOTAL_REVENUE_IN_EUR</t>
   </si>
   <si>
-    <t>Total revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services after deducting sales rebates and value added tax and other taxes directly linked to turnover. Overall turnover is equivalent to a firm's total revenues over some period of time.</t>
-  </si>
-  <si>
     <t>Carbon footprint</t>
   </si>
   <si>
     <t>CARBON_FOOTPRINT_IN_T_PER_MIO_EUR_ENTERPRISE_VALUE</t>
   </si>
   <si>
-    <t>Tonnes of GHG emissions per million EUR enterprise value.</t>
-  </si>
-  <si>
     <t>Tonnes / €M Enterprise Value</t>
   </si>
   <si>
@@ -343,9 +289,6 @@
     <t>GHG_INTENSITY_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
     <t>Tonnes / €M Revenue</t>
   </si>
   <si>
@@ -355,48 +298,30 @@
     <t>GHG_INTENSITY_SCOPE_1_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions).</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 2</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_2_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions.</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 3</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_3_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions.</t>
-  </si>
-  <si>
     <t>GHG intensity - scope 4</t>
   </si>
   <si>
     <t>GHG_INTENSITY_SCOPE_4_IN_T_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Tonnes of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
-  </si>
-  <si>
     <t>Fossil Fuel Sector Exposure</t>
   </si>
   <si>
     <t>FOSSIL_FUEL_SECTOR_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company derive any revenues from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels? (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
-    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).</t>
-  </si>
-  <si>
     <t>Yes/No</t>
   </si>
   <si>
@@ -406,9 +331,6 @@
     <t>FINANCED_SCOPE_1_2_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>The sum of scope 1 and scope 2 emissions of financed companies.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tonnes </t>
   </si>
   <si>
@@ -418,9 +340,6 @@
     <t>FINANCED_SCOPE_3_EMISSIONS_IN_T</t>
   </si>
   <si>
-    <t>The scope 3 emissions of financed companies.</t>
-  </si>
-  <si>
     <t>Energy performance</t>
   </si>
   <si>
@@ -430,9 +349,6 @@
     <t>RENEWABLE_ENERGY_PROD_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
     <t>GWh</t>
   </si>
   <si>
@@ -442,27 +358,18 @@
     <t>RENEWABLE_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Production</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_PROD_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of non-renewable energy produced, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
     <t>Relative Non-Renewable Energy Production</t>
   </si>
   <si>
     <t>REL_NON_RENEWABLE_ENERGY_PROD_PCT</t>
   </si>
   <si>
-    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
     <t>Percent</t>
   </si>
   <si>
@@ -472,30 +379,18 @@
     <t>NON_RENEWABLE_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>Total value of non-renewable energy consumed, meaning energy from sources other than non-fossil sources. See also Regulation (EU) 2022/1288, Annex I, top (7).</t>
-  </si>
-  <si>
     <t>Relative Non-Renewable Energy Consumption</t>
   </si>
   <si>
     <t>REL_NON_RENEWABLE_ENERGY_CONS_PCT</t>
   </si>
   <si>
-    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable).</t>
-  </si>
-  <si>
     <t>Applicable High Impact Climate Sectors</t>
   </si>
   <si>
     <t>APPLICABLE_HIGH_IMPACT_CLIMATE_SECTORS</t>
   </si>
   <si>
-    <t>Please select any sector(s) applicable activities (NACE Codes A-H, L).</t>
-  </si>
-  <si>
-    <t>Sector applicable activities.</t>
-  </si>
-  <si>
     <t>Custom - SFDR High Impact Climate Sectors</t>
   </si>
   <si>
@@ -505,72 +400,48 @@
     <t>TOTAL_HIGH_IMPACT_CLIMATE_SECTOR_ENERGY_CONS_IN_GWH</t>
   </si>
   <si>
-    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1).</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Fossil Fuels</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_FOSSIL_FUELS_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, nuclear energy, lignite and coal) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Crude Oil</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_CRUDE_OIL_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Natural Gas</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_NATURAL_GAS_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Lignite</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_LIGNITE_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Coal</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_COAL_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Nuclear Energy</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_NUCLEAR_ENERGY_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Non-Renewable Energy Consumption Other</t>
   </si>
   <si>
     <t>NON_RENEWABLE_ENERGY_CONS_OTHER_IN_GWH</t>
   </si>
   <si>
-    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Biodiversity</t>
   </si>
   <si>
@@ -580,132 +451,66 @@
     <t>PRIMARY_FOREST_AND_WOODED_LAND_OF_NATIVE_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments? Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
-    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. Refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7 for more details.</t>
-  </si>
-  <si>
     <t>Protected Areas Exposure</t>
   </si>
   <si>
     <t>PROTECTED_AREAS_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions? For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
-    <t>Sites or operations that are partially or fully located in or near protected areas, where their activities adversely impact these regions. For further details, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7.</t>
-  </si>
-  <si>
     <t>Rare Or Endangered Ecosystems Exposure</t>
   </si>
   <si>
     <t>RARE_OR_ENDANGERED_ECOSYSTEMS_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated? For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
-    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. For more information, please refer to Regulation (EU) 2022/1288, Annex I, table 1, indicator number 7, and Annex I, item 18(a).</t>
-  </si>
-  <si>
     <t>Highly Biodiverse Grassland Exposure</t>
   </si>
   <si>
     <t>HIGHLY_BIODIVERSE_GRASSLAND_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status?</t>
-  </si>
-  <si>
-    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.</t>
-  </si>
-  <si>
     <t>Manufacture Of Agrochemical Pesticides Products</t>
   </si>
   <si>
     <t>MANUFACTURE_OF_AGROCHEMICAL_PESTICIDES_PRODUCTS</t>
   </si>
   <si>
-    <t>Is the company involved in manufacture of pesticides and other agrochemical products? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
-    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 9 and Regulation (EC) No 1893/2006, Annex I, Division 20.2.</t>
-  </si>
-  <si>
     <t>Land Degradation Desertification Soil Sealing Exposure</t>
   </si>
   <si>
     <t>LAND_DEGRADATION_DESERTIFICATION_SOIL_SEALING_EXPOSURE</t>
   </si>
   <si>
-    <t>Is the company involved in activities, which cause land degradation, desertification or soil sealing? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
-    <t>Involvement in activities, which cause land degradation, desertification or soil sealing. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Sustainable Agriculture Policy</t>
   </si>
   <si>
     <t>SUSTAINABLE_AGRICULTURE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have sustainable land or agriculture practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Existence of sustainable land or agriculture practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>Sustainable Oceans And Seas Policy</t>
   </si>
   <si>
     <t>SUSTAINABLE_OCEANS_AND_SEAS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have sustainable oceans or seas practices or policies? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Existence of sustainable oceans or seas practices or policies. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 12.</t>
-  </si>
-  <si>
     <t>Threatened Species Exposure</t>
   </si>
   <si>
     <t>THREATENED_SPECIES_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have operations, which affect threatened species? See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
-    <t>Operations, which affect threatened species. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.1 .</t>
-  </si>
-  <si>
     <t>Biodiversity Protection Policy</t>
   </si>
   <si>
     <t>BIODIVERSITY_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 14.2 .</t>
-  </si>
-  <si>
     <t>Deforestation Policy</t>
   </si>
   <si>
     <t>DEFORESTATION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy to address deforestation? If yes, please share the policy with us. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
-    <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 15.</t>
-  </si>
-  <si>
     <t>Water</t>
   </si>
   <si>
@@ -715,18 +520,9 @@
     <t>EMISSIONS_TO_WATER_IN_T</t>
   </si>
   <si>
-    <t>Emissions to water in tonnes (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See  Regulation (EU) 2022/1288, Annex I, top (12).</t>
-  </si>
-  <si>
-    <t>Water Consumption</t>
-  </si>
-  <si>
     <t>WATER_CONS_IN_M3</t>
   </si>
   <si>
-    <t>Amount of water consumed by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1 .</t>
-  </si>
-  <si>
     <t>Cubic Meters</t>
   </si>
   <si>
@@ -736,18 +532,12 @@
     <t>WATER_REUSED_IN_M3</t>
   </si>
   <si>
-    <t>Amount of water recycled and reused by the company. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.2 .</t>
-  </si>
-  <si>
     <t>Relative Water Usage</t>
   </si>
   <si>
     <t>REL_WATER_USAGE_IN_M3_PER_MIO_EUR_REVENUE</t>
   </si>
   <si>
-    <t>Amount in cubic meters of fresh water used per million EUR revenue. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 6.1.</t>
-  </si>
-  <si>
     <t>Cubic Meters / €M Revenue</t>
   </si>
   <si>
@@ -757,24 +547,12 @@
     <t>WATER_MANAGEMENT_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures for water management? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Existence of policies and procedures for water management. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 7.</t>
-  </si>
-  <si>
     <t>High Water Stress Area Exposure</t>
   </si>
   <si>
     <t>HIGH_WATER_STRESS_AREA_EXPOSURE</t>
   </si>
   <si>
-    <t>Does the company have sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy? See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
-    <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy. See Regulation (EU) 2022/1288, Annex I, top (13) and table 2, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Waste</t>
   </si>
   <si>
@@ -784,18 +562,12 @@
     <t>HAZARDOUS_AND_RADIOACTIVE_WASTE_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactice waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).</t>
-  </si>
-  <si>
     <t>Non-Recycled Waste</t>
   </si>
   <si>
     <t>NON_RECYCLED_WASTE_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17) and table 2, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Emissions</t>
   </si>
   <si>
@@ -805,39 +577,24 @@
     <t>EMISSIONS_OF_INORGANIC_POLLUTANTS_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of emissions by inorganic pollutants. Inorganic pollutants include those resulting from radiant energy, noise, heat, or light, as well as substances like arsenic, cadmium, lead, mercury, chromium, aluminum, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, iron, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27) and table 2, indicator nr. 1.</t>
-  </si>
-  <si>
     <t>Emissions of Air Pollutants</t>
   </si>
   <si>
     <t>EMISSIONS_OF_AIR_POLLUTANTS_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and table 2, indicator nr. 2 and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.</t>
-  </si>
-  <si>
     <t>Emissions of Ozone Depletion Substances</t>
   </si>
   <si>
     <t>EMISSIONS_OF_OZONE_DEPLETION_SUBSTANCES_IN_T</t>
   </si>
   <si>
-    <t>Tonnes of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and table 2, indicator nr. 3 and the Montreal Protocol on Substances that Deplete the Ozone Layer.</t>
-  </si>
-  <si>
     <t>Carbon Reduction Initiatives</t>
   </si>
   <si>
     <t>CARBON_REDUCTION_INITIATIVES</t>
   </si>
   <si>
-    <t>Does the company have any policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement? (See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement. See Regulation (EU) 2022/1288, Annex I, table 2, indicator nr. 4.</t>
-  </si>
-  <si>
     <t>Social</t>
   </si>
   <si>
@@ -850,33 +607,18 @@
     <t>HUMAN_RIGHTS_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Has the company been involved in Human Rights related legal proceedings?</t>
-  </si>
-  <si>
-    <t>Involvement in Human Rights related legal proceedings.</t>
-  </si>
-  <si>
     <t>ILO Core Labour Standards</t>
   </si>
   <si>
     <t>ILO_CORE_LABOUR_STANDARDS</t>
   </si>
   <si>
-    <t>Does the company abide by the ILO Core Labour Standards?</t>
-  </si>
-  <si>
-    <t>Abidance by the ILO Core Labour Standards.</t>
-  </si>
-  <si>
     <t>Environmental Policy</t>
   </si>
   <si>
     <t>ENVIRONMENTAL_POLICY</t>
   </si>
   <si>
-    <t>Does the company have an environmental policy? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of an environmental policy.</t>
   </si>
   <si>
@@ -886,21 +628,12 @@
     <t>CORRUPTION_LEGAL_PROCEEDINGS</t>
   </si>
   <si>
-    <t>Has the company been involved in corruption-related legal proceedings?</t>
-  </si>
-  <si>
-    <t>Involvement in corruption-related legal proceedings.</t>
-  </si>
-  <si>
     <t>Transparency Disclosure Policy</t>
   </si>
   <si>
     <t>TRANSPARENCY_DISCLOSURE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a transparency policy? If yes, please share the policy with us. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
-  </si>
-  <si>
     <t>Existence of a transparency policy. According to the OECD Guidelines for Multinational Enterprises, multinational companies should inform the public not only about their financial performance, but also about all of the important aspects of their business activities, such as how they are meeting social and environmental standards and what risks they foresee linked to their business activities.</t>
   </si>
   <si>
@@ -910,45 +643,24 @@
     <t>HUMAN_RIGHTS_DUE_DILIGENCE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.</t>
-  </si>
-  <si>
     <t>Policy against Child Labour</t>
   </si>
   <si>
     <t>POLICY_AGAINST_CHILD_LABOUR</t>
   </si>
   <si>
-    <t>Does the company have policies in place to abolish all forms of child labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to abolish all forms of child labour.</t>
-  </si>
-  <si>
     <t>Policy against Forced Labour</t>
   </si>
   <si>
     <t>POLICY_AGAINST_FORCED_LABOUR</t>
   </si>
   <si>
-    <t>Does the company have policies in place to abolish all forms of forced labour? If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of policies in place to abolish all forms of forced labour.</t>
-  </si>
-  <si>
     <t>Policy against Discrimination in the Workplace</t>
   </si>
   <si>
     <t>POLICY_AGAINST_DISCRIMINATION_IN_THE_WORKPLACE</t>
   </si>
   <si>
-    <t>Does the company have policies in place to eliminate discrimination in the workplace? If yes, please share the policy with us.</t>
-  </si>
-  <si>
     <t>Existence of policies in place to eliminate discrimination in the workplace.</t>
   </si>
   <si>
@@ -958,33 +670,18 @@
     <t>ISO_14001_CERTIFICATE</t>
   </si>
   <si>
-    <t>Is the company ISO 14001 certified (Environmental Management)? If yes, please share the certificate with us.</t>
-  </si>
-  <si>
-    <t>The company is ISO 14001 certified.</t>
-  </si>
-  <si>
     <t>Policy against Bribery and Corruption</t>
   </si>
   <si>
     <t>POLICY_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t>Does the company have a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 15.</t>
-  </si>
-  <si>
     <t>Fair Business Marketing Advertising Policy</t>
   </si>
   <si>
     <t>FAIR_BUSINESS_MARKETING_ADVERTISING_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place to apply fair business, marketing and advertising practices and to guarantee the safety and quality of the goods and services.</t>
   </si>
   <si>
@@ -994,9 +691,6 @@
     <t>TECHNOLOGIES_EXPERTISE_TRANSFER_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place to permit the transfer and rapid dissemination of technologies and expertise.</t>
   </si>
   <si>
@@ -1006,9 +700,6 @@
     <t>FAIR_COMPETITION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have policies and procedures in place related to fair competition and anti-competitive cartels? If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
     <t>Existence of policies and procedures in place related to fair competition and anti-competitive cartels.</t>
   </si>
   <si>
@@ -1018,45 +709,24 @@
     <t>VIOLATION_OF_TAX_RULES_AND_REGULATION</t>
   </si>
   <si>
-    <t>Is the company involved in a violation of OECD Guidelines for Multinational Enterprises for Taxation? In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
-    <t>Involvement in a violation of OECD Guidelines for Multinational Enterprises for Taxation: In the field of taxation, multinational enterprises should make their contribution to public finances within the framework of applicable law and regulations, in accordance with the tax rules and regulations of the host countries, and should cooperate with the tax authorities.</t>
-  </si>
-  <si>
     <t>UN Global Compact Principles Compliance Policy</t>
   </si>
   <si>
     <t>UNGC_PRINCIPLES_COMPLIANCE_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the relevant documents with us.</t>
-  </si>
-  <si>
-    <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>OECD Guidelines For Multinational Enterprises Grievance Handling</t>
   </si>
   <si>
     <t>OECD_GUIDELINES_GRIEVANCE_HANDLING</t>
   </si>
   <si>
-    <t>Does the company have grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises? (See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises. See Regulation (EU) 2022/1288, Annex I, top (22) and table 1, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>Average Gross Hourly Earnings Male Employees</t>
   </si>
   <si>
     <t>AVG_GROSS_HOURLY_EARNINGS_MALE_EMPLOYEES</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of male employees</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -1066,27 +736,18 @@
     <t>AVG_GROSS_HOURLY_EARNINGS_FEMALE_EMPLOYEES</t>
   </si>
   <si>
-    <t>Average gross hourly earnings of female employees</t>
-  </si>
-  <si>
     <t>Unadjusted gender pay gap</t>
   </si>
   <si>
     <t>UNADJUSTED_GENDER_PAY_GAP_PCT</t>
   </si>
   <si>
-    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).</t>
-  </si>
-  <si>
     <t>Female Board Members - Supervisory Board</t>
   </si>
   <si>
     <t>FEMALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
   </si>
   <si>
-    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
     <t>Integer</t>
   </si>
   <si>
@@ -1096,36 +757,24 @@
     <t>FEMALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
   </si>
   <si>
-    <t>Number of females on the board of directors of the company</t>
-  </si>
-  <si>
     <t>Male Board Members - Supervisory Board</t>
   </si>
   <si>
     <t>MALE_BOARD_MEMBERS_SUPERVISORY_BOARD</t>
   </si>
   <si>
-    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company</t>
-  </si>
-  <si>
     <t>Male Board Members - Board of Directors</t>
   </si>
   <si>
     <t>MALE_BOARD_MEMBERS_BOARD_OF_DIRECTORS</t>
   </si>
   <si>
-    <t>Number of males on the board of directors of the company</t>
-  </si>
-  <si>
     <t>Board gender diversity - Supervisory Board</t>
   </si>
   <si>
     <t>BOARD_GENDER_DIVERSITY_SUPERVISORY_BOARD_PCT</t>
   </si>
   <si>
-    <t>Percentage of female board members among all supervisory board members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Allowed Range: [0, 100]</t>
   </si>
   <si>
@@ -1135,51 +784,30 @@
     <t>BOARD_GENDER_DIVERSITY_BOARD_OF_DIRECTORS_PCT</t>
   </si>
   <si>
-    <t>Percentage of female board members among all board of directors members. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Controversial Weapons Exposure</t>
   </si>
   <si>
     <t>CONTROVERSIAL_WEAPONS_EXPOSURE</t>
   </si>
   <si>
-    <t>Is the company involved in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons? See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
-    <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons. See Regulation (EU) 2022/1288, Annex I, table 1, indicator nr. 14.</t>
-  </si>
-  <si>
     <t>Workplace Accident Prevention Policy</t>
   </si>
   <si>
     <t>WORKPLACE_ACCIDENT_PREVENTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a workplace accident prevention policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of a workplace accident prevention policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 1.</t>
-  </si>
-  <si>
     <t>Rate Of Accidents</t>
   </si>
   <si>
     <t>RATE_OF_ACCIDENTS</t>
   </si>
   <si>
-    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 2.</t>
-  </si>
-  <si>
     <t>Workdays Lost</t>
   </si>
   <si>
     <t>WORKDAYS_LOST</t>
   </si>
   <si>
-    <t>Number of workdays lost to injuries, accidents, fatalities or illness in total</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
@@ -1189,63 +817,36 @@
     <t>SUPPLIER_CODE_OF_CONDUCT</t>
   </si>
   <si>
-    <t>Does the company have a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.) If yes, please share the document with us.</t>
-  </si>
-  <si>
-    <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labor, and forced labor. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 4.</t>
-  </si>
-  <si>
     <t>Grievance Handling Mechanism</t>
   </si>
   <si>
     <t>GRIEVANCE_HANDLING_MECHANISM</t>
   </si>
   <si>
-    <t>Does the company have a grievance/complaints handling mechanism related to employee matters? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
-    <t>Existence of a grievance/complaints handling mechanism related to employee matters. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 5.</t>
-  </si>
-  <si>
     <t>Whistleblower Protection Policy</t>
   </si>
   <si>
     <t>WHISTLEBLOWER_PROTECTION_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy on the protection of whistleblowers? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of a policy on the protection of whistleblowers. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 6.</t>
-  </si>
-  <si>
     <t>Reported Incidents Of Discrimination</t>
   </si>
   <si>
     <t>REPORTED_INCIDENTS_OF_DISCRIMINATION</t>
   </si>
   <si>
-    <t>Number of reported discrimination-related incidents. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.1 .</t>
-  </si>
-  <si>
     <t>Sanctioned Incidents Of Discrimination</t>
   </si>
   <si>
     <t>SANCTIONED_INCIDENTS_OF_DISCRIMINATION</t>
   </si>
   <si>
-    <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 7.2 .</t>
-  </si>
-  <si>
     <t>Excessive CEO pay ratio</t>
   </si>
   <si>
     <t>EXCESSIVE_CEO_PAY_RATIO</t>
   </si>
   <si>
-    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual). See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 8.</t>
-  </si>
-  <si>
     <t>Green securities</t>
   </si>
   <si>
@@ -1255,9 +856,6 @@
     <t>SECURITIES_NOT_CERTIFIED_AS_GREEN</t>
   </si>
   <si>
-    <t>Does the company have securities in investments not certified as green under a future EU legal act setting up an EU Green Bond Standard?</t>
-  </si>
-  <si>
     <t>Possession of securities in investments that are not certified as green under a future EU legal act setting up an EU Green Bond Standard.</t>
   </si>
   <si>
@@ -1270,69 +868,36 @@
     <t>HUMAN_RIGHTS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a human rights policy? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.) If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of a human rights policy. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 9.</t>
-  </si>
-  <si>
     <t>Human Rights Due Diligence</t>
   </si>
   <si>
     <t>HUMAN_RIGHTS_DUE_DILIGENCE</t>
   </si>
   <si>
-    <t>Does the company have due diligence processes to identify, prevent, mitigate and address adverse human rights impacts? See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
-    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 10.</t>
-  </si>
-  <si>
     <t>Trafficking In Human Beings Policy</t>
   </si>
   <si>
     <t>TRAFFICKING_IN_HUMAN_BEINGS_POLICY</t>
   </si>
   <si>
-    <t>Does the company have a policy against trafficking in human beings? (See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.)  If yes, please share the policy with us.</t>
-  </si>
-  <si>
-    <t>Existence of a policy against trafficking in human beings. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 11.</t>
-  </si>
-  <si>
     <t>Reported Child Labour Incidents</t>
   </si>
   <si>
     <t>REPORTED_CHILD_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Does the company have reported incidents of child labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
-  </si>
-  <si>
-    <t>Reported incidents of child labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 12.</t>
-  </si>
-  <si>
     <t>Reported Forced Or Compulsory Labour Incidents</t>
   </si>
   <si>
     <t>REPORTED_FORCED_OR_COMPULSORY_LABOUR_INCIDENTS</t>
   </si>
   <si>
-    <t>Does the company have reported incidents of forced or compulsory labor within own operations or supply chain? Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
-    <t>Reported incidents of forced or compulsory labor within own operations or supply chain. Linked to Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 13.</t>
-  </si>
-  <si>
     <t>Number Of Reported Incidents Of Human Rights Violations</t>
   </si>
   <si>
     <t>NO_OF_REPORTED_INCIDENTS_OF_HUMAN_RIGHTS_VIOLATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of cases of severe human rights issues and incidents connected to the company. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 14. </t>
-  </si>
-  <si>
     <t>Anti-corruption and anti-bribery</t>
   </si>
   <si>
@@ -1342,32 +907,708 @@
     <t>CASES_OF_INSUFFICIENT_ACTION_AGAINST_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 16. </t>
-  </si>
-  <si>
     <t>Reported Convictions Of Bribery and Corruption</t>
   </si>
   <si>
     <t>REPORTED_CONVICTIONS_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of reported convictions for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
-  </si>
-  <si>
     <t>Total Amount Of Reported Fines Of Bribery and Corruption</t>
   </si>
   <si>
     <t>TOTAL_AMOUNT_OF_REPORTED_FINES_OF_BRIBERY_AND_CORRUPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount of fines for violations of anti-corruption and anti-bribery laws. See Regulation (EU) 2022/1288, Annex I, table 3, indicator nr. 17. </t>
+    <t>Scope 1 greenhouse gas emissions, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used). See also Regulation (EU) 2016/1011 Annex III (1)(e)(i).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions computed using the location-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions computed using the market-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions (computed preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the location-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1 and 2 greenhouse gas emissions, using the market-based method to compute the scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 3 greenhouse gas emissions in tons, i.e., all indirect upstream and downstream emissions that are neither covered by scope 1 ghg emissions nor by scope 2 ghg emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions from activities related to the production and distribution of goods and services purchased by the reporting company (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Indirect (gross) scope 3 greenhouse gas emissions that occur as a result of the use or disposal of the reporting company’s sold products and services (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions (computed preferably using the location-based method and equity share). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii) and Regulation (EU) 2022/1288, Annex I, top (4) and formula (2)+(3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the location-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Sum of scope 1, 2 and 3 greenhouse gas emissions, using the market-based method to compute scope 2 greenhouse gas emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(i)+(ii)+(iii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4) and formula (1)+(2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2</t>
+  </si>
+  <si>
+    <t>Total net or gross revenue in EUR for the financial year. i.e., income arising in the course of an entity's ordinary activities, the amounts derived from the sale of products and the provision of services. Overall turnover is equivalent to a firm's total revenues over some period of time. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of GHG emissions per million EUR enterprise value. See also (EU) 2022/1288 Annex I formula (2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 2</t>
+  </si>
+  <si>
+    <t>Tons of GHG emissions per million EUR revenue, preferably calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 1 GHG emissions per million EUR revenue. Scope 1 carbon emissions are emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used for emissions). See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 2 GHG emissions per million EUR revenue. Scope 2 emissions refer to those generated from the consumption of purchased electricity, steam, or other energy sources produced upstream by external entities or companies. Preferably, these should be calculated using the location-based method and the equity share approach for emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>Tons of scope 3 GHG emissions per million EUR revenue. Scope 3 emissions encompass all indirect upstream and downstream emissions not covered by Scope 2. Preferably, the equity share approach should be used for calculating these emissions. See also Regulation (EU) 2022/1288, Annex I, formula (3).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 3</t>
+  </si>
+  <si>
+    <t>(Part of) revenues derived from exploration, mining, extraction, production, processing, storage, refining or distribution, including transportation, storage and trade, of fossil fuels. (Fossil fuels mean non-renewable carbon-based energy sources such as solid fuels, natural gas and oil.) See also Regulation (EU) 2022/1288, Annex I, top (5).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 4</t>
+  </si>
+  <si>
+    <t>The sum of scope 1 and scope 2 emissions of financed companies.
+Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
+  </si>
+  <si>
+    <t>The scope 3 emissions of financed companies.
+Is part of scope 3 emissions and can be reported in Category 15 (Investments).</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy produced, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of renewable energy consumed, meaning energy from non-fossil sources, namely wind, solar (solar thermal and solar photovoltaic) and geothermal energy, ambient energy, tide, wave and other ocean energy, hydropower, biomass, landfill gas, sewage treatment plant gas, and biogas. See also Regulation (EU) 2022/1288, Annex I, top (6).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy produced, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy production from total energy production (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Total value of non-renewable energy consumed, meaning energy from sources other than renewable sources. See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Share of non-renewable energy consumption from total energy consumption (i.e. renewable plus non-renewable). See also Regulation (EU) 2022/1288, Annex I, top (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Sector applicable activities. See also Regulation (EU) 2022/1288, Annex I, top (9).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+  </si>
+  <si>
+    <t>"High impact climate sectors" refers to the sectors outlined in Sections A to H and Section L of Annex I of Regulation (EC) No 1893/2006 by the European Parliament and Council. This regulation, established on 20 December 2006, provides the statistical classification of economic activities known as NACE Revision 2 and amends Council Regulation (EEC) No 3037/90 and certain EC regulations related to specific statistical areas (OJ L 393, 30.12.2006, p. 1). See also Regulation (EU) 2022/1288, Annex I, top (9).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 6</t>
+  </si>
+  <si>
+    <t>Energy consumption from fossil fuels (sum of crude oil, natural gas, lignite and coal, etc.) (non-renewable energy source).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from crude oil (including petrol, diesel, fuel oil and others) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from natural gas (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from lignite (non-renewable energy source) Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from coal (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from nuclear energy (Uranium) (non-renewable energy source). Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Energy consumption from any other available (used) non-renewable source of energy. Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse sustainability indicator 5</t>
+  </si>
+  <si>
+    <t>Sites or operations that are located, either partially or entirely, in or near primary forests and other wooded areas where their activities have a negative impact on these environments. See also Regulation (EU) 2022/1288, Annex I, top (19).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <r>
+      <t>Sites or operations that are partially or fully located in or near protected or biodiversity-sensitive areas, where their activities adversely impact these regions.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+    </r>
+  </si>
+  <si>
+    <t>Sites or operations located in or near areas designated for the protection of species, including flora and fauna, where their activities lead to the deterioration of natural habitats and disturb the species for which these areas have been designated. See also Regulation (EU) 2022/1288, Annex I, top 18(a).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Sites or operations that are partially or fully situated in areas of highly biodiverse grassland, which may be categorized as either: (i) natural grassland, meaning areas that would remain grassland without human intervention and preserve natural species composition and ecological characteristics; or (ii) non-natural grassland, meaning areas that would no longer be grassland without human intervention but are species-rich and not degraded, unless it is demonstrated that harvesting the raw material is essential to maintain its grassland status.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 7</t>
+  </si>
+  <si>
+    <t>Involvements in manufacture of pesticides and other agrochemical products. See Regulation (EC) No 1893/2006, Annex I, Division 20.2.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 9</t>
+  </si>
+  <si>
+    <t>Involvement in activities, which cause land degradation, desertification or soil sealing.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of sustainable land or agriculture practices or policies.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of sustainable oceans or seas practices or policies.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Operations, which affect threatened species. See also Regulation (EU) 2022/1288, Annex I, top (20).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.1</t>
+  </si>
+  <si>
+    <t>Existence of a biodiversity protection policy that encompasses operational sites owned, leased, managed in, or adjacent to a protected area or an area of high biodiversity value outside protected areas.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 14.2</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy to address deforestation. "Deforestation" means the human-induced conversion of forested land to non-forested land, which can be permanent, when this change is definitive, or temporary when this change is part of a cycle that includes natural or assisted regeneration, according to the Intergovernmental Science-Policy Platform on Biodiversity and Ecosystem Services (IPBES) as referred to in paragraph 100 of Decision No 1386/2013/EU of the European Parliament and of the Council. See also Regulation (EU) 2022/1288, Annex I, top (21).</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 15</t>
+    </r>
+  </si>
+  <si>
+    <t>Emissions to water in tons (direct emissions of priority substances as defined in Article 2(30) of Directive 2000/60/EC of the European Parliament and of the Council and direct emissions of nitrates, phosphates and pesticides). See Regulation (EU) 2022/1288, Annex I, top (12).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 8</t>
+  </si>
+  <si>
+    <t>Amount of water withdrawn by the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Amount of water recycled or reused by the company.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Amount in cubic meters of water withdrawn per million EUR revenue.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 6.1</t>
+  </si>
+  <si>
+    <t>Existence of a policy for water management.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factors 7, 8</t>
+  </si>
+  <si>
+    <r>
+      <t>Sites or operations that are located, either partially or entirely, in "areas of high water stress", i.e. in regions where the percentage of total water withdrawn is high (40-80%) or extremely high (greater than 80%), without a water management policy.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 8</t>
+    </r>
+  </si>
+  <si>
+    <t>Tons of hazardous waste and radioactive waste generated: Hazardous waste are Explosives, Oxidizing substances, Highly flammable, Flammable, Irritant Harmful, Toxic, Carcinogenic, Corrosive, Infectious, Toxic for reproduction, Mutagenic, waste which releases toxic or very toxic gases in contact with water, air or an acid, Sensitizing, Ecotoxic, waste capable by any means after disposal of yielding another substance which possesses any of the characteristics listed above. Radioactive waste means radioactive material in gaseous, liquid or solid form for which no further use is foreseen. See Regulation (EU) 2022/1288, Annex I, top (14)-(16), Directive 2008/98/EC Annex III and Council Directive 2011/70/Euratom, Article 3 (7).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 9</t>
+  </si>
+  <si>
+    <t>Tons of non-recycled waste generated. "Non-recycled waste" means any waste not recycled within the meaning of ‘recycling’ in Article 3(17) of Directive 2008/98/EC. See Regulation (EU) 2022/1288, Annex I, top (17).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <t>Tons of emissions by inorganic pollutants. Inorganic pollutants include substances like arsenic, cadmium, lead, mercury, chromium, aluminium, nitrates, nitrites, fluorides, and water contaminants such as arsenic, fluoride, nitrate, and heavy metals. See Regulation (EU) 2022/1288, Annex I, top (27).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 1</t>
+  </si>
+  <si>
+    <t>Tons of emissions by air pollutants. Emissions by air pollutants include direct sulphur oxides (Sox/SO2) emissions, direct nitrogen oxides (NOx/NO2) emissions, direct ammonia (NH3) emissions, direct particulate matter (PM2.5) emissions, direct non-methane volatile organic compounds (NMVOC) emissions and direct total heavy metals (HM) emissions (encompassing cadmium, mercury and lead). See Regulation (EU) 2022/1288, Annex I, top (28) and Directive (EU) 2016/2284, Article 3, points (5)-(8) and Annex I, table A.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 2</t>
+  </si>
+  <si>
+    <t>Tons of ozone depletion substances, chemicals that destroy the earth's protective ozone layer. They include: chlorofluorocarbons (CFCs), halons, carbon tetrachloride (CCl4), methyl chloroform (CH3CCl3), hydrobromofluorocarbons (HBFCs), hydrochlorofluorocarbons (HCFCs), methyl bromide (CH3Br), bromochloromethane (CH2BrCl), hydrofluorocarbons (HFCs). See Regulation (EU) 2022/1288, Annex I, top (29) and the Montreal Protocol on Substances that Deplete the Ozone Layer.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 3</t>
+  </si>
+  <si>
+    <t>Existence of policies or procedures for carbon emission reduction aimed at aligning with the Paris Agreement.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 2, Adverse impact on sustainability factor 4</t>
+  </si>
+  <si>
+    <t>Involvement in Human Rights related legal proceedings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+  </si>
+  <si>
+    <t>Abidance by the ILO Core Labour Standards.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factors 12, 13, 14</t>
+  </si>
+  <si>
+    <t>Involvement in corruption-related legal proceedings.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to support/respect human rights and carry out due diligence to ensure that the business activities do not have a negative human rights impact.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of child labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Existence of policies in place to abolish all forms of forced labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <t>The whole company is ISO 14001 certified.</t>
+  </si>
+  <si>
+    <t>Existence of a policy on anti-corruption and anti-bribery consistent with the United Nations Convention against Corruption.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 15</t>
+  </si>
+  <si>
+    <t>Involvement in a violation of the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy to monitor compliance with the UNGC principles or OECD Guidelines for Multinational Enterprises.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of grievance/complaints handling mechanisms to address violations of the UNGC principles or OECD Guidelines for Multinational Enterprises.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 11</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of male employees
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>Average gross hourly earnings of female employees
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>(average gross hourly earnings of male paid employees - average gross hourly earnings of female paid employees)/ average gross hourly earnings of male paid employees (in Percent). See Regulation (EU) 2022/1288, Annex I, top (23).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 12</t>
+  </si>
+  <si>
+    <t>Number of females on the supervisory board, i.e. means the administrative, management or supervisory body of a company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of females on the board of directors of the company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of males on the supervisory board, i.e. means the administrative, management or supervisory body of a company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Number of males on the board of directors of the company
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all supervisory board members.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <t>Percentage of female board members among all board of directors members.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 13</t>
+  </si>
+  <si>
+    <r>
+      <t>Involvement in the manufacture or selling of controversial weapons such as anti-personnel mines, cluster munitions, chemical weapons and biological weapons.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 14</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of a workplace accident prevention policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 1</t>
+  </si>
+  <si>
+    <t>Rate of recordable work-related injuries as defined in GRI, i.e. (Number of recordable work-related injuries) /  (number of hours worked ) x 200,000.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 2</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of workdays lost to injuries, accidents, fatalities or illness in total.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a supplier code of conduct addressing unsafe working conditions, precarious work, child labour, and forced labour.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 4</t>
+    </r>
+  </si>
+  <si>
+    <t>Existence of a grievance/complaints handling mechanism related to employee matters.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 5</t>
+  </si>
+  <si>
+    <t>Existence of a policy on the protection of whistleblowers. See also Regulation (EU) 2022/1288, Annex I, top (26).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 6</t>
+  </si>
+  <si>
+    <t>Number of reported discrimination-related incidents.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.1</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of discrimination related incidents reported that lead to any kind of penalty and/or fine.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 7.2</t>
+    </r>
+  </si>
+  <si>
+    <t>Annual total compensation for the highest compensated individual divided by the median annual total compensation for all employees (excluding the highest-compensated individual).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 8</t>
+  </si>
+  <si>
+    <t>Existence of a human rights policy.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 9</t>
+  </si>
+  <si>
+    <t>Existence of due diligence processes to identify, prevent, mitigate and address adverse human rights impacts.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 10</t>
+  </si>
+  <si>
+    <r>
+      <t>Existence of a policy against trafficking in human beings.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 11</t>
+    </r>
+  </si>
+  <si>
+    <t>Operations or suppliers at significant risk of incidents of child labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 12</t>
+  </si>
+  <si>
+    <t>Operations or suppliers at significant risk of incidents of forced or compulsory labour.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 13</t>
+  </si>
+  <si>
+    <r>
+      <t>Number of cases of severe human rights issues and incidents connected to the company.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Identified insufficiencies in actions taken to address breaches in procedures and standards of anti-corruption and anti-bribery.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Number of reported convictions for violations of anti-corruption and anti-bribery laws.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
+    </r>
+  </si>
+  <si>
+    <t>Amount of fines for violations of anti-corruption and anti-bribery laws.
+Linked to Regulation (EU) 2022/1288, Annex I, Table 3, Adverse impact on sustainability factor 17</t>
+  </si>
+  <si>
+    <t>Scope 3 downstream GHG emissions</t>
+  </si>
+  <si>
+    <t>Data Point Type Name Overwrite</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Water Consumption</t>
+    </r>
+  </si>
+  <si>
+    <t>Tons of scope 4 GHG emissions per million EUR revenue. As per the GHG Protocol, Scope 4 refers to emissions avoided when a product is used as a substitute for other goods or services, providing the same functions with a lower carbon footprint.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1423,6 +1664,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1441,9 +1707,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1462,11 +1732,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{F4874FAC-3F68-485B-89BC-5B693C7A2A35}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{074E82A9-1A36-405D-A4C5-F2557832B1C3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1778,25 +2052,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O114"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:P114"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="255.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="255.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1842,8 +2116,11 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1859,7 +2136,7 @@
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1881,7 +2158,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1897,12 +2174,10 @@
       <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
         <v>24</v>
       </c>
@@ -1919,7 +2194,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1929,18 +2204,16 @@
       <c r="C4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>20</v>
       </c>
@@ -1957,7 +2230,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1967,20 +2240,18 @@
       <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
@@ -1993,358 +2264,350 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:15" s="6" customFormat="1">
+    <row r="6" spans="1:16" s="6" customFormat="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
+      <c r="F6" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="K6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="6" customFormat="1">
+    <row r="7" spans="1:16" s="6" customFormat="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
+      <c r="F7" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="6" customFormat="1">
+    <row r="8" spans="1:16" s="6" customFormat="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>47</v>
+      <c r="D8" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="K8" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="6" customFormat="1">
+    <row r="9" spans="1:16" s="6" customFormat="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>50</v>
+      <c r="D9" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
+        <v>47</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="K9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="6" customFormat="1">
+    <row r="10" spans="1:16" s="6" customFormat="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>53</v>
+        <v>41</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="6" customFormat="1">
+    <row r="11" spans="1:16" s="6" customFormat="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="6" customFormat="1">
+    <row r="12" spans="1:16" s="6" customFormat="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="6" customFormat="1">
+    <row r="13" spans="1:16" s="6" customFormat="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>62</v>
+      <c r="D13" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="K13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="6" customFormat="1">
+    <row r="14" spans="1:16" s="6" customFormat="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>41</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
+        <v>57</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="6" customFormat="1">
+    <row r="15" spans="1:16" s="6" customFormat="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>388</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" t="s">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="6" customFormat="1">
+    <row r="16" spans="1:16" s="6" customFormat="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>26</v>
@@ -2355,27 +2618,27 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>74</v>
+        <v>41</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" t="s">
-        <v>76</v>
+        <v>62</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>26</v>
@@ -2386,27 +2649,27 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>77</v>
+        <v>41</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>79</v>
+        <v>64</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>26</v>
@@ -2417,29 +2680,27 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>80</v>
+        <v>41</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>26</v>
@@ -2450,27 +2711,27 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>83</v>
+        <v>41</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>85</v>
+        <v>69</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>26</v>
@@ -2481,27 +2742,27 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>87</v>
+        <v>41</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>26</v>
@@ -2512,29 +2773,27 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>26</v>
@@ -2545,29 +2804,27 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>94</v>
+        <v>41</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>26</v>
@@ -2578,27 +2835,27 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>98</v>
+        <v>41</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" t="s">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>26</v>
@@ -2609,27 +2866,27 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>101</v>
+        <v>41</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
-        <v>103</v>
+        <v>82</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>26</v>
@@ -2640,27 +2897,27 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>104</v>
+        <v>41</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
+        <v>84</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>26</v>
@@ -2671,27 +2928,27 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>107</v>
+        <v>41</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" t="s">
-        <v>109</v>
+        <v>86</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>26</v>
@@ -2702,25 +2959,23 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>110</v>
+        <v>41</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" t="s">
-        <v>113</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G28"/>
       <c r="H28" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>19</v>
@@ -2735,27 +2990,27 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>115</v>
+        <v>41</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" t="s">
-        <v>117</v>
+        <v>91</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>26</v>
@@ -2766,27 +3021,27 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>119</v>
+        <v>41</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="5" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>26</v>
@@ -2797,29 +3052,29 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>123</v>
+        <v>95</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" t="s">
-        <v>125</v>
+        <v>97</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>26</v>
@@ -2830,29 +3085,29 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>127</v>
+        <v>95</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" t="s">
-        <v>129</v>
+        <v>100</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>26</v>
@@ -2863,31 +3118,29 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>130</v>
+        <v>95</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F33" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>26</v>
@@ -2898,31 +3151,29 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>133</v>
+        <v>95</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>26</v>
@@ -2933,31 +3184,29 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>137</v>
+        <v>95</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>26</v>
@@ -2968,31 +3217,29 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>140</v>
+        <v>95</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>26</v>
@@ -3003,25 +3250,23 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>143</v>
+        <v>95</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G37" t="s">
-        <v>146</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G37"/>
       <c r="H37" s="4" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>19</v>
@@ -3038,29 +3283,29 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>148</v>
+        <v>95</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" t="s">
-        <v>150</v>
+        <v>114</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>26</v>
@@ -3071,31 +3316,29 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>151</v>
+        <v>95</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>115</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>26</v>
@@ -3106,31 +3349,29 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>154</v>
+        <v>95</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F40" t="s">
-        <v>156</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>26</v>
@@ -3141,31 +3382,29 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>157</v>
+        <v>95</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" t="s">
-        <v>159</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>26</v>
@@ -3176,31 +3415,29 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" t="s">
-        <v>162</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="F42" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>26</v>
@@ -3211,31 +3448,29 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>163</v>
+        <v>95</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" t="s">
-        <v>165</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>26</v>
@@ -3246,31 +3481,29 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>166</v>
+        <v>95</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" t="s">
-        <v>168</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>26</v>
@@ -3281,31 +3514,29 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>169</v>
+        <v>95</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" t="s">
-        <v>171</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>26</v>
@@ -3316,25 +3547,23 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>173</v>
+        <v>129</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F46" t="s">
-        <v>175</v>
-      </c>
-      <c r="G46" t="s">
-        <v>176</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G46"/>
       <c r="H46" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>19</v>
@@ -3351,25 +3580,23 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>177</v>
+        <v>129</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F47" t="s">
-        <v>179</v>
-      </c>
-      <c r="G47" t="s">
-        <v>180</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G47"/>
       <c r="H47" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>19</v>
@@ -3386,25 +3613,23 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>181</v>
+        <v>129</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F48" t="s">
-        <v>183</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>184</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>19</v>
@@ -3421,25 +3646,23 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>185</v>
+        <v>129</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F49" t="s">
-        <v>187</v>
-      </c>
-      <c r="G49" t="s">
-        <v>188</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G49"/>
       <c r="H49" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>19</v>
@@ -3456,25 +3679,23 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>189</v>
+        <v>129</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F50" t="s">
-        <v>191</v>
-      </c>
-      <c r="G50" t="s">
-        <v>192</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G50"/>
       <c r="H50" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>19</v>
@@ -3491,25 +3712,23 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>193</v>
+        <v>129</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G51" t="s">
-        <v>196</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G51"/>
       <c r="H51" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>19</v>
@@ -3526,25 +3745,23 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>197</v>
+        <v>129</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F52" t="s">
-        <v>199</v>
-      </c>
-      <c r="G52" t="s">
-        <v>200</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G52"/>
       <c r="H52" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>19</v>
@@ -3561,25 +3778,23 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>201</v>
+        <v>129</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F53" t="s">
-        <v>203</v>
-      </c>
-      <c r="G53" t="s">
-        <v>204</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53"/>
       <c r="H53" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>19</v>
@@ -3596,25 +3811,23 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>205</v>
+        <v>129</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F54" t="s">
-        <v>207</v>
-      </c>
-      <c r="G54" t="s">
-        <v>208</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G54"/>
       <c r="H54" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>19</v>
@@ -3631,25 +3844,23 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>209</v>
+        <v>129</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F55" t="s">
-        <v>211</v>
-      </c>
-      <c r="G55" t="s">
-        <v>212</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G55"/>
       <c r="H55" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>19</v>
@@ -3666,25 +3877,23 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>213</v>
+        <v>129</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F56" t="s">
-        <v>215</v>
-      </c>
-      <c r="G56" t="s">
-        <v>216</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G56"/>
       <c r="H56" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>19</v>
@@ -3701,31 +3910,29 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>218</v>
+        <v>152</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F57" t="s">
-        <v>220</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J57" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>26</v>
@@ -3736,31 +3943,29 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>221</v>
+        <v>152</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>390</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F58" t="s">
-        <v>223</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G58" s="4"/>
       <c r="H58" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>26</v>
@@ -3771,31 +3976,29 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>225</v>
+        <v>152</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F59" t="s">
-        <v>227</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G59" s="4"/>
       <c r="H59" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>26</v>
@@ -3806,31 +4009,29 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>228</v>
+        <v>152</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>159</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F60" t="s">
-        <v>230</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G60" s="4"/>
       <c r="H60" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>26</v>
@@ -3841,25 +4042,23 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>232</v>
+        <v>152</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F61" t="s">
-        <v>234</v>
-      </c>
-      <c r="G61" t="s">
-        <v>235</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G61"/>
       <c r="H61" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>19</v>
@@ -3876,25 +4075,23 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>236</v>
+        <v>152</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F62" t="s">
-        <v>238</v>
-      </c>
-      <c r="G62" t="s">
-        <v>239</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G62"/>
       <c r="H62" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>19</v>
@@ -3911,29 +4108,29 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>241</v>
+        <v>166</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>167</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F63" t="s">
-        <v>243</v>
+        <v>168</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J63" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>26</v>
@@ -3944,29 +4141,29 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>244</v>
+        <v>166</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F64" t="s">
-        <v>246</v>
+        <v>170</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>26</v>
@@ -3977,29 +4174,29 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>248</v>
+        <v>171</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F65" t="s">
-        <v>250</v>
+        <v>173</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J65" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>26</v>
@@ -4010,29 +4207,29 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>251</v>
+        <v>171</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>174</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F66" t="s">
-        <v>253</v>
+        <v>175</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J66" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>26</v>
@@ -4043,29 +4240,29 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>254</v>
+        <v>171</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F67" t="s">
-        <v>256</v>
+        <v>177</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J67" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>26</v>
@@ -4076,25 +4273,23 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>257</v>
+        <v>171</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F68" t="s">
-        <v>259</v>
-      </c>
-      <c r="G68" t="s">
-        <v>260</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G68"/>
       <c r="H68" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>19</v>
@@ -4111,25 +4306,23 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>263</v>
+        <v>181</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G69" t="s">
-        <v>266</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G69"/>
       <c r="H69" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>19</v>
@@ -4146,25 +4339,23 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>267</v>
+        <v>181</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G70" t="s">
-        <v>270</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G70"/>
       <c r="H70" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>19</v>
@@ -4181,25 +4372,23 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>271</v>
+        <v>181</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>186</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="G71" t="s">
-        <v>274</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G71"/>
       <c r="H71" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>19</v>
@@ -4216,25 +4405,23 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>275</v>
+        <v>181</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>189</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G72" t="s">
-        <v>278</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G72"/>
       <c r="H72" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>19</v>
@@ -4251,25 +4438,23 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>279</v>
+        <v>181</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>282</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G73" s="5"/>
       <c r="H73" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>19</v>
@@ -4286,25 +4471,23 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>283</v>
+        <v>181</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>286</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G74" s="5"/>
       <c r="H74" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>19</v>
@@ -4321,25 +4504,23 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>287</v>
+        <v>181</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>290</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G75" s="5"/>
       <c r="H75" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>19</v>
@@ -4356,25 +4537,23 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>291</v>
+        <v>181</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>294</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G76" s="4"/>
       <c r="H76" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>19</v>
@@ -4391,25 +4570,23 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>295</v>
+        <v>181</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>298</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G77" s="4"/>
       <c r="H77" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>19</v>
@@ -4426,25 +4603,23 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>299</v>
+        <v>181</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="G78" t="s">
-        <v>302</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G78"/>
       <c r="H78" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>19</v>
@@ -4461,25 +4636,23 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>303</v>
+        <v>181</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F79" t="s">
-        <v>305</v>
-      </c>
-      <c r="G79" t="s">
-        <v>306</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G79"/>
       <c r="H79" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>19</v>
@@ -4496,25 +4669,23 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>307</v>
+        <v>181</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>310</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>19</v>
@@ -4531,25 +4702,23 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>311</v>
+        <v>181</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>314</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G81" s="4"/>
       <c r="H81" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>19</v>
@@ -4566,25 +4735,23 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>315</v>
+        <v>181</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>213</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>318</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>19</v>
@@ -4601,25 +4768,23 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>319</v>
+        <v>181</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>322</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G83" s="5"/>
       <c r="H83" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>19</v>
@@ -4636,25 +4801,23 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>323</v>
+        <v>181</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F84" t="s">
-        <v>325</v>
-      </c>
-      <c r="G84" t="s">
-        <v>326</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G84"/>
       <c r="H84" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>19</v>
@@ -4671,25 +4834,23 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>327</v>
+        <v>181</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F85" t="s">
-        <v>329</v>
-      </c>
-      <c r="G85" t="s">
-        <v>330</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G85"/>
       <c r="H85" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>19</v>
@@ -4706,28 +4867,26 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>331</v>
+        <v>181</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>334</v>
+        <v>224</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>19</v>
@@ -4741,28 +4900,26 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>335</v>
+        <v>181</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G87" s="4"/>
       <c r="H87" s="4" t="s">
-        <v>334</v>
+        <v>224</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>19</v>
@@ -4776,29 +4933,27 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>338</v>
+        <v>181</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F88" t="s">
-        <v>340</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>26</v>
@@ -4809,26 +4964,26 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>341</v>
+        <v>181</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>343</v>
+        <v>230</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
@@ -4840,26 +4995,26 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>345</v>
+        <v>181</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>347</v>
+        <v>233</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4" t="s">
@@ -4871,26 +5026,26 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>348</v>
+        <v>181</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>234</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>350</v>
+        <v>235</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
@@ -4902,26 +5057,26 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>351</v>
+        <v>181</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>353</v>
+        <v>237</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
@@ -4933,29 +5088,29 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>354</v>
+        <v>181</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F93" t="s">
-        <v>356</v>
+        <v>239</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>357</v>
+        <v>240</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>26</v>
@@ -4966,29 +5121,29 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>358</v>
+        <v>181</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>241</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="F94" t="s">
-        <v>360</v>
+        <v>242</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>357</v>
+        <v>240</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>26</v>
@@ -4999,25 +5154,23 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>361</v>
+        <v>181</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>243</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F95" t="s">
-        <v>363</v>
-      </c>
-      <c r="G95" t="s">
-        <v>364</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G95"/>
       <c r="H95" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>19</v>
@@ -5034,25 +5187,23 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>365</v>
+        <v>181</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="F96" t="s">
-        <v>367</v>
-      </c>
-      <c r="G96" t="s">
-        <v>368</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G96"/>
       <c r="H96" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>19</v>
@@ -5069,26 +5220,26 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>369</v>
+        <v>181</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="F97" t="s">
+        <v>248</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>371</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4" t="s">
@@ -5100,29 +5251,29 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D98" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>375</v>
+        <v>251</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>26</v>
@@ -5133,25 +5284,23 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>376</v>
+        <v>181</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F99" t="s">
-        <v>378</v>
-      </c>
-      <c r="G99" t="s">
-        <v>379</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G99"/>
       <c r="H99" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>19</v>
@@ -5168,25 +5317,23 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>380</v>
+        <v>181</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="F100" t="s">
-        <v>382</v>
-      </c>
-      <c r="G100" t="s">
-        <v>383</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G100"/>
       <c r="H100" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>19</v>
@@ -5203,25 +5350,23 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>384</v>
+        <v>181</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F101" t="s">
-        <v>386</v>
-      </c>
-      <c r="G101" t="s">
-        <v>387</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G101"/>
       <c r="H101" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>19</v>
@@ -5238,26 +5383,26 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>388</v>
+        <v>181</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F102" t="s">
-        <v>390</v>
+        <v>259</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>19</v>
@@ -5271,26 +5416,26 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F103" t="s">
-        <v>393</v>
+      <c r="F103" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>19</v>
@@ -5304,26 +5449,26 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C104" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>394</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F104" t="s">
-        <v>396</v>
+        <v>263</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4" t="s">
@@ -5335,25 +5480,23 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>398</v>
+        <v>264</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>265</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>401</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G105" s="5"/>
       <c r="H105" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>19</v>
@@ -5370,25 +5513,23 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>402</v>
+        <v>268</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>403</v>
+        <v>269</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F106" t="s">
-        <v>405</v>
-      </c>
-      <c r="G106" t="s">
-        <v>406</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G106"/>
       <c r="H106" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>19</v>
@@ -5405,25 +5546,23 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>402</v>
+        <v>268</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>407</v>
+        <v>271</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F107" t="s">
-        <v>409</v>
-      </c>
-      <c r="G107" t="s">
-        <v>410</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G107"/>
       <c r="H107" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5440,25 +5579,23 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>411</v>
+        <v>268</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F108" t="s">
-        <v>413</v>
-      </c>
-      <c r="G108" t="s">
-        <v>414</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G108"/>
       <c r="H108" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>19</v>
@@ -5475,25 +5612,23 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>415</v>
+        <v>268</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="F109" t="s">
-        <v>417</v>
-      </c>
-      <c r="G109" t="s">
-        <v>418</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G109"/>
       <c r="H109" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>19</v>
@@ -5510,25 +5645,23 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>419</v>
+        <v>268</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F110" t="s">
-        <v>421</v>
-      </c>
-      <c r="G110" t="s">
-        <v>422</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G110"/>
       <c r="H110" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>19</v>
@@ -5545,26 +5678,26 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>423</v>
+        <v>268</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>279</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="F111" t="s">
-        <v>425</v>
+        <v>280</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>19</v>
@@ -5578,28 +5711,26 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>427</v>
+        <v>281</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>282</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F112" t="s">
-        <v>429</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G112" s="4"/>
       <c r="H112" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>19</v>
@@ -5613,28 +5744,26 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>430</v>
+        <v>281</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F113" t="s">
-        <v>432</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G113" s="4"/>
       <c r="H113" s="4" t="s">
-        <v>344</v>
+        <v>231</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>19</v>
@@ -5648,28 +5777,26 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>433</v>
+        <v>281</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F114" t="s">
-        <v>435</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G114" s="4"/>
       <c r="H114" s="4" t="s">
-        <v>334</v>
+        <v>224</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>19</v>
